--- a/Data/stocks_data.xlsx
+++ b/Data/stocks_data.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5293295e4a5c52e/Documents/QF634/QF634_Research_Methods/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_DCBFBB33F4C4EE63E5C257B7DBEBB376ABD02B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97B5FAAF-58CB-4A19-8A78-2C3FD9C772C0}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_76CD2EE0D7B7477F159F423C8B89990BF2D46F76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9B052B0-3A61-42C9-9DD1-D616DFFC97CE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="APPL" sheetId="1" r:id="rId1"/>
+    <sheet name="AAPL" sheetId="1" r:id="rId1"/>
     <sheet name="MSFT" sheetId="2" r:id="rId2"/>
     <sheet name="PG" sheetId="3" r:id="rId3"/>
     <sheet name="XOM" sheetId="4" r:id="rId4"/>
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="7">
   <si>
-    <t>Date</t>
+    <t>date</t>
   </si>
   <si>
     <t>Adj Close</t>
@@ -419,7 +419,7 @@
   <dimension ref="A1:G482"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="20.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -450,7 +450,7 @@
         <v>44929</v>
       </c>
       <c r="B2">
-        <v>123.7684631347656</v>
+        <v>123.76845550537109</v>
       </c>
       <c r="C2">
         <v>125.0699996948242</v>
@@ -473,7 +473,7 @@
         <v>44930</v>
       </c>
       <c r="B3">
-        <v>125.045036315918</v>
+        <v>125.0450439453125</v>
       </c>
       <c r="C3">
         <v>126.36000061035161</v>
@@ -496,7 +496,7 @@
         <v>44931</v>
       </c>
       <c r="B4">
-        <v>123.71897888183589</v>
+        <v>123.7189865112305</v>
       </c>
       <c r="C4">
         <v>125.01999664306641</v>
@@ -565,7 +565,7 @@
         <v>44936</v>
       </c>
       <c r="B7">
-        <v>129.3695373535156</v>
+        <v>129.36956787109381</v>
       </c>
       <c r="C7">
         <v>130.72999572753909</v>
@@ -611,7 +611,7 @@
         <v>44938</v>
       </c>
       <c r="B9">
-        <v>132.02166748046881</v>
+        <v>132.02168273925781</v>
       </c>
       <c r="C9">
         <v>133.4100036621094</v>
@@ -634,7 +634,7 @@
         <v>44939</v>
       </c>
       <c r="B10">
-        <v>133.35762023925781</v>
+        <v>133.3576354980469</v>
       </c>
       <c r="C10">
         <v>134.75999450683591</v>
@@ -680,7 +680,7 @@
         <v>44944</v>
       </c>
       <c r="B12">
-        <v>133.8029479980469</v>
+        <v>133.80293273925781</v>
       </c>
       <c r="C12">
         <v>135.21000671386719</v>
@@ -703,7 +703,7 @@
         <v>44945</v>
       </c>
       <c r="B13">
-        <v>133.86228942871091</v>
+        <v>133.86231994628909</v>
       </c>
       <c r="C13">
         <v>135.27000427246091</v>
@@ -749,7 +749,7 @@
         <v>44949</v>
       </c>
       <c r="B15">
-        <v>139.64154052734381</v>
+        <v>139.64155578613281</v>
       </c>
       <c r="C15">
         <v>141.11000061035159</v>
@@ -772,7 +772,7 @@
         <v>44950</v>
       </c>
       <c r="B16">
-        <v>141.0467529296875</v>
+        <v>141.04676818847659</v>
       </c>
       <c r="C16">
         <v>142.5299987792969</v>
@@ -795,7 +795,7 @@
         <v>44951</v>
       </c>
       <c r="B17">
-        <v>140.38374328613281</v>
+        <v>140.38371276855469</v>
       </c>
       <c r="C17">
         <v>141.86000061035159</v>
@@ -818,7 +818,7 @@
         <v>44952</v>
       </c>
       <c r="B18">
-        <v>142.46189880371091</v>
+        <v>142.46185302734381</v>
       </c>
       <c r="C18">
         <v>143.96000671386719</v>
@@ -841,7 +841,7 @@
         <v>44953</v>
       </c>
       <c r="B19">
-        <v>144.41139221191409</v>
+        <v>144.411376953125</v>
       </c>
       <c r="C19">
         <v>145.92999267578119</v>
@@ -1002,7 +1002,7 @@
         <v>44964</v>
       </c>
       <c r="B26">
-        <v>153.04063415527341</v>
+        <v>153.0406188964844</v>
       </c>
       <c r="C26">
         <v>154.6499938964844</v>
@@ -1048,7 +1048,7 @@
         <v>44966</v>
       </c>
       <c r="B28">
-        <v>149.29997253417969</v>
+        <v>149.2999572753906</v>
       </c>
       <c r="C28">
         <v>150.8699951171875</v>
@@ -1071,7 +1071,7 @@
         <v>44967</v>
       </c>
       <c r="B29">
-        <v>149.66668701171881</v>
+        <v>149.66667175292969</v>
       </c>
       <c r="C29">
         <v>151.00999450683591</v>
@@ -1117,7 +1117,7 @@
         <v>44971</v>
       </c>
       <c r="B31">
-        <v>151.83720397949219</v>
+        <v>151.8371887207031</v>
       </c>
       <c r="C31">
         <v>153.19999694824219</v>
@@ -1163,7 +1163,7 @@
         <v>44973</v>
       </c>
       <c r="B33">
-        <v>152.3426818847656</v>
+        <v>152.34266662597659</v>
       </c>
       <c r="C33">
         <v>153.71000671386719</v>
@@ -1186,7 +1186,7 @@
         <v>44974</v>
       </c>
       <c r="B34">
-        <v>151.1929931640625</v>
+        <v>151.19297790527341</v>
       </c>
       <c r="C34">
         <v>152.55000305175781</v>
@@ -1255,7 +1255,7 @@
         <v>44980</v>
       </c>
       <c r="B37">
-        <v>148.07099914550781</v>
+        <v>148.0710144042969</v>
       </c>
       <c r="C37">
         <v>149.3999938964844</v>
@@ -1301,7 +1301,7 @@
         <v>44984</v>
       </c>
       <c r="B39">
-        <v>146.6041564941406</v>
+        <v>146.60418701171881</v>
       </c>
       <c r="C39">
         <v>147.91999816894531</v>
@@ -1324,7 +1324,7 @@
         <v>44985</v>
       </c>
       <c r="B40">
-        <v>146.09869384765619</v>
+        <v>146.0987243652344</v>
       </c>
       <c r="C40">
         <v>147.4100036621094</v>
@@ -1347,7 +1347,7 @@
         <v>44986</v>
       </c>
       <c r="B41">
-        <v>144.01737976074219</v>
+        <v>144.01739501953119</v>
       </c>
       <c r="C41">
         <v>145.30999755859381</v>
@@ -1370,7 +1370,7 @@
         <v>44987</v>
       </c>
       <c r="B42">
-        <v>144.61207580566409</v>
+        <v>144.61204528808591</v>
       </c>
       <c r="C42">
         <v>145.9100036621094</v>
@@ -1393,7 +1393,7 @@
         <v>44988</v>
       </c>
       <c r="B43">
-        <v>149.68650817871091</v>
+        <v>149.6864929199219</v>
       </c>
       <c r="C43">
         <v>151.0299987792969</v>
@@ -1416,7 +1416,7 @@
         <v>44991</v>
       </c>
       <c r="B44">
-        <v>152.46159362792969</v>
+        <v>152.4615783691406</v>
       </c>
       <c r="C44">
         <v>153.83000183105469</v>
@@ -1485,7 +1485,7 @@
         <v>44994</v>
       </c>
       <c r="B47">
-        <v>149.2503967285156</v>
+        <v>149.25041198730469</v>
       </c>
       <c r="C47">
         <v>150.5899963378906</v>
@@ -1600,7 +1600,7 @@
         <v>45001</v>
       </c>
       <c r="B52">
-        <v>154.46363830566409</v>
+        <v>154.46360778808591</v>
       </c>
       <c r="C52">
         <v>155.8500061035156</v>
@@ -1623,7 +1623,7 @@
         <v>45002</v>
       </c>
       <c r="B53">
-        <v>153.6212158203125</v>
+        <v>153.6211853027344</v>
       </c>
       <c r="C53">
         <v>155</v>
@@ -1646,7 +1646,7 @@
         <v>45005</v>
       </c>
       <c r="B54">
-        <v>155.9998474121094</v>
+        <v>155.99983215332031</v>
       </c>
       <c r="C54">
         <v>157.3999938964844</v>
@@ -1669,7 +1669,7 @@
         <v>45006</v>
       </c>
       <c r="B55">
-        <v>157.86309814453119</v>
+        <v>157.8631286621094</v>
       </c>
       <c r="C55">
         <v>159.2799987792969</v>
@@ -1715,7 +1715,7 @@
         <v>45008</v>
       </c>
       <c r="B57">
-        <v>157.51622009277341</v>
+        <v>157.5162353515625</v>
       </c>
       <c r="C57">
         <v>158.92999267578119</v>
@@ -1738,7 +1738,7 @@
         <v>45009</v>
       </c>
       <c r="B58">
-        <v>158.8244934082031</v>
+        <v>158.82447814941409</v>
       </c>
       <c r="C58">
         <v>160.25</v>
@@ -1761,7 +1761,7 @@
         <v>45012</v>
       </c>
       <c r="B59">
-        <v>156.87202453613281</v>
+        <v>156.87200927734381</v>
       </c>
       <c r="C59">
         <v>158.2799987792969</v>
@@ -1784,7 +1784,7 @@
         <v>45013</v>
       </c>
       <c r="B60">
-        <v>156.24760437011719</v>
+        <v>156.24761962890619</v>
       </c>
       <c r="C60">
         <v>157.6499938964844</v>
@@ -1899,7 +1899,7 @@
         <v>45020</v>
       </c>
       <c r="B65">
-        <v>164.1566467285156</v>
+        <v>164.15663146972659</v>
       </c>
       <c r="C65">
         <v>165.6300048828125</v>
@@ -1922,7 +1922,7 @@
         <v>45021</v>
       </c>
       <c r="B66">
-        <v>162.3032531738281</v>
+        <v>162.30326843261719</v>
       </c>
       <c r="C66">
         <v>163.75999450683591</v>
@@ -1945,7 +1945,7 @@
         <v>45022</v>
       </c>
       <c r="B67">
-        <v>163.19526672363281</v>
+        <v>163.19525146484381</v>
       </c>
       <c r="C67">
         <v>164.6600036621094</v>
@@ -1991,7 +1991,7 @@
         <v>45027</v>
       </c>
       <c r="B69">
-        <v>159.36961364746091</v>
+        <v>159.3695983886719</v>
       </c>
       <c r="C69">
         <v>160.80000305175781</v>
@@ -2014,7 +2014,7 @@
         <v>45028</v>
       </c>
       <c r="B70">
-        <v>158.6758117675781</v>
+        <v>158.67582702636719</v>
       </c>
       <c r="C70">
         <v>160.1000061035156</v>
@@ -2037,7 +2037,7 @@
         <v>45029</v>
       </c>
       <c r="B71">
-        <v>164.0872497558594</v>
+        <v>164.08726501464841</v>
       </c>
       <c r="C71">
         <v>165.55999755859381</v>
@@ -2060,7 +2060,7 @@
         <v>45030</v>
       </c>
       <c r="B72">
-        <v>163.74037170410159</v>
+        <v>163.7403869628906</v>
       </c>
       <c r="C72">
         <v>165.21000671386719</v>
@@ -2106,7 +2106,7 @@
         <v>45034</v>
       </c>
       <c r="B74">
-        <v>164.98915100097659</v>
+        <v>164.9891662597656</v>
       </c>
       <c r="C74">
         <v>166.4700012207031</v>
@@ -2152,7 +2152,7 @@
         <v>45036</v>
       </c>
       <c r="B76">
-        <v>165.16754150390619</v>
+        <v>165.16755676269531</v>
       </c>
       <c r="C76">
         <v>166.6499938964844</v>
@@ -2175,7 +2175,7 @@
         <v>45037</v>
       </c>
       <c r="B77">
-        <v>163.55207824707031</v>
+        <v>163.55204772949219</v>
       </c>
       <c r="C77">
         <v>165.02000427246091</v>
@@ -2198,7 +2198,7 @@
         <v>45040</v>
       </c>
       <c r="B78">
-        <v>163.85929870605469</v>
+        <v>163.85931396484381</v>
       </c>
       <c r="C78">
         <v>165.33000183105469</v>
@@ -2221,7 +2221,7 @@
         <v>45041</v>
       </c>
       <c r="B79">
-        <v>162.31317138671881</v>
+        <v>162.31318664550781</v>
       </c>
       <c r="C79">
         <v>163.77000427246091</v>
@@ -2244,7 +2244,7 @@
         <v>45042</v>
       </c>
       <c r="B80">
-        <v>162.3032531738281</v>
+        <v>162.30326843261719</v>
       </c>
       <c r="C80">
         <v>163.75999450683591</v>
@@ -2267,7 +2267,7 @@
         <v>45043</v>
       </c>
       <c r="B81">
-        <v>166.91192626953119</v>
+        <v>166.91191101074219</v>
       </c>
       <c r="C81">
         <v>168.4100036621094</v>
@@ -2290,7 +2290,7 @@
         <v>45044</v>
       </c>
       <c r="B82">
-        <v>168.17059326171881</v>
+        <v>168.17060852050781</v>
       </c>
       <c r="C82">
         <v>169.67999267578119</v>
@@ -2313,7 +2313,7 @@
         <v>45047</v>
       </c>
       <c r="B83">
-        <v>168.0814208984375</v>
+        <v>168.08140563964841</v>
       </c>
       <c r="C83">
         <v>169.5899963378906</v>
@@ -2336,7 +2336,7 @@
         <v>45048</v>
       </c>
       <c r="B84">
-        <v>167.0407409667969</v>
+        <v>167.04072570800781</v>
       </c>
       <c r="C84">
         <v>168.53999328613281</v>
@@ -2359,7 +2359,7 @@
         <v>45049</v>
       </c>
       <c r="B85">
-        <v>165.96044921875</v>
+        <v>165.96043395996091</v>
       </c>
       <c r="C85">
         <v>167.44999694824219</v>
@@ -2382,7 +2382,7 @@
         <v>45050</v>
       </c>
       <c r="B86">
-        <v>164.31520080566409</v>
+        <v>164.31517028808591</v>
       </c>
       <c r="C86">
         <v>165.78999328613281</v>
@@ -2428,7 +2428,7 @@
         <v>45054</v>
       </c>
       <c r="B88">
-        <v>171.95661926269531</v>
+        <v>171.9566345214844</v>
       </c>
       <c r="C88">
         <v>173.5</v>
@@ -2497,7 +2497,7 @@
         <v>45057</v>
       </c>
       <c r="B91">
-        <v>172.20440673828119</v>
+        <v>172.20439147949219</v>
       </c>
       <c r="C91">
         <v>173.75</v>
@@ -2520,7 +2520,7 @@
         <v>45058</v>
       </c>
       <c r="B92">
-        <v>171.271484375</v>
+        <v>171.27146911621091</v>
       </c>
       <c r="C92">
         <v>172.57000732421881</v>
@@ -2635,7 +2635,7 @@
         <v>45065</v>
       </c>
       <c r="B97">
-        <v>173.84197998046881</v>
+        <v>173.84199523925781</v>
       </c>
       <c r="C97">
         <v>175.1600036621094</v>
@@ -2681,7 +2681,7 @@
         <v>45069</v>
       </c>
       <c r="B99">
-        <v>170.2690734863281</v>
+        <v>170.26905822753909</v>
       </c>
       <c r="C99">
         <v>171.55999755859381</v>
@@ -2704,7 +2704,7 @@
         <v>45070</v>
       </c>
       <c r="B100">
-        <v>170.5469665527344</v>
+        <v>170.54698181152341</v>
       </c>
       <c r="C100">
         <v>171.8399963378906</v>
@@ -2865,7 +2865,7 @@
         <v>45082</v>
       </c>
       <c r="B107">
-        <v>178.22871398925781</v>
+        <v>178.22869873046881</v>
       </c>
       <c r="C107">
         <v>179.58000183105469</v>
@@ -2888,7 +2888,7 @@
         <v>45083</v>
       </c>
       <c r="B108">
-        <v>177.86152648925781</v>
+        <v>177.86151123046881</v>
       </c>
       <c r="C108">
         <v>179.21000671386719</v>
@@ -2911,7 +2911,7 @@
         <v>45084</v>
       </c>
       <c r="B109">
-        <v>176.4819641113281</v>
+        <v>176.48199462890619</v>
       </c>
       <c r="C109">
         <v>177.82000732421881</v>
@@ -2934,7 +2934,7 @@
         <v>45085</v>
       </c>
       <c r="B110">
-        <v>179.2112731933594</v>
+        <v>179.21125793457031</v>
       </c>
       <c r="C110">
         <v>180.57000732421881</v>
@@ -2957,7 +2957,7 @@
         <v>45086</v>
       </c>
       <c r="B111">
-        <v>179.5983581542969</v>
+        <v>179.59834289550781</v>
       </c>
       <c r="C111">
         <v>180.96000671386719</v>
@@ -2980,7 +2980,7 @@
         <v>45089</v>
       </c>
       <c r="B112">
-        <v>182.40704345703119</v>
+        <v>182.4070129394531</v>
       </c>
       <c r="C112">
         <v>183.78999328613281</v>
@@ -3003,7 +3003,7 @@
         <v>45090</v>
       </c>
       <c r="B113">
-        <v>181.9306335449219</v>
+        <v>181.93064880371091</v>
       </c>
       <c r="C113">
         <v>183.30999755859381</v>
@@ -3026,7 +3026,7 @@
         <v>45091</v>
       </c>
       <c r="B114">
-        <v>182.56584167480469</v>
+        <v>182.5658264160156</v>
       </c>
       <c r="C114">
         <v>183.94999694824219</v>
@@ -3072,7 +3072,7 @@
         <v>45093</v>
       </c>
       <c r="B116">
-        <v>183.5285339355469</v>
+        <v>183.52851867675781</v>
       </c>
       <c r="C116">
         <v>184.91999816894531</v>
@@ -3095,7 +3095,7 @@
         <v>45097</v>
       </c>
       <c r="B117">
-        <v>183.61784362792969</v>
+        <v>183.61785888671881</v>
       </c>
       <c r="C117">
         <v>185.00999450683591</v>
@@ -3118,7 +3118,7 @@
         <v>45098</v>
       </c>
       <c r="B118">
-        <v>182.5757751464844</v>
+        <v>182.57574462890619</v>
       </c>
       <c r="C118">
         <v>183.96000671386719</v>
@@ -3141,7 +3141,7 @@
         <v>45099</v>
       </c>
       <c r="B119">
-        <v>185.5928955078125</v>
+        <v>185.59288024902341</v>
       </c>
       <c r="C119">
         <v>187</v>
@@ -3164,7 +3164,7 @@
         <v>45100</v>
       </c>
       <c r="B120">
-        <v>185.2752990722656</v>
+        <v>185.2752685546875</v>
       </c>
       <c r="C120">
         <v>186.67999267578119</v>
@@ -3187,7 +3187,7 @@
         <v>45103</v>
       </c>
       <c r="B121">
-        <v>183.87590026855469</v>
+        <v>183.8758850097656</v>
       </c>
       <c r="C121">
         <v>185.27000427246091</v>
@@ -3279,7 +3279,7 @@
         <v>45107</v>
       </c>
       <c r="B125">
-        <v>192.51045227050781</v>
+        <v>192.51043701171881</v>
       </c>
       <c r="C125">
         <v>193.9700012207031</v>
@@ -3302,7 +3302,7 @@
         <v>45110</v>
       </c>
       <c r="B126">
-        <v>191.01179504394531</v>
+        <v>191.0118103027344</v>
       </c>
       <c r="C126">
         <v>192.46000671386719</v>
@@ -3371,7 +3371,7 @@
         <v>45114</v>
       </c>
       <c r="B129">
-        <v>189.24519348144531</v>
+        <v>189.24517822265619</v>
       </c>
       <c r="C129">
         <v>190.67999267578119</v>
@@ -3394,7 +3394,7 @@
         <v>45117</v>
       </c>
       <c r="B130">
-        <v>187.1907653808594</v>
+        <v>187.1907958984375</v>
       </c>
       <c r="C130">
         <v>188.61000061035159</v>
@@ -3417,7 +3417,7 @@
         <v>45118</v>
       </c>
       <c r="B131">
-        <v>186.6647644042969</v>
+        <v>186.66474914550781</v>
       </c>
       <c r="C131">
         <v>188.08000183105469</v>
@@ -3440,7 +3440,7 @@
         <v>45119</v>
       </c>
       <c r="B132">
-        <v>188.34205627441409</v>
+        <v>188.342041015625</v>
       </c>
       <c r="C132">
         <v>189.77000427246091</v>
@@ -3463,7 +3463,7 @@
         <v>45120</v>
       </c>
       <c r="B133">
-        <v>189.10624694824219</v>
+        <v>189.1062316894531</v>
       </c>
       <c r="C133">
         <v>190.53999328613281</v>
@@ -3486,7 +3486,7 @@
         <v>45121</v>
       </c>
       <c r="B134">
-        <v>189.25514221191409</v>
+        <v>189.25511169433591</v>
       </c>
       <c r="C134">
         <v>190.69000244140619</v>
@@ -3532,7 +3532,7 @@
         <v>45125</v>
       </c>
       <c r="B136">
-        <v>192.2722473144531</v>
+        <v>192.27223205566409</v>
       </c>
       <c r="C136">
         <v>193.72999572753909</v>
@@ -3555,7 +3555,7 @@
         <v>45126</v>
       </c>
       <c r="B137">
-        <v>193.6319580078125</v>
+        <v>193.63194274902341</v>
       </c>
       <c r="C137">
         <v>195.1000061035156</v>
@@ -3693,7 +3693,7 @@
         <v>45134</v>
       </c>
       <c r="B143">
-        <v>191.7660827636719</v>
+        <v>191.76609802246091</v>
       </c>
       <c r="C143">
         <v>193.2200012207031</v>
@@ -3716,7 +3716,7 @@
         <v>45135</v>
       </c>
       <c r="B144">
-        <v>194.3564758300781</v>
+        <v>194.35646057128909</v>
       </c>
       <c r="C144">
         <v>195.83000183105469</v>
@@ -3739,7 +3739,7 @@
         <v>45138</v>
       </c>
       <c r="B145">
-        <v>194.9717712402344</v>
+        <v>194.97175598144531</v>
       </c>
       <c r="C145">
         <v>196.44999694824219</v>
@@ -3762,7 +3762,7 @@
         <v>45139</v>
       </c>
       <c r="B146">
-        <v>194.1380920410156</v>
+        <v>194.13810729980469</v>
       </c>
       <c r="C146">
         <v>195.61000061035159</v>
@@ -3785,7 +3785,7 @@
         <v>45140</v>
       </c>
       <c r="B147">
-        <v>191.13092041015619</v>
+        <v>191.13090515136719</v>
       </c>
       <c r="C147">
         <v>192.58000183105469</v>
@@ -3808,7 +3808,7 @@
         <v>45141</v>
       </c>
       <c r="B148">
-        <v>189.73149108886719</v>
+        <v>189.73150634765619</v>
       </c>
       <c r="C148">
         <v>191.16999816894531</v>
@@ -3831,7 +3831,7 @@
         <v>45142</v>
       </c>
       <c r="B149">
-        <v>180.62059020996091</v>
+        <v>180.62060546875</v>
       </c>
       <c r="C149">
         <v>181.99000549316409</v>
@@ -3877,7 +3877,7 @@
         <v>45146</v>
       </c>
       <c r="B151">
-        <v>178.4470520019531</v>
+        <v>178.44708251953119</v>
       </c>
       <c r="C151">
         <v>179.80000305175781</v>
@@ -3900,7 +3900,7 @@
         <v>45147</v>
       </c>
       <c r="B152">
-        <v>176.84919738769531</v>
+        <v>176.84918212890619</v>
       </c>
       <c r="C152">
         <v>178.19000244140619</v>
@@ -3969,7 +3969,7 @@
         <v>45152</v>
       </c>
       <c r="B155">
-        <v>178.35015869140619</v>
+        <v>178.35014343261719</v>
       </c>
       <c r="C155">
         <v>179.46000671386719</v>
@@ -3992,7 +3992,7 @@
         <v>45153</v>
       </c>
       <c r="B156">
-        <v>176.35255432128909</v>
+        <v>176.3525695800781</v>
       </c>
       <c r="C156">
         <v>177.44999694824219</v>
@@ -4015,7 +4015,7 @@
         <v>45154</v>
       </c>
       <c r="B157">
-        <v>175.47804260253909</v>
+        <v>175.47801208496091</v>
       </c>
       <c r="C157">
         <v>176.57000732421881</v>
@@ -4061,7 +4061,7 @@
         <v>45156</v>
       </c>
       <c r="B159">
-        <v>173.41090393066409</v>
+        <v>173.410888671875</v>
       </c>
       <c r="C159">
         <v>174.49000549316409</v>
@@ -4130,7 +4130,7 @@
         <v>45161</v>
       </c>
       <c r="B162">
-        <v>179.99986267089841</v>
+        <v>179.9998779296875</v>
       </c>
       <c r="C162">
         <v>181.1199951171875</v>
@@ -4245,7 +4245,7 @@
         <v>45168</v>
       </c>
       <c r="B167">
-        <v>186.4894714355469</v>
+        <v>186.48948669433591</v>
       </c>
       <c r="C167">
         <v>187.6499938964844</v>
@@ -4337,7 +4337,7 @@
         <v>45175</v>
       </c>
       <c r="B171">
-        <v>181.77880859375</v>
+        <v>181.77882385253909</v>
       </c>
       <c r="C171">
         <v>182.9100036621094</v>
@@ -4360,7 +4360,7 @@
         <v>45176</v>
       </c>
       <c r="B172">
-        <v>176.4618835449219</v>
+        <v>176.46186828613281</v>
       </c>
       <c r="C172">
         <v>177.55999755859381</v>
@@ -4383,7 +4383,7 @@
         <v>45177</v>
       </c>
       <c r="B173">
-        <v>177.0780334472656</v>
+        <v>177.07804870605469</v>
       </c>
       <c r="C173">
         <v>178.17999267578119</v>
@@ -4406,7 +4406,7 @@
         <v>45180</v>
       </c>
       <c r="B174">
-        <v>178.25074768066409</v>
+        <v>178.2507629394531</v>
       </c>
       <c r="C174">
         <v>179.36000061035159</v>
@@ -4429,7 +4429,7 @@
         <v>45181</v>
       </c>
       <c r="B175">
-        <v>175.2096862792969</v>
+        <v>175.20970153808591</v>
       </c>
       <c r="C175">
         <v>176.30000305175781</v>
@@ -4452,7 +4452,7 @@
         <v>45182</v>
       </c>
       <c r="B176">
-        <v>173.13261413574219</v>
+        <v>173.13262939453119</v>
       </c>
       <c r="C176">
         <v>174.21000671386719</v>
@@ -4475,7 +4475,7 @@
         <v>45183</v>
       </c>
       <c r="B177">
-        <v>174.65315246582031</v>
+        <v>174.65313720703119</v>
       </c>
       <c r="C177">
         <v>175.74000549316409</v>
@@ -4567,7 +4567,7 @@
         <v>45189</v>
       </c>
       <c r="B181">
-        <v>174.40470886230469</v>
+        <v>174.4046936035156</v>
       </c>
       <c r="C181">
         <v>175.49000549316409</v>
@@ -4590,7 +4590,7 @@
         <v>45190</v>
       </c>
       <c r="B182">
-        <v>172.8543395996094</v>
+        <v>172.85432434082031</v>
       </c>
       <c r="C182">
         <v>173.92999267578119</v>
@@ -4613,7 +4613,7 @@
         <v>45191</v>
       </c>
       <c r="B183">
-        <v>173.7090148925781</v>
+        <v>173.70899963378909</v>
       </c>
       <c r="C183">
         <v>174.78999328613281</v>
@@ -4636,7 +4636,7 @@
         <v>45194</v>
       </c>
       <c r="B184">
-        <v>174.99104309082031</v>
+        <v>174.9910583496094</v>
       </c>
       <c r="C184">
         <v>176.08000183105469</v>
@@ -4659,7 +4659,7 @@
         <v>45195</v>
       </c>
       <c r="B185">
-        <v>170.89653015136719</v>
+        <v>170.89654541015619</v>
       </c>
       <c r="C185">
         <v>171.96000671386719</v>
@@ -4682,7 +4682,7 @@
         <v>45196</v>
       </c>
       <c r="B186">
-        <v>169.37599182128909</v>
+        <v>169.3759765625</v>
       </c>
       <c r="C186">
         <v>170.42999267578119</v>
@@ -4728,7 +4728,7 @@
         <v>45198</v>
       </c>
       <c r="B188">
-        <v>170.15116882324219</v>
+        <v>170.1511535644531</v>
       </c>
       <c r="C188">
         <v>171.21000671386719</v>
@@ -4751,7 +4751,7 @@
         <v>45201</v>
       </c>
       <c r="B189">
-        <v>172.67546081542969</v>
+        <v>172.6754455566406</v>
       </c>
       <c r="C189">
         <v>173.75</v>
@@ -4866,7 +4866,7 @@
         <v>45208</v>
       </c>
       <c r="B194">
-        <v>177.883056640625</v>
+        <v>177.88304138183591</v>
       </c>
       <c r="C194">
         <v>178.99000549316409</v>
@@ -4889,7 +4889,7 @@
         <v>45209</v>
       </c>
       <c r="B195">
-        <v>177.2867736816406</v>
+        <v>177.28675842285159</v>
       </c>
       <c r="C195">
         <v>178.38999938964841</v>
@@ -4912,7 +4912,7 @@
         <v>45210</v>
       </c>
       <c r="B196">
-        <v>178.68803405761719</v>
+        <v>178.68804931640619</v>
       </c>
       <c r="C196">
         <v>179.80000305175781</v>
@@ -4935,7 +4935,7 @@
         <v>45211</v>
       </c>
       <c r="B197">
-        <v>179.5924377441406</v>
+        <v>179.5924072265625</v>
       </c>
       <c r="C197">
         <v>180.71000671386719</v>
@@ -4981,7 +4981,7 @@
         <v>45215</v>
       </c>
       <c r="B199">
-        <v>177.61473083496091</v>
+        <v>177.61470031738281</v>
       </c>
       <c r="C199">
         <v>178.7200012207031</v>
@@ -5073,7 +5073,7 @@
         <v>45219</v>
       </c>
       <c r="B203">
-        <v>171.81085205078119</v>
+        <v>171.8108215332031</v>
       </c>
       <c r="C203">
         <v>172.8800048828125</v>
@@ -5096,7 +5096,7 @@
         <v>45222</v>
       </c>
       <c r="B204">
-        <v>171.9300842285156</v>
+        <v>171.93009948730469</v>
       </c>
       <c r="C204">
         <v>173</v>
@@ -5119,7 +5119,7 @@
         <v>45223</v>
       </c>
       <c r="B205">
-        <v>172.36737060546881</v>
+        <v>172.36738586425781</v>
       </c>
       <c r="C205">
         <v>173.44000244140619</v>
@@ -5142,7 +5142,7 @@
         <v>45224</v>
       </c>
       <c r="B206">
-        <v>170.0418395996094</v>
+        <v>170.04185485839841</v>
       </c>
       <c r="C206">
         <v>171.1000061035156</v>
@@ -5165,7 +5165,7 @@
         <v>45225</v>
       </c>
       <c r="B207">
-        <v>165.85786437988281</v>
+        <v>165.8578796386719</v>
       </c>
       <c r="C207">
         <v>166.88999938964841</v>
@@ -5188,7 +5188,7 @@
         <v>45226</v>
       </c>
       <c r="B208">
-        <v>167.17964172363281</v>
+        <v>167.1796569824219</v>
       </c>
       <c r="C208">
         <v>168.2200012207031</v>
@@ -5211,7 +5211,7 @@
         <v>45229</v>
       </c>
       <c r="B209">
-        <v>169.2368469238281</v>
+        <v>169.23683166503909</v>
       </c>
       <c r="C209">
         <v>170.28999328613281</v>
@@ -5234,7 +5234,7 @@
         <v>45230</v>
       </c>
       <c r="B210">
-        <v>169.7138977050781</v>
+        <v>169.71388244628909</v>
       </c>
       <c r="C210">
         <v>170.77000427246091</v>
@@ -5395,7 +5395,7 @@
         <v>45239</v>
       </c>
       <c r="B217">
-        <v>181.2818908691406</v>
+        <v>181.28190612792969</v>
       </c>
       <c r="C217">
         <v>182.4100036621094</v>
@@ -5441,7 +5441,7 @@
         <v>45243</v>
       </c>
       <c r="B219">
-        <v>183.8990783691406</v>
+        <v>183.89906311035159</v>
       </c>
       <c r="C219">
         <v>184.80000305175781</v>
@@ -5510,7 +5510,7 @@
         <v>45246</v>
       </c>
       <c r="B222">
-        <v>188.7851257324219</v>
+        <v>188.78515625</v>
       </c>
       <c r="C222">
         <v>189.71000671386719</v>
@@ -5533,7 +5533,7 @@
         <v>45247</v>
       </c>
       <c r="B223">
-        <v>188.76524353027341</v>
+        <v>188.7652282714844</v>
       </c>
       <c r="C223">
         <v>189.69000244140619</v>
@@ -5556,7 +5556,7 @@
         <v>45250</v>
       </c>
       <c r="B224">
-        <v>190.51664733886719</v>
+        <v>190.51666259765619</v>
       </c>
       <c r="C224">
         <v>191.44999694824219</v>
@@ -5579,7 +5579,7 @@
         <v>45251</v>
       </c>
       <c r="B225">
-        <v>189.71058654785159</v>
+        <v>189.7106018066406</v>
       </c>
       <c r="C225">
         <v>190.63999938964841</v>
@@ -5648,7 +5648,7 @@
         <v>45257</v>
       </c>
       <c r="B228">
-        <v>188.86473083496091</v>
+        <v>188.86474609375</v>
       </c>
       <c r="C228">
         <v>189.78999328613281</v>
@@ -5717,7 +5717,7 @@
         <v>45260</v>
       </c>
       <c r="B231">
-        <v>189.0239562988281</v>
+        <v>189.02397155761719</v>
       </c>
       <c r="C231">
         <v>189.94999694824219</v>
@@ -5763,7 +5763,7 @@
         <v>45264</v>
       </c>
       <c r="B233">
-        <v>188.50648498535159</v>
+        <v>188.5065002441406</v>
       </c>
       <c r="C233">
         <v>189.42999267578119</v>
@@ -5786,7 +5786,7 @@
         <v>45265</v>
       </c>
       <c r="B234">
-        <v>192.47703552246091</v>
+        <v>192.47705078125</v>
       </c>
       <c r="C234">
         <v>193.41999816894531</v>
@@ -5809,7 +5809,7 @@
         <v>45266</v>
       </c>
       <c r="B235">
-        <v>191.38240051269531</v>
+        <v>191.3824157714844</v>
       </c>
       <c r="C235">
         <v>192.32000732421881</v>
@@ -5855,7 +5855,7 @@
         <v>45268</v>
       </c>
       <c r="B237">
-        <v>194.75587463378909</v>
+        <v>194.7558898925781</v>
       </c>
       <c r="C237">
         <v>195.71000671386719</v>
@@ -5901,7 +5901,7 @@
         <v>45272</v>
       </c>
       <c r="B239">
-        <v>193.7607727050781</v>
+        <v>193.76078796386719</v>
       </c>
       <c r="C239">
         <v>194.71000671386719</v>
@@ -5924,7 +5924,7 @@
         <v>45273</v>
       </c>
       <c r="B240">
-        <v>196.99493408203119</v>
+        <v>196.99491882324219</v>
       </c>
       <c r="C240">
         <v>197.96000671386719</v>
@@ -5970,7 +5970,7 @@
         <v>45275</v>
       </c>
       <c r="B242">
-        <v>196.6068115234375</v>
+        <v>196.60682678222659</v>
       </c>
       <c r="C242">
         <v>197.57000732421881</v>
@@ -5993,7 +5993,7 @@
         <v>45278</v>
       </c>
       <c r="B243">
-        <v>194.93499755859381</v>
+        <v>194.93501281738281</v>
       </c>
       <c r="C243">
         <v>195.88999938964841</v>
@@ -6016,7 +6016,7 @@
         <v>45279</v>
       </c>
       <c r="B244">
-        <v>195.97990417480469</v>
+        <v>195.9798889160156</v>
       </c>
       <c r="C244">
         <v>196.94000244140619</v>
@@ -6062,7 +6062,7 @@
         <v>45281</v>
       </c>
       <c r="B246">
-        <v>193.73088073730469</v>
+        <v>193.73089599609381</v>
       </c>
       <c r="C246">
         <v>194.67999267578119</v>
@@ -6108,7 +6108,7 @@
         <v>45286</v>
       </c>
       <c r="B248">
-        <v>192.1088562011719</v>
+        <v>192.10887145996091</v>
       </c>
       <c r="C248">
         <v>193.05000305175781</v>
@@ -6131,7 +6131,7 @@
         <v>45287</v>
       </c>
       <c r="B249">
-        <v>192.2083740234375</v>
+        <v>192.20835876464841</v>
       </c>
       <c r="C249">
         <v>193.1499938964844</v>
@@ -6154,7 +6154,7 @@
         <v>45288</v>
       </c>
       <c r="B250">
-        <v>192.63627624511719</v>
+        <v>192.63629150390619</v>
       </c>
       <c r="C250">
         <v>193.58000183105469</v>
@@ -6200,7 +6200,7 @@
         <v>45293</v>
       </c>
       <c r="B252">
-        <v>184.7349853515625</v>
+        <v>184.73497009277341</v>
       </c>
       <c r="C252">
         <v>185.63999938964841</v>
@@ -6246,7 +6246,7 @@
         <v>45295</v>
       </c>
       <c r="B254">
-        <v>181.0231628417969</v>
+        <v>181.02317810058591</v>
       </c>
       <c r="C254">
         <v>181.9100036621094</v>
@@ -6269,7 +6269,7 @@
         <v>45296</v>
       </c>
       <c r="B255">
-        <v>180.2967224121094</v>
+        <v>180.29670715332031</v>
       </c>
       <c r="C255">
         <v>181.17999267578119</v>
@@ -6384,7 +6384,7 @@
         <v>45303</v>
       </c>
       <c r="B260">
-        <v>185.01359558105469</v>
+        <v>185.01361083984381</v>
       </c>
       <c r="C260">
         <v>185.91999816894531</v>
@@ -6407,7 +6407,7 @@
         <v>45307</v>
       </c>
       <c r="B261">
-        <v>182.7347717285156</v>
+        <v>182.73478698730469</v>
       </c>
       <c r="C261">
         <v>183.6300048828125</v>
@@ -6453,7 +6453,7 @@
         <v>45309</v>
       </c>
       <c r="B263">
-        <v>187.71040344238281</v>
+        <v>187.7104187011719</v>
       </c>
       <c r="C263">
         <v>188.6300048828125</v>
@@ -6545,7 +6545,7 @@
         <v>45315</v>
       </c>
       <c r="B267">
-        <v>193.55177307128909</v>
+        <v>193.5517883300781</v>
       </c>
       <c r="C267">
         <v>194.5</v>
@@ -6568,7 +6568,7 @@
         <v>45316</v>
       </c>
       <c r="B268">
-        <v>193.22340393066409</v>
+        <v>193.223388671875</v>
       </c>
       <c r="C268">
         <v>194.16999816894531</v>
@@ -6614,7 +6614,7 @@
         <v>45320</v>
       </c>
       <c r="B270">
-        <v>190.7952880859375</v>
+        <v>190.79530334472659</v>
       </c>
       <c r="C270">
         <v>191.72999572753909</v>
@@ -6637,7 +6637,7 @@
         <v>45321</v>
       </c>
       <c r="B271">
-        <v>187.1232604980469</v>
+        <v>187.12327575683591</v>
       </c>
       <c r="C271">
         <v>188.03999328613281</v>
@@ -6729,7 +6729,7 @@
         <v>45327</v>
       </c>
       <c r="B275">
-        <v>186.76502990722659</v>
+        <v>186.7650451660156</v>
       </c>
       <c r="C275">
         <v>187.67999267578119</v>
@@ -6798,7 +6798,7 @@
         <v>45330</v>
       </c>
       <c r="B278">
-        <v>187.40193176269531</v>
+        <v>187.40191650390619</v>
       </c>
       <c r="C278">
         <v>188.32000732421881</v>
@@ -6821,7 +6821,7 @@
         <v>45331</v>
       </c>
       <c r="B279">
-        <v>188.16912841796881</v>
+        <v>188.16914367675781</v>
       </c>
       <c r="C279">
         <v>188.8500061035156</v>
@@ -7005,7 +7005,7 @@
         <v>45344</v>
       </c>
       <c r="B287">
-        <v>183.7052917480469</v>
+        <v>183.70526123046881</v>
       </c>
       <c r="C287">
         <v>184.3699951171875</v>
@@ -7028,7 +7028,7 @@
         <v>45345</v>
       </c>
       <c r="B288">
-        <v>181.86195373535159</v>
+        <v>181.8619689941406</v>
       </c>
       <c r="C288">
         <v>182.52000427246091</v>
@@ -7051,7 +7051,7 @@
         <v>45348</v>
       </c>
       <c r="B289">
-        <v>180.50685119628909</v>
+        <v>180.5068664550781</v>
       </c>
       <c r="C289">
         <v>181.1600036621094</v>
@@ -7097,7 +7097,7 @@
         <v>45350</v>
       </c>
       <c r="B291">
-        <v>180.76593017578119</v>
+        <v>180.76591491699219</v>
       </c>
       <c r="C291">
         <v>181.41999816894531</v>
@@ -7120,7 +7120,7 @@
         <v>45351</v>
       </c>
       <c r="B292">
-        <v>180.09834289550781</v>
+        <v>180.09832763671881</v>
       </c>
       <c r="C292">
         <v>180.75</v>
@@ -7166,7 +7166,7 @@
         <v>45355</v>
       </c>
       <c r="B294">
-        <v>174.4687194824219</v>
+        <v>174.46870422363281</v>
       </c>
       <c r="C294">
         <v>175.1000061035156</v>
@@ -7212,7 +7212,7 @@
         <v>45357</v>
       </c>
       <c r="B296">
-        <v>168.51025390625</v>
+        <v>168.51026916503909</v>
       </c>
       <c r="C296">
         <v>169.1199951171875</v>
@@ -7235,7 +7235,7 @@
         <v>45358</v>
       </c>
       <c r="B297">
-        <v>168.39068603515619</v>
+        <v>168.39070129394531</v>
       </c>
       <c r="C297">
         <v>169</v>
@@ -7373,7 +7373,7 @@
         <v>45366</v>
       </c>
       <c r="B303">
-        <v>171.99763488769531</v>
+        <v>171.9976501464844</v>
       </c>
       <c r="C303">
         <v>172.6199951171875</v>
@@ -7396,7 +7396,7 @@
         <v>45369</v>
       </c>
       <c r="B304">
-        <v>173.09368896484381</v>
+        <v>173.09367370605469</v>
       </c>
       <c r="C304">
         <v>173.7200012207031</v>
@@ -7419,7 +7419,7 @@
         <v>45370</v>
       </c>
       <c r="B305">
-        <v>175.44517517089841</v>
+        <v>175.4451904296875</v>
       </c>
       <c r="C305">
         <v>176.08000183105469</v>
@@ -7488,7 +7488,7 @@
         <v>45373</v>
       </c>
       <c r="B308">
-        <v>171.65887451171881</v>
+        <v>171.65885925292969</v>
       </c>
       <c r="C308">
         <v>172.2799987792969</v>
@@ -7557,7 +7557,7 @@
         <v>45378</v>
       </c>
       <c r="B311">
-        <v>172.68516540527341</v>
+        <v>172.6851501464844</v>
       </c>
       <c r="C311">
         <v>173.30999755859381</v>
@@ -7580,7 +7580,7 @@
         <v>45379</v>
       </c>
       <c r="B312">
-        <v>170.86175537109381</v>
+        <v>170.86174011230469</v>
       </c>
       <c r="C312">
         <v>171.47999572753909</v>
@@ -7603,7 +7603,7 @@
         <v>45383</v>
       </c>
       <c r="B313">
-        <v>169.41697692871091</v>
+        <v>169.4169921875</v>
       </c>
       <c r="C313">
         <v>170.0299987792969</v>
@@ -7626,7 +7626,7 @@
         <v>45384</v>
       </c>
       <c r="B314">
-        <v>168.23127746582031</v>
+        <v>168.23126220703119</v>
       </c>
       <c r="C314">
         <v>168.8399963378906</v>
@@ -7649,7 +7649,7 @@
         <v>45385</v>
       </c>
       <c r="B315">
-        <v>169.03834533691409</v>
+        <v>169.0383605957031</v>
       </c>
       <c r="C315">
         <v>169.6499938964844</v>
@@ -7672,7 +7672,7 @@
         <v>45386</v>
       </c>
       <c r="B316">
-        <v>168.21134948730469</v>
+        <v>168.21136474609381</v>
       </c>
       <c r="C316">
         <v>168.82000732421881</v>
@@ -7741,7 +7741,7 @@
         <v>45391</v>
       </c>
       <c r="B319">
-        <v>169.05828857421881</v>
+        <v>169.05827331542969</v>
       </c>
       <c r="C319">
         <v>169.66999816894531</v>
@@ -7764,7 +7764,7 @@
         <v>45392</v>
       </c>
       <c r="B320">
-        <v>167.17510986328119</v>
+        <v>167.1750793457031</v>
       </c>
       <c r="C320">
         <v>167.7799987792969</v>
@@ -7856,7 +7856,7 @@
         <v>45398</v>
       </c>
       <c r="B324">
-        <v>168.76934814453119</v>
+        <v>168.76933288574219</v>
       </c>
       <c r="C324">
         <v>169.3800048828125</v>
@@ -7948,7 +7948,7 @@
         <v>45404</v>
       </c>
       <c r="B328">
-        <v>165.2420959472656</v>
+        <v>165.24208068847659</v>
       </c>
       <c r="C328">
         <v>165.8399963378906</v>
@@ -7971,7 +7971,7 @@
         <v>45405</v>
       </c>
       <c r="B329">
-        <v>166.29826354980469</v>
+        <v>166.2982482910156</v>
       </c>
       <c r="C329">
         <v>166.8999938964844</v>
@@ -7994,7 +7994,7 @@
         <v>45406</v>
       </c>
       <c r="B330">
-        <v>168.41064453125</v>
+        <v>168.41062927246091</v>
       </c>
       <c r="C330">
         <v>169.02000427246091</v>
@@ -8086,7 +8086,7 @@
         <v>45412</v>
       </c>
       <c r="B334">
-        <v>169.7159118652344</v>
+        <v>169.71589660644531</v>
       </c>
       <c r="C334">
         <v>170.33000183105469</v>
@@ -8178,7 +8178,7 @@
         <v>45418</v>
       </c>
       <c r="B338">
-        <v>181.05488586425781</v>
+        <v>181.05487060546881</v>
       </c>
       <c r="C338">
         <v>181.71000671386719</v>
@@ -8247,7 +8247,7 @@
         <v>45421</v>
       </c>
       <c r="B341">
-        <v>183.90458679199219</v>
+        <v>183.9045715332031</v>
       </c>
       <c r="C341">
         <v>184.57000732421881</v>
@@ -8270,7 +8270,7 @@
         <v>45422</v>
       </c>
       <c r="B342">
-        <v>182.63743591308591</v>
+        <v>182.6374206542969</v>
       </c>
       <c r="C342">
         <v>183.05000305175781</v>
@@ -8293,7 +8293,7 @@
         <v>45425</v>
       </c>
       <c r="B343">
-        <v>185.8601379394531</v>
+        <v>185.86015319824219</v>
       </c>
       <c r="C343">
         <v>186.2799987792969</v>
@@ -8385,7 +8385,7 @@
         <v>45429</v>
       </c>
       <c r="B347">
-        <v>189.4420471191406</v>
+        <v>189.44206237792969</v>
       </c>
       <c r="C347">
         <v>189.8699951171875</v>
@@ -8454,7 +8454,7 @@
         <v>45434</v>
       </c>
       <c r="B350">
-        <v>190.4697265625</v>
+        <v>190.46974182128909</v>
       </c>
       <c r="C350">
         <v>190.8999938964844</v>
@@ -8523,7 +8523,7 @@
         <v>45440</v>
       </c>
       <c r="B353">
-        <v>189.56178283691409</v>
+        <v>189.5617980957031</v>
       </c>
       <c r="C353">
         <v>189.99000549316409</v>
@@ -8592,7 +8592,7 @@
         <v>45443</v>
       </c>
       <c r="B356">
-        <v>191.8166809082031</v>
+        <v>191.81669616699219</v>
       </c>
       <c r="C356">
         <v>192.25</v>
@@ -8615,7 +8615,7 @@
         <v>45446</v>
       </c>
       <c r="B357">
-        <v>193.5926818847656</v>
+        <v>193.59266662597659</v>
       </c>
       <c r="C357">
         <v>194.0299987792969</v>
@@ -8684,7 +8684,7 @@
         <v>45449</v>
       </c>
       <c r="B360">
-        <v>194.04167175292969</v>
+        <v>194.0416564941406</v>
       </c>
       <c r="C360">
         <v>194.47999572753909</v>
@@ -8707,7 +8707,7 @@
         <v>45450</v>
       </c>
       <c r="B361">
-        <v>196.44622802734381</v>
+        <v>196.44624328613281</v>
       </c>
       <c r="C361">
         <v>196.88999938964841</v>
@@ -8891,7 +8891,7 @@
         <v>45463</v>
       </c>
       <c r="B369">
-        <v>209.2073974609375</v>
+        <v>209.20741271972659</v>
       </c>
       <c r="C369">
         <v>209.67999267578119</v>
@@ -8937,7 +8937,7 @@
         <v>45467</v>
       </c>
       <c r="B371">
-        <v>207.67088317871091</v>
+        <v>207.6708679199219</v>
       </c>
       <c r="C371">
         <v>208.13999938964841</v>
@@ -9190,7 +9190,7 @@
         <v>45483</v>
       </c>
       <c r="B382">
-        <v>232.45489501953119</v>
+        <v>232.45487976074219</v>
       </c>
       <c r="C382">
         <v>232.97999572753909</v>
@@ -9282,7 +9282,7 @@
         <v>45489</v>
       </c>
       <c r="B386">
-        <v>234.2907409667969</v>
+        <v>234.29075622558591</v>
       </c>
       <c r="C386">
         <v>234.82000732421881</v>
@@ -9328,7 +9328,7 @@
         <v>45491</v>
       </c>
       <c r="B388">
-        <v>223.67472839355469</v>
+        <v>223.6747131347656</v>
       </c>
       <c r="C388">
         <v>224.17999267578119</v>
@@ -9420,7 +9420,7 @@
         <v>45497</v>
       </c>
       <c r="B392">
-        <v>218.04743957519531</v>
+        <v>218.04742431640619</v>
       </c>
       <c r="C392">
         <v>218.53999328613281</v>
@@ -9581,7 +9581,7 @@
         <v>45506</v>
       </c>
       <c r="B399">
-        <v>219.3644714355469</v>
+        <v>219.36445617675781</v>
       </c>
       <c r="C399">
         <v>219.86000061035159</v>
@@ -9627,7 +9627,7 @@
         <v>45510</v>
       </c>
       <c r="B401">
-        <v>206.762939453125</v>
+        <v>206.76292419433591</v>
       </c>
       <c r="C401">
         <v>207.22999572753909</v>
@@ -11546,7 +11546,7 @@
         <v>44929</v>
       </c>
       <c r="B2">
-        <v>235.71171569824219</v>
+        <v>235.71168518066409</v>
       </c>
       <c r="C2">
         <v>239.58000183105469</v>
@@ -11569,7 +11569,7 @@
         <v>44930</v>
       </c>
       <c r="B3">
-        <v>225.40093994140619</v>
+        <v>225.40092468261719</v>
       </c>
       <c r="C3">
         <v>229.1000061035156</v>
@@ -11615,7 +11615,7 @@
         <v>44932</v>
       </c>
       <c r="B5">
-        <v>221.2982482910156</v>
+        <v>221.2982177734375</v>
       </c>
       <c r="C5">
         <v>224.92999267578119</v>
@@ -11661,7 +11661,7 @@
         <v>44936</v>
       </c>
       <c r="B7">
-        <v>225.15495300292969</v>
+        <v>225.15496826171881</v>
       </c>
       <c r="C7">
         <v>228.8500061035156</v>
@@ -11684,7 +11684,7 @@
         <v>44937</v>
       </c>
       <c r="B8">
-        <v>231.96321105957031</v>
+        <v>231.96324157714841</v>
       </c>
       <c r="C8">
         <v>235.77000427246091</v>
@@ -11753,7 +11753,7 @@
         <v>44943</v>
       </c>
       <c r="B11">
-        <v>236.4692687988281</v>
+        <v>236.46928405761719</v>
       </c>
       <c r="C11">
         <v>240.3500061035156</v>
@@ -11776,7 +11776,7 @@
         <v>44944</v>
       </c>
       <c r="B12">
-        <v>232.0025939941406</v>
+        <v>232.0025634765625</v>
       </c>
       <c r="C12">
         <v>235.80999755859381</v>
@@ -11799,7 +11799,7 @@
         <v>44945</v>
       </c>
       <c r="B13">
-        <v>228.1852111816406</v>
+        <v>228.18524169921881</v>
       </c>
       <c r="C13">
         <v>231.92999267578119</v>
@@ -11868,7 +11868,7 @@
         <v>44950</v>
       </c>
       <c r="B16">
-        <v>238.1319885253906</v>
+        <v>238.13200378417969</v>
       </c>
       <c r="C16">
         <v>242.03999328613281</v>
@@ -11891,7 +11891,7 @@
         <v>44951</v>
       </c>
       <c r="B17">
-        <v>236.72508239746091</v>
+        <v>236.7250671386719</v>
       </c>
       <c r="C17">
         <v>240.61000061035159</v>
@@ -11914,7 +11914,7 @@
         <v>44952</v>
       </c>
       <c r="B18">
-        <v>243.99577331542969</v>
+        <v>243.99574279785159</v>
       </c>
       <c r="C18">
         <v>248</v>
@@ -11960,7 +11960,7 @@
         <v>44956</v>
       </c>
       <c r="B20">
-        <v>238.79118347167969</v>
+        <v>238.7911682128906</v>
       </c>
       <c r="C20">
         <v>242.71000671386719</v>
@@ -11983,7 +11983,7 @@
         <v>44957</v>
       </c>
       <c r="B21">
-        <v>243.808837890625</v>
+        <v>243.80882263183591</v>
       </c>
       <c r="C21">
         <v>247.80999755859381</v>
@@ -12006,7 +12006,7 @@
         <v>44958</v>
       </c>
       <c r="B22">
-        <v>248.6690368652344</v>
+        <v>248.66905212402341</v>
       </c>
       <c r="C22">
         <v>252.75</v>
@@ -12029,7 +12029,7 @@
         <v>44959</v>
       </c>
       <c r="B23">
-        <v>260.32769775390619</v>
+        <v>260.32772827148438</v>
       </c>
       <c r="C23">
         <v>264.60000610351563</v>
@@ -12052,7 +12052,7 @@
         <v>44960</v>
       </c>
       <c r="B24">
-        <v>254.1786804199219</v>
+        <v>254.17864990234381</v>
       </c>
       <c r="C24">
         <v>258.35000610351563</v>
@@ -12075,7 +12075,7 @@
         <v>44963</v>
       </c>
       <c r="B25">
-        <v>252.62413024902341</v>
+        <v>252.6241455078125</v>
       </c>
       <c r="C25">
         <v>256.76998901367188</v>
@@ -12121,7 +12121,7 @@
         <v>44965</v>
       </c>
       <c r="B27">
-        <v>262.42337036132813</v>
+        <v>262.42333984375</v>
       </c>
       <c r="C27">
         <v>266.73001098632813</v>
@@ -12213,7 +12213,7 @@
         <v>44971</v>
       </c>
       <c r="B31">
-        <v>267.7755126953125</v>
+        <v>267.77554321289063</v>
       </c>
       <c r="C31">
         <v>272.17001342773438</v>
@@ -12236,7 +12236,7 @@
         <v>44972</v>
       </c>
       <c r="B32">
-        <v>265.63519287109381</v>
+        <v>265.63522338867188</v>
       </c>
       <c r="C32">
         <v>269.32000732421881</v>
@@ -12282,7 +12282,7 @@
         <v>44974</v>
       </c>
       <c r="B34">
-        <v>254.52923583984381</v>
+        <v>254.52928161621091</v>
       </c>
       <c r="C34">
         <v>258.05999755859381</v>
@@ -12305,7 +12305,7 @@
         <v>44978</v>
       </c>
       <c r="B35">
-        <v>249.2130126953125</v>
+        <v>249.21299743652341</v>
       </c>
       <c r="C35">
         <v>252.66999816894531</v>
@@ -12328,7 +12328,7 @@
         <v>44979</v>
       </c>
       <c r="B36">
-        <v>248.06886291503909</v>
+        <v>248.0688781738281</v>
       </c>
       <c r="C36">
         <v>251.50999450683591</v>
@@ -12374,7 +12374,7 @@
         <v>44981</v>
       </c>
       <c r="B38">
-        <v>245.81019592285159</v>
+        <v>245.8102111816406</v>
       </c>
       <c r="C38">
         <v>249.2200012207031</v>
@@ -12397,7 +12397,7 @@
         <v>44984</v>
       </c>
       <c r="B39">
-        <v>246.73731994628909</v>
+        <v>246.73735046386719</v>
       </c>
       <c r="C39">
         <v>250.1600036621094</v>
@@ -12443,7 +12443,7 @@
         <v>44986</v>
       </c>
       <c r="B41">
-        <v>242.90057373046881</v>
+        <v>242.90055847167969</v>
       </c>
       <c r="C41">
         <v>246.27000427246091</v>
@@ -12466,7 +12466,7 @@
         <v>44987</v>
       </c>
       <c r="B42">
-        <v>247.6743469238281</v>
+        <v>247.67433166503909</v>
       </c>
       <c r="C42">
         <v>251.11000061035159</v>
@@ -12581,7 +12581,7 @@
         <v>44994</v>
       </c>
       <c r="B47">
-        <v>248.86781311035159</v>
+        <v>248.8677978515625</v>
       </c>
       <c r="C47">
         <v>252.32000732421881</v>
@@ -12604,7 +12604,7 @@
         <v>44995</v>
       </c>
       <c r="B48">
-        <v>245.18882751464841</v>
+        <v>245.18879699707031</v>
       </c>
       <c r="C48">
         <v>248.5899963378906</v>
@@ -12650,7 +12650,7 @@
         <v>44999</v>
       </c>
       <c r="B50">
-        <v>257.22195434570313</v>
+        <v>257.22189331054688</v>
       </c>
       <c r="C50">
         <v>260.79000854492188</v>
@@ -12673,7 +12673,7 @@
         <v>45000</v>
       </c>
       <c r="B51">
-        <v>261.808349609375</v>
+        <v>261.80828857421881</v>
       </c>
       <c r="C51">
         <v>265.44000244140619</v>
@@ -12742,7 +12742,7 @@
         <v>45005</v>
       </c>
       <c r="B54">
-        <v>268.50537109375</v>
+        <v>268.50543212890619</v>
       </c>
       <c r="C54">
         <v>272.23001098632813</v>
@@ -12765,7 +12765,7 @@
         <v>45006</v>
       </c>
       <c r="B55">
-        <v>270.0341796875</v>
+        <v>270.03411865234381</v>
       </c>
       <c r="C55">
         <v>273.77999877929688</v>
@@ -12857,7 +12857,7 @@
         <v>45012</v>
       </c>
       <c r="B59">
-        <v>272.5986328125</v>
+        <v>272.59860229492188</v>
       </c>
       <c r="C59">
         <v>276.3800048828125</v>
@@ -12880,7 +12880,7 @@
         <v>45013</v>
       </c>
       <c r="B60">
-        <v>271.46438598632813</v>
+        <v>271.46435546875</v>
       </c>
       <c r="C60">
         <v>275.23001098632813</v>
@@ -12903,7 +12903,7 @@
         <v>45014</v>
       </c>
       <c r="B61">
-        <v>276.672119140625</v>
+        <v>276.67208862304688</v>
       </c>
       <c r="C61">
         <v>280.510009765625</v>
@@ -12949,7 +12949,7 @@
         <v>45016</v>
       </c>
       <c r="B63">
-        <v>284.35552978515619</v>
+        <v>284.35549926757813</v>
       </c>
       <c r="C63">
         <v>288.29998779296881</v>
@@ -12995,7 +12995,7 @@
         <v>45020</v>
       </c>
       <c r="B65">
-        <v>283.25082397460938</v>
+        <v>283.2508544921875</v>
       </c>
       <c r="C65">
         <v>287.17999267578119</v>
@@ -13018,7 +13018,7 @@
         <v>45021</v>
       </c>
       <c r="B66">
-        <v>280.44967651367188</v>
+        <v>280.44964599609381</v>
       </c>
       <c r="C66">
         <v>284.33999633789063</v>
@@ -13041,7 +13041,7 @@
         <v>45022</v>
       </c>
       <c r="B67">
-        <v>287.6103515625</v>
+        <v>287.61038208007813</v>
       </c>
       <c r="C67">
         <v>291.60000610351563</v>
@@ -13064,7 +13064,7 @@
         <v>45026</v>
       </c>
       <c r="B68">
-        <v>285.43060302734381</v>
+        <v>285.4306640625</v>
       </c>
       <c r="C68">
         <v>289.3900146484375</v>
@@ -13110,7 +13110,7 @@
         <v>45028</v>
       </c>
       <c r="B70">
-        <v>279.61129760742188</v>
+        <v>279.611328125</v>
       </c>
       <c r="C70">
         <v>283.489990234375</v>
@@ -13133,7 +13133,7 @@
         <v>45029</v>
       </c>
       <c r="B71">
-        <v>285.87445068359381</v>
+        <v>285.87442016601563</v>
       </c>
       <c r="C71">
         <v>289.83999633789063</v>
@@ -13156,7 +13156,7 @@
         <v>45030</v>
       </c>
       <c r="B72">
-        <v>282.22509765625</v>
+        <v>282.22512817382813</v>
       </c>
       <c r="C72">
         <v>286.1400146484375</v>
@@ -13179,7 +13179,7 @@
         <v>45033</v>
       </c>
       <c r="B73">
-        <v>284.84860229492188</v>
+        <v>284.84866333007813</v>
       </c>
       <c r="C73">
         <v>288.79998779296881</v>
@@ -13225,7 +13225,7 @@
         <v>45035</v>
       </c>
       <c r="B75">
-        <v>284.50347900390619</v>
+        <v>284.50344848632813</v>
       </c>
       <c r="C75">
         <v>288.45001220703119</v>
@@ -13271,7 +13271,7 @@
         <v>45037</v>
       </c>
       <c r="B77">
-        <v>281.85025024414063</v>
+        <v>281.85031127929688</v>
       </c>
       <c r="C77">
         <v>285.760009765625</v>
@@ -13294,7 +13294,7 @@
         <v>45040</v>
       </c>
       <c r="B78">
-        <v>277.91485595703119</v>
+        <v>277.91482543945313</v>
       </c>
       <c r="C78">
         <v>281.76998901367188</v>
@@ -13317,7 +13317,7 @@
         <v>45041</v>
       </c>
       <c r="B79">
-        <v>271.65176391601563</v>
+        <v>271.6517333984375</v>
       </c>
       <c r="C79">
         <v>275.42001342773438</v>
@@ -13340,7 +13340,7 @@
         <v>45042</v>
       </c>
       <c r="B80">
-        <v>291.32876586914063</v>
+        <v>291.32882690429688</v>
       </c>
       <c r="C80">
         <v>295.3699951171875</v>
@@ -13363,7 +13363,7 @@
         <v>45043</v>
       </c>
       <c r="B81">
-        <v>300.65939331054688</v>
+        <v>300.65933227539063</v>
       </c>
       <c r="C81">
         <v>304.82998657226563</v>
@@ -13386,7 +13386,7 @@
         <v>45044</v>
       </c>
       <c r="B82">
-        <v>303.05612182617188</v>
+        <v>303.05615234375</v>
       </c>
       <c r="C82">
         <v>307.260009765625</v>
@@ -13409,7 +13409,7 @@
         <v>45047</v>
       </c>
       <c r="B83">
-        <v>301.37933349609381</v>
+        <v>301.37936401367188</v>
       </c>
       <c r="C83">
         <v>305.55999755859381</v>
@@ -13432,7 +13432,7 @@
         <v>45048</v>
       </c>
       <c r="B84">
-        <v>301.2314453125</v>
+        <v>301.23141479492188</v>
       </c>
       <c r="C84">
         <v>305.41000366210938</v>
@@ -13478,7 +13478,7 @@
         <v>45050</v>
       </c>
       <c r="B86">
-        <v>301.2314453125</v>
+        <v>301.23141479492188</v>
       </c>
       <c r="C86">
         <v>305.41000366210938</v>
@@ -13501,7 +13501,7 @@
         <v>45051</v>
       </c>
       <c r="B87">
-        <v>306.39974975585938</v>
+        <v>306.39968872070313</v>
       </c>
       <c r="C87">
         <v>310.64999389648438</v>
@@ -13524,7 +13524,7 @@
         <v>45054</v>
       </c>
       <c r="B88">
-        <v>304.42709350585938</v>
+        <v>304.42706298828119</v>
       </c>
       <c r="C88">
         <v>308.64999389648438</v>
@@ -13547,7 +13547,7 @@
         <v>45055</v>
       </c>
       <c r="B89">
-        <v>302.79965209960938</v>
+        <v>302.7996826171875</v>
       </c>
       <c r="C89">
         <v>307</v>
@@ -13593,7 +13593,7 @@
         <v>45057</v>
       </c>
       <c r="B91">
-        <v>305.86709594726563</v>
+        <v>305.8670654296875</v>
       </c>
       <c r="C91">
         <v>310.1099853515625</v>
@@ -13616,7 +13616,7 @@
         <v>45058</v>
       </c>
       <c r="B92">
-        <v>304.74270629882813</v>
+        <v>304.74273681640619</v>
       </c>
       <c r="C92">
         <v>308.97000122070313</v>
@@ -13639,7 +13639,7 @@
         <v>45061</v>
       </c>
       <c r="B93">
-        <v>305.2259521484375</v>
+        <v>305.22598266601563</v>
       </c>
       <c r="C93">
         <v>309.45999145507813</v>
@@ -13662,7 +13662,7 @@
         <v>45062</v>
       </c>
       <c r="B94">
-        <v>307.47482299804688</v>
+        <v>307.47479248046881</v>
       </c>
       <c r="C94">
         <v>311.739990234375</v>
@@ -13685,7 +13685,7 @@
         <v>45063</v>
       </c>
       <c r="B95">
-        <v>310.38092041015619</v>
+        <v>310.38095092773438</v>
       </c>
       <c r="C95">
         <v>314</v>
@@ -13708,7 +13708,7 @@
         <v>45064</v>
       </c>
       <c r="B96">
-        <v>314.84884643554688</v>
+        <v>314.84881591796881</v>
       </c>
       <c r="C96">
         <v>318.51998901367188</v>
@@ -13731,7 +13731,7 @@
         <v>45065</v>
       </c>
       <c r="B97">
-        <v>314.6708984375</v>
+        <v>314.67092895507813</v>
       </c>
       <c r="C97">
         <v>318.33999633789063</v>
@@ -13800,7 +13800,7 @@
         <v>45070</v>
       </c>
       <c r="B100">
-        <v>310.23263549804688</v>
+        <v>310.232666015625</v>
       </c>
       <c r="C100">
         <v>313.85000610351563</v>
@@ -13823,7 +13823,7 @@
         <v>45071</v>
       </c>
       <c r="B101">
-        <v>322.16357421875</v>
+        <v>322.16354370117188</v>
       </c>
       <c r="C101">
         <v>325.92001342773438</v>
@@ -13846,7 +13846,7 @@
         <v>45072</v>
       </c>
       <c r="B102">
-        <v>329.05319213867188</v>
+        <v>329.05322265625</v>
       </c>
       <c r="C102">
         <v>332.8900146484375</v>
@@ -13869,7 +13869,7 @@
         <v>45076</v>
       </c>
       <c r="B103">
-        <v>327.39260864257813</v>
+        <v>327.39254760742188</v>
       </c>
       <c r="C103">
         <v>331.20999145507813</v>
@@ -13892,7 +13892,7 @@
         <v>45077</v>
       </c>
       <c r="B104">
-        <v>324.60507202148438</v>
+        <v>324.6051025390625</v>
       </c>
       <c r="C104">
         <v>328.3900146484375</v>
@@ -13915,7 +13915,7 @@
         <v>45078</v>
       </c>
       <c r="B105">
-        <v>328.74679565429688</v>
+        <v>328.74673461914063</v>
       </c>
       <c r="C105">
         <v>332.57998657226563</v>
@@ -13961,7 +13961,7 @@
         <v>45082</v>
       </c>
       <c r="B107">
-        <v>332.06808471679688</v>
+        <v>332.06805419921881</v>
       </c>
       <c r="C107">
         <v>335.94000244140619</v>
@@ -14007,7 +14007,7 @@
         <v>45084</v>
       </c>
       <c r="B109">
-        <v>319.65280151367188</v>
+        <v>319.65277099609381</v>
       </c>
       <c r="C109">
         <v>323.3800048828125</v>
@@ -14030,7 +14030,7 @@
         <v>45085</v>
       </c>
       <c r="B110">
-        <v>321.51116943359381</v>
+        <v>321.51113891601563</v>
       </c>
       <c r="C110">
         <v>325.260009765625</v>
@@ -14053,7 +14053,7 @@
         <v>45086</v>
       </c>
       <c r="B111">
-        <v>323.02349853515619</v>
+        <v>323.02352905273438</v>
       </c>
       <c r="C111">
         <v>326.79000854492188</v>
@@ -14168,7 +14168,7 @@
         <v>45093</v>
       </c>
       <c r="B116">
-        <v>338.3843994140625</v>
+        <v>338.38436889648438</v>
       </c>
       <c r="C116">
         <v>342.32998657226563</v>
@@ -14191,7 +14191,7 @@
         <v>45097</v>
       </c>
       <c r="B117">
-        <v>334.15374755859381</v>
+        <v>334.15371704101563</v>
       </c>
       <c r="C117">
         <v>338.04998779296881</v>
@@ -14260,7 +14260,7 @@
         <v>45100</v>
       </c>
       <c r="B120">
-        <v>331.15869140625</v>
+        <v>331.15859985351563</v>
       </c>
       <c r="C120">
         <v>335.01998901367188</v>
@@ -14283,7 +14283,7 @@
         <v>45103</v>
       </c>
       <c r="B121">
-        <v>324.81265258789063</v>
+        <v>324.8126220703125</v>
       </c>
       <c r="C121">
         <v>328.60000610351563</v>
@@ -14306,7 +14306,7 @@
         <v>45104</v>
       </c>
       <c r="B122">
-        <v>330.7138671875</v>
+        <v>330.71380615234381</v>
       </c>
       <c r="C122">
         <v>334.57000732421881</v>
@@ -14329,7 +14329,7 @@
         <v>45105</v>
       </c>
       <c r="B123">
-        <v>331.9791259765625</v>
+        <v>331.97909545898438</v>
       </c>
       <c r="C123">
         <v>335.85000610351563</v>
@@ -14352,7 +14352,7 @@
         <v>45106</v>
       </c>
       <c r="B124">
-        <v>331.18832397460938</v>
+        <v>331.18829345703119</v>
       </c>
       <c r="C124">
         <v>335.04998779296881</v>
@@ -14421,7 +14421,7 @@
         <v>45112</v>
       </c>
       <c r="B127">
-        <v>334.25259399414063</v>
+        <v>334.2525634765625</v>
       </c>
       <c r="C127">
         <v>338.14999389648438</v>
@@ -14444,7 +14444,7 @@
         <v>45113</v>
       </c>
       <c r="B128">
-        <v>337.33657836914063</v>
+        <v>337.33660888671881</v>
       </c>
       <c r="C128">
         <v>341.26998901367188</v>
@@ -14467,7 +14467,7 @@
         <v>45114</v>
       </c>
       <c r="B129">
-        <v>333.33334350585938</v>
+        <v>333.33331298828119</v>
       </c>
       <c r="C129">
         <v>337.22000122070313</v>
@@ -14536,7 +14536,7 @@
         <v>45119</v>
       </c>
       <c r="B132">
-        <v>333.31356811523438</v>
+        <v>333.31350708007813</v>
       </c>
       <c r="C132">
         <v>337.20001220703119</v>
@@ -14559,7 +14559,7 @@
         <v>45120</v>
       </c>
       <c r="B133">
-        <v>338.71063232421881</v>
+        <v>338.71060180664063</v>
       </c>
       <c r="C133">
         <v>342.66000366210938</v>
@@ -14582,7 +14582,7 @@
         <v>45121</v>
       </c>
       <c r="B134">
-        <v>341.2608642578125</v>
+        <v>341.26089477539063</v>
       </c>
       <c r="C134">
         <v>345.239990234375</v>
@@ -14720,7 +14720,7 @@
         <v>45131</v>
       </c>
       <c r="B140">
-        <v>341.13238525390619</v>
+        <v>341.13232421875</v>
       </c>
       <c r="C140">
         <v>345.1099853515625</v>
@@ -14743,7 +14743,7 @@
         <v>45132</v>
       </c>
       <c r="B141">
-        <v>346.9346923828125</v>
+        <v>346.93472290039063</v>
       </c>
       <c r="C141">
         <v>350.98001098632813</v>
@@ -14766,7 +14766,7 @@
         <v>45133</v>
       </c>
       <c r="B142">
-        <v>333.87692260742188</v>
+        <v>333.876953125</v>
       </c>
       <c r="C142">
         <v>337.76998901367188</v>
@@ -14812,7 +14812,7 @@
         <v>45135</v>
       </c>
       <c r="B144">
-        <v>334.47000122070313</v>
+        <v>334.47003173828119</v>
       </c>
       <c r="C144">
         <v>338.3699951171875</v>
@@ -14835,7 +14835,7 @@
         <v>45138</v>
       </c>
       <c r="B145">
-        <v>332.04827880859381</v>
+        <v>332.04824829101563</v>
       </c>
       <c r="C145">
         <v>335.92001342773438</v>
@@ -14881,7 +14881,7 @@
         <v>45140</v>
       </c>
       <c r="B147">
-        <v>323.72528076171881</v>
+        <v>323.725341796875</v>
       </c>
       <c r="C147">
         <v>327.5</v>
@@ -14973,7 +14973,7 @@
         <v>45146</v>
       </c>
       <c r="B151">
-        <v>322.29202270507813</v>
+        <v>322.29205322265619</v>
       </c>
       <c r="C151">
         <v>326.04998779296881</v>
@@ -14996,7 +14996,7 @@
         <v>45147</v>
       </c>
       <c r="B152">
-        <v>318.51608276367188</v>
+        <v>318.51611328125</v>
       </c>
       <c r="C152">
         <v>322.23001098632813</v>
@@ -15019,7 +15019,7 @@
         <v>45148</v>
       </c>
       <c r="B153">
-        <v>319.20794677734381</v>
+        <v>319.20797729492188</v>
       </c>
       <c r="C153">
         <v>322.92999267578119</v>
@@ -15065,7 +15065,7 @@
         <v>45152</v>
       </c>
       <c r="B155">
-        <v>320.30520629882813</v>
+        <v>320.30523681640619</v>
       </c>
       <c r="C155">
         <v>324.04000854492188</v>
@@ -15111,7 +15111,7 @@
         <v>45154</v>
       </c>
       <c r="B157">
-        <v>317.377685546875</v>
+        <v>317.37771606445313</v>
       </c>
       <c r="C157">
         <v>320.39999389648438</v>
@@ -15134,7 +15134,7 @@
         <v>45155</v>
       </c>
       <c r="B158">
-        <v>313.89096069335938</v>
+        <v>313.89089965820313</v>
       </c>
       <c r="C158">
         <v>316.8800048828125</v>
@@ -15157,7 +15157,7 @@
         <v>45156</v>
       </c>
       <c r="B159">
-        <v>313.49468994140619</v>
+        <v>313.49465942382813</v>
       </c>
       <c r="C159">
         <v>316.48001098632813</v>
@@ -15203,7 +15203,7 @@
         <v>45160</v>
       </c>
       <c r="B161">
-        <v>319.41827392578119</v>
+        <v>319.41824340820313</v>
       </c>
       <c r="C161">
         <v>322.45999145507813</v>
@@ -15226,7 +15226,7 @@
         <v>45161</v>
       </c>
       <c r="B162">
-        <v>323.91546630859381</v>
+        <v>323.91543579101563</v>
       </c>
       <c r="C162">
         <v>327</v>
@@ -15249,7 +15249,7 @@
         <v>45162</v>
       </c>
       <c r="B163">
-        <v>316.9517822265625</v>
+        <v>316.95172119140619</v>
       </c>
       <c r="C163">
         <v>319.97000122070313</v>
@@ -15318,7 +15318,7 @@
         <v>45167</v>
       </c>
       <c r="B166">
-        <v>325.31216430664063</v>
+        <v>325.3121337890625</v>
       </c>
       <c r="C166">
         <v>328.41000366210938</v>
@@ -15387,7 +15387,7 @@
         <v>45170</v>
       </c>
       <c r="B169">
-        <v>325.55975341796881</v>
+        <v>325.559814453125</v>
       </c>
       <c r="C169">
         <v>328.66000366210938</v>
@@ -15433,7 +15433,7 @@
         <v>45175</v>
       </c>
       <c r="B171">
-        <v>329.739990234375</v>
+        <v>329.73995971679688</v>
       </c>
       <c r="C171">
         <v>332.8800048828125</v>
@@ -15479,7 +15479,7 @@
         <v>45177</v>
       </c>
       <c r="B173">
-        <v>331.11688232421881</v>
+        <v>331.11685180664063</v>
       </c>
       <c r="C173">
         <v>334.26998901367188</v>
@@ -15502,7 +15502,7 @@
         <v>45180</v>
       </c>
       <c r="B174">
-        <v>334.75222778320313</v>
+        <v>334.75228881835938</v>
       </c>
       <c r="C174">
         <v>337.94000244140619</v>
@@ -15548,7 +15548,7 @@
         <v>45182</v>
       </c>
       <c r="B176">
-        <v>332.8900146484375</v>
+        <v>332.88998413085938</v>
       </c>
       <c r="C176">
         <v>336.05999755859381</v>
@@ -15617,7 +15617,7 @@
         <v>45187</v>
       </c>
       <c r="B179">
-        <v>325.95599365234381</v>
+        <v>325.95602416992188</v>
       </c>
       <c r="C179">
         <v>329.05999755859381</v>
@@ -15640,7 +15640,7 @@
         <v>45188</v>
       </c>
       <c r="B180">
-        <v>325.54986572265619</v>
+        <v>325.54983520507813</v>
       </c>
       <c r="C180">
         <v>328.64999389648438</v>
@@ -15663,7 +15663,7 @@
         <v>45189</v>
       </c>
       <c r="B181">
-        <v>317.74423217773438</v>
+        <v>317.74417114257813</v>
       </c>
       <c r="C181">
         <v>320.76998901367188</v>
@@ -15755,7 +15755,7 @@
         <v>45195</v>
       </c>
       <c r="B185">
-        <v>309.19564819335938</v>
+        <v>309.19561767578119</v>
       </c>
       <c r="C185">
         <v>312.1400146484375</v>
@@ -15778,7 +15778,7 @@
         <v>45196</v>
       </c>
       <c r="B186">
-        <v>309.83944702148438</v>
+        <v>309.83950805664063</v>
       </c>
       <c r="C186">
         <v>312.79000854492188</v>
@@ -15824,7 +15824,7 @@
         <v>45198</v>
       </c>
       <c r="B188">
-        <v>312.77157592773438</v>
+        <v>312.77151489257813</v>
       </c>
       <c r="C188">
         <v>315.75</v>
@@ -15847,7 +15847,7 @@
         <v>45201</v>
       </c>
       <c r="B189">
-        <v>318.76449584960938</v>
+        <v>318.76443481445313</v>
       </c>
       <c r="C189">
         <v>321.79998779296881</v>
@@ -15870,7 +15870,7 @@
         <v>45202</v>
       </c>
       <c r="B190">
-        <v>310.43380737304688</v>
+        <v>310.433837890625</v>
       </c>
       <c r="C190">
         <v>313.3900146484375</v>
@@ -15939,7 +15939,7 @@
         <v>45205</v>
       </c>
       <c r="B193">
-        <v>324.17300415039063</v>
+        <v>324.1729736328125</v>
       </c>
       <c r="C193">
         <v>327.260009765625</v>
@@ -16031,7 +16031,7 @@
         <v>45211</v>
       </c>
       <c r="B197">
-        <v>328.03622436523438</v>
+        <v>328.03619384765619</v>
       </c>
       <c r="C197">
         <v>331.16000366210938</v>
@@ -16077,7 +16077,7 @@
         <v>45215</v>
       </c>
       <c r="B199">
-        <v>329.50225830078119</v>
+        <v>329.50222778320313</v>
       </c>
       <c r="C199">
         <v>332.6400146484375</v>
@@ -16123,7 +16123,7 @@
         <v>45217</v>
       </c>
       <c r="B201">
-        <v>326.99609375</v>
+        <v>326.99606323242188</v>
       </c>
       <c r="C201">
         <v>330.1099853515625</v>
@@ -16146,7 +16146,7 @@
         <v>45218</v>
       </c>
       <c r="B202">
-        <v>328.19467163085938</v>
+        <v>328.1947021484375</v>
       </c>
       <c r="C202">
         <v>331.32000732421881</v>
@@ -16169,7 +16169,7 @@
         <v>45219</v>
       </c>
       <c r="B203">
-        <v>323.58856201171881</v>
+        <v>323.58859252929688</v>
       </c>
       <c r="C203">
         <v>326.67001342773438</v>
@@ -16192,7 +16192,7 @@
         <v>45222</v>
       </c>
       <c r="B204">
-        <v>326.21356201171881</v>
+        <v>326.21359252929688</v>
       </c>
       <c r="C204">
         <v>329.32000732421881</v>
@@ -16215,7 +16215,7 @@
         <v>45223</v>
       </c>
       <c r="B205">
-        <v>327.41217041015619</v>
+        <v>327.41213989257813</v>
       </c>
       <c r="C205">
         <v>330.52999877929688</v>
@@ -16238,7 +16238,7 @@
         <v>45224</v>
       </c>
       <c r="B206">
-        <v>337.45651245117188</v>
+        <v>337.45648193359381</v>
       </c>
       <c r="C206">
         <v>340.67001342773438</v>
@@ -16307,7 +16307,7 @@
         <v>45229</v>
       </c>
       <c r="B209">
-        <v>334.128173828125</v>
+        <v>334.12820434570313</v>
       </c>
       <c r="C209">
         <v>337.30999755859381</v>
@@ -16376,7 +16376,7 @@
         <v>45232</v>
       </c>
       <c r="B212">
-        <v>345.03436279296881</v>
+        <v>345.03433227539063</v>
       </c>
       <c r="C212">
         <v>348.32000732421881</v>
@@ -16422,7 +16422,7 @@
         <v>45236</v>
       </c>
       <c r="B214">
-        <v>353.1668701171875</v>
+        <v>353.16690063476563</v>
       </c>
       <c r="C214">
         <v>356.52999877929688</v>
@@ -16468,7 +16468,7 @@
         <v>45238</v>
       </c>
       <c r="B216">
-        <v>359.77398681640619</v>
+        <v>359.77395629882813</v>
       </c>
       <c r="C216">
         <v>363.20001220703119</v>
@@ -16491,7 +16491,7 @@
         <v>45239</v>
       </c>
       <c r="B217">
-        <v>357.28765869140619</v>
+        <v>357.28762817382813</v>
       </c>
       <c r="C217">
         <v>360.69000244140619</v>
@@ -16514,7 +16514,7 @@
         <v>45240</v>
       </c>
       <c r="B218">
-        <v>366.18295288085938</v>
+        <v>366.18292236328119</v>
       </c>
       <c r="C218">
         <v>369.67001342773438</v>
@@ -16560,7 +16560,7 @@
         <v>45244</v>
       </c>
       <c r="B220">
-        <v>366.77728271484381</v>
+        <v>366.77725219726563</v>
       </c>
       <c r="C220">
         <v>370.26998901367188</v>
@@ -16583,7 +16583,7 @@
         <v>45245</v>
       </c>
       <c r="B221">
-        <v>366.92617797851563</v>
+        <v>366.9261474609375</v>
       </c>
       <c r="C221">
         <v>369.67001342773438</v>
@@ -16606,7 +16606,7 @@
         <v>45246</v>
       </c>
       <c r="B222">
-        <v>373.37796020507813</v>
+        <v>373.3779296875</v>
       </c>
       <c r="C222">
         <v>376.17001342773438</v>
@@ -16629,7 +16629,7 @@
         <v>45247</v>
       </c>
       <c r="B223">
-        <v>367.10482788085938</v>
+        <v>367.1048583984375</v>
       </c>
       <c r="C223">
         <v>369.85000610351563</v>
@@ -16698,7 +16698,7 @@
         <v>45252</v>
       </c>
       <c r="B226">
-        <v>375.04544067382813</v>
+        <v>375.04547119140619</v>
       </c>
       <c r="C226">
         <v>377.85000610351563</v>
@@ -16744,7 +16744,7 @@
         <v>45257</v>
       </c>
       <c r="B228">
-        <v>375.7998046875</v>
+        <v>375.79977416992188</v>
       </c>
       <c r="C228">
         <v>378.6099853515625</v>
@@ -16767,7 +16767,7 @@
         <v>45258</v>
       </c>
       <c r="B229">
-        <v>379.8594970703125</v>
+        <v>379.85946655273438</v>
       </c>
       <c r="C229">
         <v>382.70001220703119</v>
@@ -16790,7 +16790,7 @@
         <v>45259</v>
       </c>
       <c r="B230">
-        <v>376.03802490234381</v>
+        <v>376.03805541992188</v>
       </c>
       <c r="C230">
         <v>378.85000610351563</v>
@@ -16836,7 +16836,7 @@
         <v>45261</v>
       </c>
       <c r="B232">
-        <v>371.73025512695313</v>
+        <v>371.730224609375</v>
       </c>
       <c r="C232">
         <v>374.510009765625</v>
@@ -16882,7 +16882,7 @@
         <v>45265</v>
       </c>
       <c r="B234">
-        <v>369.75497436523438</v>
+        <v>369.7550048828125</v>
       </c>
       <c r="C234">
         <v>372.51998901367188</v>
@@ -16905,7 +16905,7 @@
         <v>45266</v>
       </c>
       <c r="B235">
-        <v>366.06259155273438</v>
+        <v>366.06265258789063</v>
       </c>
       <c r="C235">
         <v>368.79998779296881</v>
@@ -16951,7 +16951,7 @@
         <v>45268</v>
       </c>
       <c r="B237">
-        <v>371.45236206054688</v>
+        <v>371.45230102539063</v>
       </c>
       <c r="C237">
         <v>374.23001098632813</v>
@@ -16997,7 +16997,7 @@
         <v>45272</v>
       </c>
       <c r="B239">
-        <v>371.60122680664063</v>
+        <v>371.6011962890625</v>
       </c>
       <c r="C239">
         <v>374.3800048828125</v>
@@ -17020,7 +17020,7 @@
         <v>45273</v>
       </c>
       <c r="B240">
-        <v>371.59124755859381</v>
+        <v>371.59127807617188</v>
       </c>
       <c r="C240">
         <v>374.3699951171875</v>
@@ -17043,7 +17043,7 @@
         <v>45274</v>
       </c>
       <c r="B241">
-        <v>363.21389770507813</v>
+        <v>363.21392822265619</v>
       </c>
       <c r="C241">
         <v>365.92999267578119</v>
@@ -17066,7 +17066,7 @@
         <v>45275</v>
       </c>
       <c r="B242">
-        <v>367.97833251953119</v>
+        <v>367.97830200195313</v>
       </c>
       <c r="C242">
         <v>370.73001098632813</v>
@@ -17319,7 +17319,7 @@
         <v>45294</v>
       </c>
       <c r="B253">
-        <v>367.8492431640625</v>
+        <v>367.84927368164063</v>
       </c>
       <c r="C253">
         <v>370.60000610351563</v>
@@ -17365,7 +17365,7 @@
         <v>45296</v>
       </c>
       <c r="B255">
-        <v>365.02044677734381</v>
+        <v>365.0203857421875</v>
       </c>
       <c r="C255">
         <v>367.75</v>
@@ -17411,7 +17411,7 @@
         <v>45300</v>
       </c>
       <c r="B257">
-        <v>373.00076293945313</v>
+        <v>373.000732421875</v>
       </c>
       <c r="C257">
         <v>375.79000854492188</v>
@@ -17434,7 +17434,7 @@
         <v>45301</v>
       </c>
       <c r="B258">
-        <v>379.92892456054688</v>
+        <v>379.92889404296881</v>
       </c>
       <c r="C258">
         <v>382.76998901367188</v>
@@ -17457,7 +17457,7 @@
         <v>45302</v>
       </c>
       <c r="B259">
-        <v>381.77511596679688</v>
+        <v>381.775146484375</v>
       </c>
       <c r="C259">
         <v>384.6300048828125</v>
@@ -17480,7 +17480,7 @@
         <v>45303</v>
       </c>
       <c r="B260">
-        <v>385.58663940429688</v>
+        <v>385.58660888671881</v>
       </c>
       <c r="C260">
         <v>388.47000122070313</v>
@@ -17572,7 +17572,7 @@
         <v>45310</v>
       </c>
       <c r="B264">
-        <v>395.71096801757813</v>
+        <v>395.71090698242188</v>
       </c>
       <c r="C264">
         <v>398.67001342773438</v>
@@ -17595,7 +17595,7 @@
         <v>45313</v>
       </c>
       <c r="B265">
-        <v>393.56692504882813</v>
+        <v>393.56698608398438</v>
       </c>
       <c r="C265">
         <v>396.510009765625</v>
@@ -17641,7 +17641,7 @@
         <v>45315</v>
       </c>
       <c r="B267">
-        <v>399.572021484375</v>
+        <v>399.57205200195313</v>
       </c>
       <c r="C267">
         <v>402.55999755859381</v>
@@ -17664,7 +17664,7 @@
         <v>45316</v>
       </c>
       <c r="B268">
-        <v>401.86492919921881</v>
+        <v>401.86489868164063</v>
       </c>
       <c r="C268">
         <v>404.8699951171875</v>
@@ -17687,7 +17687,7 @@
         <v>45317</v>
       </c>
       <c r="B269">
-        <v>400.931884765625</v>
+        <v>400.93185424804688</v>
       </c>
       <c r="C269">
         <v>403.92999267578119</v>
@@ -17710,7 +17710,7 @@
         <v>45320</v>
       </c>
       <c r="B270">
-        <v>406.67889404296881</v>
+        <v>406.67886352539063</v>
       </c>
       <c r="C270">
         <v>409.72000122070313</v>
@@ -17756,7 +17756,7 @@
         <v>45322</v>
       </c>
       <c r="B272">
-        <v>394.6290283203125</v>
+        <v>394.62899780273438</v>
       </c>
       <c r="C272">
         <v>397.57998657226563</v>
@@ -17779,7 +17779,7 @@
         <v>45323</v>
       </c>
       <c r="B273">
-        <v>400.78302001953119</v>
+        <v>400.78298950195313</v>
       </c>
       <c r="C273">
         <v>403.77999877929688</v>
@@ -17802,7 +17802,7 @@
         <v>45324</v>
       </c>
       <c r="B274">
-        <v>408.16778564453119</v>
+        <v>408.16775512695313</v>
       </c>
       <c r="C274">
         <v>411.22000122070313</v>
@@ -17825,7 +17825,7 @@
         <v>45327</v>
       </c>
       <c r="B275">
-        <v>402.63912963867188</v>
+        <v>402.63909912109381</v>
       </c>
       <c r="C275">
         <v>405.64999389648438</v>
@@ -17848,7 +17848,7 @@
         <v>45328</v>
       </c>
       <c r="B276">
-        <v>402.48028564453119</v>
+        <v>402.48025512695313</v>
       </c>
       <c r="C276">
         <v>405.489990234375</v>
@@ -17871,7 +17871,7 @@
         <v>45329</v>
       </c>
       <c r="B277">
-        <v>410.97671508789063</v>
+        <v>410.97677612304688</v>
       </c>
       <c r="C277">
         <v>414.04998779296881</v>
@@ -17894,7 +17894,7 @@
         <v>45330</v>
       </c>
       <c r="B278">
-        <v>411.03631591796881</v>
+        <v>411.03628540039063</v>
       </c>
       <c r="C278">
         <v>414.1099853515625</v>
@@ -18078,7 +18078,7 @@
         <v>45343</v>
       </c>
       <c r="B286">
-        <v>399.93307495117188</v>
+        <v>399.93304443359381</v>
       </c>
       <c r="C286">
         <v>402.17999267578119</v>
@@ -18101,7 +18101,7 @@
         <v>45344</v>
       </c>
       <c r="B287">
-        <v>409.35018920898438</v>
+        <v>409.35015869140619</v>
       </c>
       <c r="C287">
         <v>411.64999389648438</v>
@@ -18124,7 +18124,7 @@
         <v>45345</v>
       </c>
       <c r="B288">
-        <v>408.04751586914063</v>
+        <v>408.0474853515625</v>
       </c>
       <c r="C288">
         <v>410.33999633789063</v>
@@ -18147,7 +18147,7 @@
         <v>45348</v>
       </c>
       <c r="B289">
-        <v>405.26312255859381</v>
+        <v>405.26315307617188</v>
       </c>
       <c r="C289">
         <v>407.54000854492188</v>
@@ -18170,7 +18170,7 @@
         <v>45349</v>
       </c>
       <c r="B290">
-        <v>405.2034912109375</v>
+        <v>405.20346069335938</v>
       </c>
       <c r="C290">
         <v>407.48001098632813</v>
@@ -18193,7 +18193,7 @@
         <v>45350</v>
       </c>
       <c r="B291">
-        <v>405.442138671875</v>
+        <v>405.44210815429688</v>
       </c>
       <c r="C291">
         <v>407.72000122070313</v>
@@ -18216,7 +18216,7 @@
         <v>45351</v>
       </c>
       <c r="B292">
-        <v>411.3291015625</v>
+        <v>411.32907104492188</v>
       </c>
       <c r="C292">
         <v>413.6400146484375</v>
@@ -18285,7 +18285,7 @@
         <v>45356</v>
       </c>
       <c r="B295">
-        <v>400.40045166015619</v>
+        <v>400.40042114257813</v>
       </c>
       <c r="C295">
         <v>402.64999389648438</v>
@@ -18308,7 +18308,7 @@
         <v>45357</v>
       </c>
       <c r="B296">
-        <v>399.84356689453119</v>
+        <v>399.84353637695313</v>
       </c>
       <c r="C296">
         <v>402.08999633789063</v>
@@ -18331,7 +18331,7 @@
         <v>45358</v>
       </c>
       <c r="B297">
-        <v>406.85418701171881</v>
+        <v>406.85421752929688</v>
       </c>
       <c r="C297">
         <v>409.1400146484375</v>
@@ -18377,7 +18377,7 @@
         <v>45362</v>
       </c>
       <c r="B299">
-        <v>402.260009765625</v>
+        <v>402.25997924804688</v>
       </c>
       <c r="C299">
         <v>404.51998901367188</v>
@@ -18630,7 +18630,7 @@
         <v>45377</v>
       </c>
       <c r="B310">
-        <v>419.29428100585938</v>
+        <v>419.29425048828119</v>
       </c>
       <c r="C310">
         <v>421.64999389648438</v>
@@ -18653,7 +18653,7 @@
         <v>45378</v>
       </c>
       <c r="B311">
-        <v>419.07553100585938</v>
+        <v>419.07550048828119</v>
       </c>
       <c r="C311">
         <v>421.42999267578119</v>
@@ -18699,7 +18699,7 @@
         <v>45383</v>
       </c>
       <c r="B313">
-        <v>422.19796752929688</v>
+        <v>422.197998046875</v>
       </c>
       <c r="C313">
         <v>424.57000732421881</v>
@@ -18837,7 +18837,7 @@
         <v>45391</v>
       </c>
       <c r="B319">
-        <v>423.8984375</v>
+        <v>423.89840698242188</v>
       </c>
       <c r="C319">
         <v>426.27999877929688</v>
@@ -18860,7 +18860,7 @@
         <v>45392</v>
       </c>
       <c r="B320">
-        <v>420.89532470703119</v>
+        <v>420.89529418945313</v>
       </c>
       <c r="C320">
         <v>423.260009765625</v>
@@ -18929,7 +18929,7 @@
         <v>45397</v>
       </c>
       <c r="B323">
-        <v>411.3291015625</v>
+        <v>411.32907104492188</v>
       </c>
       <c r="C323">
         <v>413.6400146484375</v>
@@ -18952,7 +18952,7 @@
         <v>45398</v>
       </c>
       <c r="B324">
-        <v>412.26376342773438</v>
+        <v>412.2637939453125</v>
       </c>
       <c r="C324">
         <v>414.57998657226563</v>
@@ -18975,7 +18975,7 @@
         <v>45399</v>
       </c>
       <c r="B325">
-        <v>409.5390625</v>
+        <v>409.53909301757813</v>
       </c>
       <c r="C325">
         <v>411.83999633789063</v>
@@ -19044,7 +19044,7 @@
         <v>45404</v>
       </c>
       <c r="B328">
-        <v>398.71990966796881</v>
+        <v>398.71987915039063</v>
       </c>
       <c r="C328">
         <v>400.95999145507813</v>
@@ -19113,7 +19113,7 @@
         <v>45407</v>
       </c>
       <c r="B331">
-        <v>396.81063842773438</v>
+        <v>396.81060791015619</v>
       </c>
       <c r="C331">
         <v>399.04000854492188</v>
@@ -19205,7 +19205,7 @@
         <v>45413</v>
       </c>
       <c r="B335">
-        <v>392.73355102539063</v>
+        <v>392.7335205078125</v>
       </c>
       <c r="C335">
         <v>394.94000244140619</v>
@@ -19274,7 +19274,7 @@
         <v>45418</v>
       </c>
       <c r="B338">
-        <v>411.22958374023438</v>
+        <v>411.2296142578125</v>
       </c>
       <c r="C338">
         <v>413.54000854492188</v>
@@ -19366,7 +19366,7 @@
         <v>45422</v>
       </c>
       <c r="B342">
-        <v>412.42291259765619</v>
+        <v>412.42288208007813</v>
       </c>
       <c r="C342">
         <v>414.739990234375</v>
@@ -19435,7 +19435,7 @@
         <v>45427</v>
       </c>
       <c r="B345">
-        <v>421.47515869140619</v>
+        <v>421.47512817382813</v>
       </c>
       <c r="C345">
         <v>423.07998657226563</v>
@@ -19458,7 +19458,7 @@
         <v>45428</v>
       </c>
       <c r="B346">
-        <v>419.39306640625</v>
+        <v>419.39309692382813</v>
       </c>
       <c r="C346">
         <v>420.989990234375</v>
@@ -19527,7 +19527,7 @@
         <v>45433</v>
       </c>
       <c r="B349">
-        <v>427.41253662109381</v>
+        <v>427.41256713867188</v>
       </c>
       <c r="C349">
         <v>429.04000854492188</v>
@@ -19619,7 +19619,7 @@
         <v>45440</v>
       </c>
       <c r="B353">
-        <v>428.68771362304688</v>
+        <v>428.68768310546881</v>
       </c>
       <c r="C353">
         <v>430.32000732421881</v>
@@ -20033,7 +20033,7 @@
         <v>45467</v>
       </c>
       <c r="B371">
-        <v>445.97189331054688</v>
+        <v>445.971923828125</v>
       </c>
       <c r="C371">
         <v>447.67001342773438</v>
@@ -20102,7 +20102,7 @@
         <v>45470</v>
       </c>
       <c r="B374">
-        <v>451.13226318359381</v>
+        <v>451.13223266601563</v>
       </c>
       <c r="C374">
         <v>452.85000610351563</v>
@@ -20309,7 +20309,7 @@
         <v>45484</v>
       </c>
       <c r="B383">
-        <v>452.97525024414063</v>
+        <v>452.9752197265625</v>
       </c>
       <c r="C383">
         <v>454.70001220703119</v>
@@ -20355,7 +20355,7 @@
         <v>45488</v>
       </c>
       <c r="B385">
-        <v>452.23800659179688</v>
+        <v>452.238037109375</v>
       </c>
       <c r="C385">
         <v>453.95999145507813</v>
@@ -20378,7 +20378,7 @@
         <v>45489</v>
       </c>
       <c r="B386">
-        <v>447.81484985351563</v>
+        <v>447.81488037109381</v>
       </c>
       <c r="C386">
         <v>449.51998901367188</v>
@@ -20470,7 +20470,7 @@
         <v>45495</v>
       </c>
       <c r="B390">
-        <v>441.25985717773438</v>
+        <v>441.25982666015619</v>
       </c>
       <c r="C390">
         <v>442.94000244140619</v>
@@ -20516,7 +20516,7 @@
         <v>45497</v>
       </c>
       <c r="B392">
-        <v>427.27310180664063</v>
+        <v>427.2730712890625</v>
       </c>
       <c r="C392">
         <v>428.89999389648438</v>
@@ -20631,7 +20631,7 @@
         <v>45504</v>
       </c>
       <c r="B397">
-        <v>416.76309204101563</v>
+        <v>416.76312255859381</v>
       </c>
       <c r="C397">
         <v>418.35000610351563</v>
@@ -20654,7 +20654,7 @@
         <v>45505</v>
       </c>
       <c r="B398">
-        <v>415.52777099609381</v>
+        <v>415.52780151367188</v>
       </c>
       <c r="C398">
         <v>417.1099853515625</v>
@@ -20677,7 +20677,7 @@
         <v>45506</v>
       </c>
       <c r="B399">
-        <v>406.94052124023438</v>
+        <v>406.94049072265619</v>
       </c>
       <c r="C399">
         <v>408.489990234375</v>
@@ -20746,7 +20746,7 @@
         <v>45511</v>
       </c>
       <c r="B402">
-        <v>396.91864013671881</v>
+        <v>396.91867065429688</v>
       </c>
       <c r="C402">
         <v>398.42999267578119</v>
@@ -22642,7 +22642,7 @@
         <v>44929</v>
       </c>
       <c r="B2">
-        <v>144.2268981933594</v>
+        <v>144.22686767578119</v>
       </c>
       <c r="C2">
         <v>151.57000732421881</v>
@@ -22665,7 +22665,7 @@
         <v>44930</v>
       </c>
       <c r="B3">
-        <v>144.8548889160156</v>
+        <v>144.85487365722659</v>
       </c>
       <c r="C3">
         <v>152.22999572753909</v>
@@ -22688,7 +22688,7 @@
         <v>44931</v>
       </c>
       <c r="B4">
-        <v>143.05644226074219</v>
+        <v>143.05645751953119</v>
       </c>
       <c r="C4">
         <v>150.3399963378906</v>
@@ -22711,7 +22711,7 @@
         <v>44932</v>
       </c>
       <c r="B5">
-        <v>146.46299743652341</v>
+        <v>146.4630126953125</v>
       </c>
       <c r="C5">
         <v>153.91999816894531</v>
@@ -22734,7 +22734,7 @@
         <v>44935</v>
       </c>
       <c r="B6">
-        <v>144.67408752441409</v>
+        <v>144.6741027832031</v>
       </c>
       <c r="C6">
         <v>152.03999328613281</v>
@@ -22826,7 +22826,7 @@
         <v>44939</v>
       </c>
       <c r="B10">
-        <v>143.57029724121091</v>
+        <v>143.5703125</v>
       </c>
       <c r="C10">
         <v>150.8800048828125</v>
@@ -22849,7 +22849,7 @@
         <v>44943</v>
       </c>
       <c r="B11">
-        <v>143.15162658691409</v>
+        <v>143.15159606933591</v>
       </c>
       <c r="C11">
         <v>150.44000244140619</v>
@@ -22872,7 +22872,7 @@
         <v>44944</v>
       </c>
       <c r="B12">
-        <v>139.31683349609381</v>
+        <v>139.31684875488281</v>
       </c>
       <c r="C12">
         <v>146.4100036621094</v>
@@ -22941,7 +22941,7 @@
         <v>44949</v>
       </c>
       <c r="B15">
-        <v>135.05873107910159</v>
+        <v>135.0587463378906</v>
       </c>
       <c r="C15">
         <v>141.05000305175781</v>
@@ -22964,7 +22964,7 @@
         <v>44950</v>
       </c>
       <c r="B16">
-        <v>135.79603576660159</v>
+        <v>135.7960205078125</v>
       </c>
       <c r="C16">
         <v>141.82000732421881</v>
@@ -22987,7 +22987,7 @@
         <v>44951</v>
       </c>
       <c r="B17">
-        <v>135.70030212402341</v>
+        <v>135.7002868652344</v>
       </c>
       <c r="C17">
         <v>141.7200012207031</v>
@@ -23010,7 +23010,7 @@
         <v>44952</v>
       </c>
       <c r="B18">
-        <v>135.15449523925781</v>
+        <v>135.15447998046881</v>
       </c>
       <c r="C18">
         <v>141.1499938964844</v>
@@ -23033,7 +23033,7 @@
         <v>44953</v>
       </c>
       <c r="B19">
-        <v>134.59913635253909</v>
+        <v>134.59912109375</v>
       </c>
       <c r="C19">
         <v>140.57000732421881</v>
@@ -23056,7 +23056,7 @@
         <v>44956</v>
       </c>
       <c r="B20">
-        <v>135.02043151855469</v>
+        <v>135.02044677734381</v>
       </c>
       <c r="C20">
         <v>141.00999450683591</v>
@@ -23079,7 +23079,7 @@
         <v>44957</v>
       </c>
       <c r="B21">
-        <v>136.33221435546881</v>
+        <v>136.33226013183591</v>
       </c>
       <c r="C21">
         <v>142.3800048828125</v>
@@ -23102,7 +23102,7 @@
         <v>44958</v>
       </c>
       <c r="B22">
-        <v>137.10783386230469</v>
+        <v>137.10786437988281</v>
       </c>
       <c r="C22">
         <v>143.19000244140619</v>
@@ -23125,7 +23125,7 @@
         <v>44959</v>
       </c>
       <c r="B23">
-        <v>136.13116455078119</v>
+        <v>136.13117980957031</v>
       </c>
       <c r="C23">
         <v>142.16999816894531</v>
@@ -23171,7 +23171,7 @@
         <v>44963</v>
       </c>
       <c r="B25">
-        <v>135.39385986328119</v>
+        <v>135.39387512207031</v>
       </c>
       <c r="C25">
         <v>141.3999938964844</v>
@@ -23194,7 +23194,7 @@
         <v>44964</v>
       </c>
       <c r="B26">
-        <v>134.07252502441409</v>
+        <v>134.07249450683591</v>
       </c>
       <c r="C26">
         <v>140.02000427246091</v>
@@ -23217,7 +23217,7 @@
         <v>44965</v>
       </c>
       <c r="B27">
-        <v>132.68408203125</v>
+        <v>132.68409729003909</v>
       </c>
       <c r="C27">
         <v>138.57000732421881</v>
@@ -23240,7 +23240,7 @@
         <v>44966</v>
       </c>
       <c r="B28">
-        <v>131.22865295410159</v>
+        <v>131.2286376953125</v>
       </c>
       <c r="C28">
         <v>137.05000305175781</v>
@@ -23263,7 +23263,7 @@
         <v>44967</v>
       </c>
       <c r="B29">
-        <v>132.3872375488281</v>
+        <v>132.38726806640619</v>
       </c>
       <c r="C29">
         <v>138.25999450683591</v>
@@ -23286,7 +23286,7 @@
         <v>44970</v>
       </c>
       <c r="B30">
-        <v>134.12037658691409</v>
+        <v>134.12034606933591</v>
       </c>
       <c r="C30">
         <v>140.07000732421881</v>
@@ -23332,7 +23332,7 @@
         <v>44972</v>
       </c>
       <c r="B32">
-        <v>133.05751037597659</v>
+        <v>133.0575256347656</v>
       </c>
       <c r="C32">
         <v>138.96000671386719</v>
@@ -23378,7 +23378,7 @@
         <v>44974</v>
       </c>
       <c r="B34">
-        <v>134.06292724609381</v>
+        <v>134.06291198730469</v>
       </c>
       <c r="C34">
         <v>140.00999450683591</v>
@@ -23401,7 +23401,7 @@
         <v>44978</v>
       </c>
       <c r="B35">
-        <v>133.96717834472659</v>
+        <v>133.9671630859375</v>
       </c>
       <c r="C35">
         <v>139.9100036621094</v>
@@ -23424,7 +23424,7 @@
         <v>44979</v>
       </c>
       <c r="B36">
-        <v>134.53208923339841</v>
+        <v>134.53211975097659</v>
       </c>
       <c r="C36">
         <v>140.5</v>
@@ -23447,7 +23447,7 @@
         <v>44980</v>
       </c>
       <c r="B37">
-        <v>134.1012268066406</v>
+        <v>134.10121154785159</v>
       </c>
       <c r="C37">
         <v>140.05000305175781</v>
@@ -23470,7 +23470,7 @@
         <v>44981</v>
       </c>
       <c r="B38">
-        <v>133.3447570800781</v>
+        <v>133.34477233886719</v>
       </c>
       <c r="C38">
         <v>139.25999450683591</v>
@@ -23493,7 +23493,7 @@
         <v>44984</v>
       </c>
       <c r="B39">
-        <v>133.2298889160156</v>
+        <v>133.22987365722659</v>
       </c>
       <c r="C39">
         <v>139.13999938964841</v>
@@ -23539,7 +23539,7 @@
         <v>44986</v>
       </c>
       <c r="B41">
-        <v>131.812744140625</v>
+        <v>131.81272888183591</v>
       </c>
       <c r="C41">
         <v>137.6600036621094</v>
@@ -23562,7 +23562,7 @@
         <v>44987</v>
       </c>
       <c r="B42">
-        <v>133.9862976074219</v>
+        <v>133.98631286621091</v>
       </c>
       <c r="C42">
         <v>139.92999267578119</v>
@@ -23585,7 +23585,7 @@
         <v>44988</v>
       </c>
       <c r="B43">
-        <v>134.9629821777344</v>
+        <v>134.96296691894531</v>
       </c>
       <c r="C43">
         <v>140.94999694824219</v>
@@ -23608,7 +23608,7 @@
         <v>44991</v>
       </c>
       <c r="B44">
-        <v>134.3884582519531</v>
+        <v>134.38847351074219</v>
       </c>
       <c r="C44">
         <v>140.3500061035156</v>
@@ -23677,7 +23677,7 @@
         <v>44994</v>
       </c>
       <c r="B47">
-        <v>130.76905822753909</v>
+        <v>130.76904296875</v>
       </c>
       <c r="C47">
         <v>136.57000732421881</v>
@@ -23700,7 +23700,7 @@
         <v>44995</v>
       </c>
       <c r="B48">
-        <v>131.36268615722659</v>
+        <v>131.3627014160156</v>
       </c>
       <c r="C48">
         <v>137.19000244140619</v>
@@ -23723,7 +23723,7 @@
         <v>44998</v>
       </c>
       <c r="B49">
-        <v>132.2723388671875</v>
+        <v>132.2723693847656</v>
       </c>
       <c r="C49">
         <v>138.13999938964841</v>
@@ -23746,7 +23746,7 @@
         <v>44999</v>
       </c>
       <c r="B50">
-        <v>133.9096984863281</v>
+        <v>133.90974426269531</v>
       </c>
       <c r="C50">
         <v>139.8500061035156</v>
@@ -23792,7 +23792,7 @@
         <v>45001</v>
       </c>
       <c r="B52">
-        <v>136.820556640625</v>
+        <v>136.82057189941409</v>
       </c>
       <c r="C52">
         <v>142.88999938964841</v>
@@ -23815,7 +23815,7 @@
         <v>45002</v>
       </c>
       <c r="B53">
-        <v>136.8588562011719</v>
+        <v>136.85887145996091</v>
       </c>
       <c r="C53">
         <v>142.92999267578119</v>
@@ -23838,7 +23838,7 @@
         <v>45005</v>
       </c>
       <c r="B54">
-        <v>138.9654235839844</v>
+        <v>138.96543884277341</v>
       </c>
       <c r="C54">
         <v>145.1300048828125</v>
@@ -23861,7 +23861,7 @@
         <v>45006</v>
       </c>
       <c r="B55">
-        <v>137.96003723144531</v>
+        <v>137.9600524902344</v>
       </c>
       <c r="C55">
         <v>144.08000183105469</v>
@@ -23907,7 +23907,7 @@
         <v>45008</v>
       </c>
       <c r="B57">
-        <v>137.682373046875</v>
+        <v>137.68235778808591</v>
       </c>
       <c r="C57">
         <v>143.78999328613281</v>
@@ -23930,7 +23930,7 @@
         <v>45009</v>
       </c>
       <c r="B58">
-        <v>140.48789978027341</v>
+        <v>140.4879150390625</v>
       </c>
       <c r="C58">
         <v>146.7200012207031</v>
@@ -23953,7 +23953,7 @@
         <v>45012</v>
       </c>
       <c r="B59">
-        <v>139.7506103515625</v>
+        <v>139.75059509277341</v>
       </c>
       <c r="C59">
         <v>145.94999694824219</v>
@@ -23976,7 +23976,7 @@
         <v>45013</v>
       </c>
       <c r="B60">
-        <v>140.14320373535159</v>
+        <v>140.1431884765625</v>
       </c>
       <c r="C60">
         <v>146.36000061035159</v>
@@ -24114,7 +24114,7 @@
         <v>45021</v>
       </c>
       <c r="B66">
-        <v>144.83506774902341</v>
+        <v>144.8350524902344</v>
       </c>
       <c r="C66">
         <v>151.25999450683591</v>
@@ -24137,7 +24137,7 @@
         <v>45022</v>
       </c>
       <c r="B67">
-        <v>145.7542724609375</v>
+        <v>145.7543029785156</v>
       </c>
       <c r="C67">
         <v>152.2200012207031</v>
@@ -24160,7 +24160,7 @@
         <v>45026</v>
       </c>
       <c r="B68">
-        <v>144.5478210449219</v>
+        <v>144.54779052734381</v>
       </c>
       <c r="C68">
         <v>150.96000671386719</v>
@@ -24206,7 +24206,7 @@
         <v>45028</v>
       </c>
       <c r="B70">
-        <v>144.65312194824219</v>
+        <v>144.65313720703119</v>
       </c>
       <c r="C70">
         <v>151.07000732421881</v>
@@ -24229,7 +24229,7 @@
         <v>45029</v>
       </c>
       <c r="B71">
-        <v>145.32342529296881</v>
+        <v>145.32341003417969</v>
       </c>
       <c r="C71">
         <v>151.77000427246091</v>
@@ -24252,7 +24252,7 @@
         <v>45030</v>
       </c>
       <c r="B72">
-        <v>144.58610534667969</v>
+        <v>144.5860900878906</v>
       </c>
       <c r="C72">
         <v>151</v>
@@ -24275,7 +24275,7 @@
         <v>45033</v>
       </c>
       <c r="B73">
-        <v>144.63395690917969</v>
+        <v>144.63397216796881</v>
       </c>
       <c r="C73">
         <v>151.05000305175781</v>
@@ -24298,7 +24298,7 @@
         <v>45034</v>
       </c>
       <c r="B74">
-        <v>144.7872009277344</v>
+        <v>144.78718566894531</v>
       </c>
       <c r="C74">
         <v>151.21000671386719</v>
@@ -24321,7 +24321,7 @@
         <v>45035</v>
       </c>
       <c r="B75">
-        <v>144.81590270996091</v>
+        <v>144.81591796875</v>
       </c>
       <c r="C75">
         <v>151.24000549316409</v>
@@ -24344,7 +24344,7 @@
         <v>45036</v>
       </c>
       <c r="B76">
-        <v>145.34681701660159</v>
+        <v>145.3468322753906</v>
       </c>
       <c r="C76">
         <v>150.8500061035156</v>
@@ -24390,7 +24390,7 @@
         <v>45040</v>
       </c>
       <c r="B78">
-        <v>150.64617919921881</v>
+        <v>150.64616394042969</v>
       </c>
       <c r="C78">
         <v>156.3500061035156</v>
@@ -24413,7 +24413,7 @@
         <v>45041</v>
       </c>
       <c r="B79">
-        <v>150.6846923828125</v>
+        <v>150.68470764160159</v>
       </c>
       <c r="C79">
         <v>156.38999938964841</v>
@@ -24459,7 +24459,7 @@
         <v>45043</v>
       </c>
       <c r="B81">
-        <v>150.76179504394531</v>
+        <v>150.76177978515619</v>
       </c>
       <c r="C81">
         <v>156.4700012207031</v>
@@ -24482,7 +24482,7 @@
         <v>45044</v>
       </c>
       <c r="B82">
-        <v>150.67506408691409</v>
+        <v>150.6750793457031</v>
       </c>
       <c r="C82">
         <v>156.3800048828125</v>
@@ -24505,7 +24505,7 @@
         <v>45047</v>
       </c>
       <c r="B83">
-        <v>150.85813903808591</v>
+        <v>150.858154296875</v>
       </c>
       <c r="C83">
         <v>156.57000732421881</v>
@@ -24551,7 +24551,7 @@
         <v>45049</v>
       </c>
       <c r="B85">
-        <v>150.5305480957031</v>
+        <v>150.530517578125</v>
       </c>
       <c r="C85">
         <v>156.22999572753909</v>
@@ -24620,7 +24620,7 @@
         <v>45054</v>
       </c>
       <c r="B88">
-        <v>149.63447570800781</v>
+        <v>149.63446044921881</v>
       </c>
       <c r="C88">
         <v>155.30000305175781</v>
@@ -24643,7 +24643,7 @@
         <v>45055</v>
       </c>
       <c r="B89">
-        <v>148.10249328613281</v>
+        <v>148.10246276855469</v>
       </c>
       <c r="C89">
         <v>153.71000671386719</v>
@@ -24666,7 +24666,7 @@
         <v>45056</v>
       </c>
       <c r="B90">
-        <v>148.41078186035159</v>
+        <v>148.4107971191406</v>
       </c>
       <c r="C90">
         <v>154.0299987792969</v>
@@ -24689,7 +24689,7 @@
         <v>45057</v>
       </c>
       <c r="B91">
-        <v>148.7576599121094</v>
+        <v>148.75764465332031</v>
       </c>
       <c r="C91">
         <v>154.38999938964841</v>
@@ -24712,7 +24712,7 @@
         <v>45058</v>
       </c>
       <c r="B92">
-        <v>150.27040100097659</v>
+        <v>150.2703857421875</v>
       </c>
       <c r="C92">
         <v>155.96000671386719</v>
@@ -24735,7 +24735,7 @@
         <v>45061</v>
       </c>
       <c r="B93">
-        <v>150.31858825683591</v>
+        <v>150.31854248046881</v>
       </c>
       <c r="C93">
         <v>156.00999450683591</v>
@@ -24758,7 +24758,7 @@
         <v>45062</v>
       </c>
       <c r="B94">
-        <v>150.05841064453119</v>
+        <v>150.05842590332031</v>
       </c>
       <c r="C94">
         <v>155.74000549316409</v>
@@ -24804,7 +24804,7 @@
         <v>45064</v>
       </c>
       <c r="B96">
-        <v>146.96551513671881</v>
+        <v>146.96549987792969</v>
       </c>
       <c r="C96">
         <v>152.5299987792969</v>
@@ -24827,7 +24827,7 @@
         <v>45065</v>
       </c>
       <c r="B97">
-        <v>147.58216857910159</v>
+        <v>147.5821838378906</v>
       </c>
       <c r="C97">
         <v>153.16999816894531</v>
@@ -24873,7 +24873,7 @@
         <v>45069</v>
       </c>
       <c r="B99">
-        <v>142.1672058105469</v>
+        <v>142.16719055175781</v>
       </c>
       <c r="C99">
         <v>147.55000305175781</v>
@@ -24896,7 +24896,7 @@
         <v>45070</v>
       </c>
       <c r="B100">
-        <v>140.99169921875</v>
+        <v>140.99171447753909</v>
       </c>
       <c r="C100">
         <v>146.33000183105469</v>
@@ -24919,7 +24919,7 @@
         <v>45071</v>
       </c>
       <c r="B101">
-        <v>140.08598327636719</v>
+        <v>140.08599853515619</v>
       </c>
       <c r="C101">
         <v>145.38999938964841</v>
@@ -24942,7 +24942,7 @@
         <v>45072</v>
       </c>
       <c r="B102">
-        <v>140.09562683105469</v>
+        <v>140.0956115722656</v>
       </c>
       <c r="C102">
         <v>145.3999938964844</v>
@@ -24965,7 +24965,7 @@
         <v>45076</v>
       </c>
       <c r="B103">
-        <v>137.9566345214844</v>
+        <v>137.95660400390619</v>
       </c>
       <c r="C103">
         <v>143.17999267578119</v>
@@ -25011,7 +25011,7 @@
         <v>45078</v>
       </c>
       <c r="B105">
-        <v>138.70817565917969</v>
+        <v>138.7081604003906</v>
       </c>
       <c r="C105">
         <v>143.96000671386719</v>
@@ -25057,7 +25057,7 @@
         <v>45082</v>
       </c>
       <c r="B107">
-        <v>140.61592102050781</v>
+        <v>140.6159362792969</v>
       </c>
       <c r="C107">
         <v>145.94000244140619</v>
@@ -25103,7 +25103,7 @@
         <v>45084</v>
       </c>
       <c r="B109">
-        <v>139.51753234863281</v>
+        <v>139.51751708984381</v>
       </c>
       <c r="C109">
         <v>144.80000305175781</v>
@@ -25126,7 +25126,7 @@
         <v>45085</v>
       </c>
       <c r="B110">
-        <v>141.09770202636719</v>
+        <v>141.0976867675781</v>
       </c>
       <c r="C110">
         <v>146.44000244140619</v>
@@ -25149,7 +25149,7 @@
         <v>45086</v>
       </c>
       <c r="B111">
-        <v>141.21330261230469</v>
+        <v>141.21331787109381</v>
       </c>
       <c r="C111">
         <v>146.55999755859381</v>
@@ -25218,7 +25218,7 @@
         <v>45091</v>
       </c>
       <c r="B114">
-        <v>141.07841491699219</v>
+        <v>141.07843017578119</v>
       </c>
       <c r="C114">
         <v>146.41999816894531</v>
@@ -25264,7 +25264,7 @@
         <v>45093</v>
       </c>
       <c r="B116">
-        <v>144.08457946777341</v>
+        <v>144.0845947265625</v>
       </c>
       <c r="C116">
         <v>149.53999328613281</v>
@@ -25287,7 +25287,7 @@
         <v>45097</v>
       </c>
       <c r="B117">
-        <v>142.75494384765619</v>
+        <v>142.75495910644531</v>
       </c>
       <c r="C117">
         <v>148.1600036621094</v>
@@ -25310,7 +25310,7 @@
         <v>45098</v>
       </c>
       <c r="B118">
-        <v>143.98828125</v>
+        <v>143.98822021484381</v>
       </c>
       <c r="C118">
         <v>149.44000244140619</v>
@@ -25379,7 +25379,7 @@
         <v>45103</v>
       </c>
       <c r="B121">
-        <v>143.18853759765619</v>
+        <v>143.1885070800781</v>
       </c>
       <c r="C121">
         <v>148.61000061035159</v>
@@ -25402,7 +25402,7 @@
         <v>45104</v>
       </c>
       <c r="B122">
-        <v>144.54707336425781</v>
+        <v>144.5470886230469</v>
       </c>
       <c r="C122">
         <v>150.02000427246091</v>
@@ -25425,7 +25425,7 @@
         <v>45105</v>
       </c>
       <c r="B123">
-        <v>144.51817321777341</v>
+        <v>144.51820373535159</v>
       </c>
       <c r="C123">
         <v>149.99000549316409</v>
@@ -25471,7 +25471,7 @@
         <v>45107</v>
       </c>
       <c r="B125">
-        <v>146.20436096191409</v>
+        <v>146.204345703125</v>
       </c>
       <c r="C125">
         <v>151.74000549316409</v>
@@ -25517,7 +25517,7 @@
         <v>45112</v>
       </c>
       <c r="B127">
-        <v>146.68611145019531</v>
+        <v>146.68609619140619</v>
       </c>
       <c r="C127">
         <v>152.24000549316409</v>
@@ -25540,7 +25540,7 @@
         <v>45113</v>
       </c>
       <c r="B128">
-        <v>146.44523620605469</v>
+        <v>146.4452209472656</v>
       </c>
       <c r="C128">
         <v>151.99000549316409</v>
@@ -25609,7 +25609,7 @@
         <v>45118</v>
       </c>
       <c r="B131">
-        <v>142.67787170410159</v>
+        <v>142.6778564453125</v>
       </c>
       <c r="C131">
         <v>148.08000183105469</v>
@@ -25632,7 +25632,7 @@
         <v>45119</v>
       </c>
       <c r="B132">
-        <v>143.41978454589841</v>
+        <v>143.4197692871094</v>
       </c>
       <c r="C132">
         <v>148.8500061035156</v>
@@ -25655,7 +25655,7 @@
         <v>45120</v>
       </c>
       <c r="B133">
-        <v>143.51612854003909</v>
+        <v>143.51611328125</v>
       </c>
       <c r="C133">
         <v>148.94999694824219</v>
@@ -25678,7 +25678,7 @@
         <v>45121</v>
       </c>
       <c r="B134">
-        <v>144.57598876953119</v>
+        <v>144.57597351074219</v>
       </c>
       <c r="C134">
         <v>150.05000305175781</v>
@@ -25701,7 +25701,7 @@
         <v>45124</v>
       </c>
       <c r="B135">
-        <v>143.5546569824219</v>
+        <v>143.55467224121091</v>
       </c>
       <c r="C135">
         <v>148.99000549316409</v>
@@ -25724,7 +25724,7 @@
         <v>45125</v>
       </c>
       <c r="B136">
-        <v>143.824462890625</v>
+        <v>143.8244323730469</v>
       </c>
       <c r="C136">
         <v>149.27000427246091</v>
@@ -25747,7 +25747,7 @@
         <v>45126</v>
       </c>
       <c r="B137">
-        <v>144.80723571777341</v>
+        <v>144.8072204589844</v>
       </c>
       <c r="C137">
         <v>150.28999328613281</v>
@@ -25770,7 +25770,7 @@
         <v>45127</v>
       </c>
       <c r="B138">
-        <v>145.98143005371091</v>
+        <v>145.98139953613281</v>
       </c>
       <c r="C138">
         <v>150.55999755859381</v>
@@ -25816,7 +25816,7 @@
         <v>45131</v>
       </c>
       <c r="B140">
-        <v>148.75444030761719</v>
+        <v>148.7544250488281</v>
       </c>
       <c r="C140">
         <v>153.41999816894531</v>
@@ -25862,7 +25862,7 @@
         <v>45133</v>
       </c>
       <c r="B142">
-        <v>149.25862121582031</v>
+        <v>149.2586364746094</v>
       </c>
       <c r="C142">
         <v>153.94000244140619</v>
@@ -25931,7 +25931,7 @@
         <v>45138</v>
       </c>
       <c r="B145">
-        <v>151.5468444824219</v>
+        <v>151.546875</v>
       </c>
       <c r="C145">
         <v>156.30000305175781</v>
@@ -25954,7 +25954,7 @@
         <v>45139</v>
       </c>
       <c r="B146">
-        <v>151.49836730957031</v>
+        <v>151.4983825683594</v>
       </c>
       <c r="C146">
         <v>156.25</v>
@@ -26000,7 +26000,7 @@
         <v>45141</v>
       </c>
       <c r="B148">
-        <v>152.22557067871091</v>
+        <v>152.2255554199219</v>
       </c>
       <c r="C148">
         <v>157</v>
@@ -26115,7 +26115,7 @@
         <v>45148</v>
       </c>
       <c r="B153">
-        <v>151.3626403808594</v>
+        <v>151.36262512207031</v>
       </c>
       <c r="C153">
         <v>156.11000061035159</v>
@@ -26138,7 +26138,7 @@
         <v>45149</v>
       </c>
       <c r="B154">
-        <v>152.2449645996094</v>
+        <v>152.24497985839841</v>
       </c>
       <c r="C154">
         <v>157.02000427246091</v>
@@ -26161,7 +26161,7 @@
         <v>45152</v>
       </c>
       <c r="B155">
-        <v>151.05235290527341</v>
+        <v>151.0523681640625</v>
       </c>
       <c r="C155">
         <v>155.78999328613281</v>
@@ -26207,7 +26207,7 @@
         <v>45154</v>
       </c>
       <c r="B157">
-        <v>148.55082702636719</v>
+        <v>148.55084228515619</v>
       </c>
       <c r="C157">
         <v>153.21000671386719</v>
@@ -26322,7 +26322,7 @@
         <v>45161</v>
       </c>
       <c r="B162">
-        <v>148.58958435058591</v>
+        <v>148.589599609375</v>
       </c>
       <c r="C162">
         <v>153.25</v>
@@ -26414,7 +26414,7 @@
         <v>45167</v>
       </c>
       <c r="B166">
-        <v>149.19075012207031</v>
+        <v>149.19073486328119</v>
       </c>
       <c r="C166">
         <v>153.8699951171875</v>
@@ -26437,7 +26437,7 @@
         <v>45168</v>
       </c>
       <c r="B167">
-        <v>149.3555603027344</v>
+        <v>149.35557556152341</v>
       </c>
       <c r="C167">
         <v>154.03999328613281</v>
@@ -26460,7 +26460,7 @@
         <v>45169</v>
       </c>
       <c r="B168">
-        <v>149.64646911621091</v>
+        <v>149.6464538574219</v>
       </c>
       <c r="C168">
         <v>154.3399963378906</v>
@@ -26483,7 +26483,7 @@
         <v>45170</v>
       </c>
       <c r="B169">
-        <v>149.811279296875</v>
+        <v>149.81129455566409</v>
       </c>
       <c r="C169">
         <v>154.50999450683591</v>
@@ -26506,7 +26506,7 @@
         <v>45174</v>
       </c>
       <c r="B170">
-        <v>147.8042297363281</v>
+        <v>147.80424499511719</v>
       </c>
       <c r="C170">
         <v>152.44000244140619</v>
@@ -26529,7 +26529,7 @@
         <v>45175</v>
       </c>
       <c r="B171">
-        <v>147.51335144042969</v>
+        <v>147.51336669921881</v>
       </c>
       <c r="C171">
         <v>152.13999938964841</v>
@@ -26552,7 +26552,7 @@
         <v>45176</v>
       </c>
       <c r="B172">
-        <v>148.91926574707031</v>
+        <v>148.91925048828119</v>
       </c>
       <c r="C172">
         <v>153.5899963378906</v>
@@ -26598,7 +26598,7 @@
         <v>45180</v>
       </c>
       <c r="B174">
-        <v>150.0439758300781</v>
+        <v>150.04399108886719</v>
       </c>
       <c r="C174">
         <v>154.75</v>
@@ -26690,7 +26690,7 @@
         <v>45184</v>
       </c>
       <c r="B178">
-        <v>148.80291748046881</v>
+        <v>148.8028869628906</v>
       </c>
       <c r="C178">
         <v>153.4700012207031</v>
@@ -26759,7 +26759,7 @@
         <v>45189</v>
       </c>
       <c r="B181">
-        <v>148.80291748046881</v>
+        <v>148.8028869628906</v>
       </c>
       <c r="C181">
         <v>153.4700012207031</v>
@@ -26782,7 +26782,7 @@
         <v>45190</v>
       </c>
       <c r="B182">
-        <v>147.51335144042969</v>
+        <v>147.51336669921881</v>
       </c>
       <c r="C182">
         <v>152.13999938964841</v>
@@ -26828,7 +26828,7 @@
         <v>45194</v>
       </c>
       <c r="B184">
-        <v>146.07838439941409</v>
+        <v>146.078369140625</v>
       </c>
       <c r="C184">
         <v>150.6600036621094</v>
@@ -26851,7 +26851,7 @@
         <v>45195</v>
       </c>
       <c r="B185">
-        <v>144.77912902832031</v>
+        <v>144.77911376953119</v>
       </c>
       <c r="C185">
         <v>149.32000732421881</v>
@@ -26874,7 +26874,7 @@
         <v>45196</v>
       </c>
       <c r="B186">
-        <v>142.85931396484381</v>
+        <v>142.85932922363281</v>
       </c>
       <c r="C186">
         <v>147.3399963378906</v>
@@ -26897,7 +26897,7 @@
         <v>45197</v>
       </c>
       <c r="B187">
-        <v>141.8897399902344</v>
+        <v>141.88972473144531</v>
       </c>
       <c r="C187">
         <v>146.3399963378906</v>
@@ -27058,7 +27058,7 @@
         <v>45208</v>
       </c>
       <c r="B194">
-        <v>139.0003662109375</v>
+        <v>139.00035095214841</v>
       </c>
       <c r="C194">
         <v>143.36000061035159</v>
@@ -27081,7 +27081,7 @@
         <v>45209</v>
       </c>
       <c r="B195">
-        <v>140.37718200683591</v>
+        <v>140.3771667480469</v>
       </c>
       <c r="C195">
         <v>144.7799987792969</v>
@@ -27104,7 +27104,7 @@
         <v>45210</v>
       </c>
       <c r="B196">
-        <v>138.65132141113281</v>
+        <v>138.65130615234381</v>
       </c>
       <c r="C196">
         <v>143</v>
@@ -27150,7 +27150,7 @@
         <v>45212</v>
       </c>
       <c r="B198">
-        <v>140.28990173339841</v>
+        <v>140.2899169921875</v>
       </c>
       <c r="C198">
         <v>144.69000244140619</v>
@@ -27196,7 +27196,7 @@
         <v>45216</v>
       </c>
       <c r="B200">
-        <v>141.81217956542969</v>
+        <v>141.8121643066406</v>
       </c>
       <c r="C200">
         <v>146.25999450683591</v>
@@ -27219,7 +27219,7 @@
         <v>45217</v>
       </c>
       <c r="B201">
-        <v>145.467529296875</v>
+        <v>145.46751403808591</v>
       </c>
       <c r="C201">
         <v>150.0299987792969</v>
@@ -27357,7 +27357,7 @@
         <v>45225</v>
       </c>
       <c r="B207">
-        <v>146.16127014160159</v>
+        <v>146.1612548828125</v>
       </c>
       <c r="C207">
         <v>149.80000305175781</v>
@@ -27380,7 +27380,7 @@
         <v>45226</v>
       </c>
       <c r="B208">
-        <v>143.58537292480469</v>
+        <v>143.58540344238281</v>
       </c>
       <c r="C208">
         <v>147.1600036621094</v>
@@ -27426,7 +27426,7 @@
         <v>45230</v>
       </c>
       <c r="B210">
-        <v>146.38568115234381</v>
+        <v>146.38566589355469</v>
       </c>
       <c r="C210">
         <v>150.0299987792969</v>
@@ -27449,7 +27449,7 @@
         <v>45231</v>
       </c>
       <c r="B211">
-        <v>145.9758605957031</v>
+        <v>145.97587585449219</v>
       </c>
       <c r="C211">
         <v>149.61000061035159</v>
@@ -27472,7 +27472,7 @@
         <v>45232</v>
       </c>
       <c r="B212">
-        <v>147.76141357421881</v>
+        <v>147.76142883300781</v>
       </c>
       <c r="C212">
         <v>151.44000244140619</v>
@@ -27495,7 +27495,7 @@
         <v>45233</v>
       </c>
       <c r="B213">
-        <v>146.42469787597659</v>
+        <v>146.4247131347656</v>
       </c>
       <c r="C213">
         <v>150.07000732421881</v>
@@ -27564,7 +27564,7 @@
         <v>45238</v>
       </c>
       <c r="B216">
-        <v>146.36613464355469</v>
+        <v>146.36614990234381</v>
       </c>
       <c r="C216">
         <v>150.00999450683591</v>
@@ -27587,7 +27587,7 @@
         <v>45239</v>
       </c>
       <c r="B217">
-        <v>146.6979064941406</v>
+        <v>146.69789123535159</v>
       </c>
       <c r="C217">
         <v>150.3500061035156</v>
@@ -27610,7 +27610,7 @@
         <v>45240</v>
       </c>
       <c r="B218">
-        <v>147.73216247558591</v>
+        <v>147.7321472167969</v>
       </c>
       <c r="C218">
         <v>151.4100036621094</v>
@@ -27633,7 +27633,7 @@
         <v>45243</v>
       </c>
       <c r="B219">
-        <v>148.75665283203119</v>
+        <v>148.75663757324219</v>
       </c>
       <c r="C219">
         <v>152.46000671386719</v>
@@ -27679,7 +27679,7 @@
         <v>45245</v>
       </c>
       <c r="B221">
-        <v>147.7419128417969</v>
+        <v>147.74188232421881</v>
       </c>
       <c r="C221">
         <v>151.41999816894531</v>
@@ -27771,7 +27771,7 @@
         <v>45251</v>
       </c>
       <c r="B225">
-        <v>145.9758605957031</v>
+        <v>145.97587585449219</v>
       </c>
       <c r="C225">
         <v>149.61000061035159</v>
@@ -27817,7 +27817,7 @@
         <v>45254</v>
       </c>
       <c r="B227">
-        <v>147.70286560058591</v>
+        <v>147.702880859375</v>
       </c>
       <c r="C227">
         <v>151.3800048828125</v>
@@ -27909,7 +27909,7 @@
         <v>45260</v>
       </c>
       <c r="B231">
-        <v>149.79090881347659</v>
+        <v>149.7908935546875</v>
       </c>
       <c r="C231">
         <v>153.52000427246091</v>
@@ -27955,7 +27955,7 @@
         <v>45264</v>
       </c>
       <c r="B233">
-        <v>148.3663635253906</v>
+        <v>148.36634826660159</v>
       </c>
       <c r="C233">
         <v>152.05999755859381</v>
@@ -27978,7 +27978,7 @@
         <v>45265</v>
       </c>
       <c r="B234">
-        <v>143.19508361816409</v>
+        <v>143.1950988769531</v>
       </c>
       <c r="C234">
         <v>146.75999450683591</v>
@@ -28001,7 +28001,7 @@
         <v>45266</v>
       </c>
       <c r="B235">
-        <v>143.08775329589841</v>
+        <v>143.0877685546875</v>
       </c>
       <c r="C235">
         <v>146.6499938964844</v>
@@ -28047,7 +28047,7 @@
         <v>45268</v>
       </c>
       <c r="B237">
-        <v>141.62419128417969</v>
+        <v>141.62422180175781</v>
       </c>
       <c r="C237">
         <v>145.1499938964844</v>
@@ -28116,7 +28116,7 @@
         <v>45273</v>
       </c>
       <c r="B240">
-        <v>144.97090148925781</v>
+        <v>144.97088623046881</v>
       </c>
       <c r="C240">
         <v>148.58000183105469</v>
@@ -28162,7 +28162,7 @@
         <v>45275</v>
       </c>
       <c r="B242">
-        <v>140.463134765625</v>
+        <v>140.46311950683591</v>
       </c>
       <c r="C242">
         <v>143.96000671386719</v>
@@ -28254,7 +28254,7 @@
         <v>45281</v>
       </c>
       <c r="B246">
-        <v>140.7558288574219</v>
+        <v>140.75581359863281</v>
       </c>
       <c r="C246">
         <v>144.25999450683591</v>
@@ -28369,7 +28369,7 @@
         <v>45289</v>
       </c>
       <c r="B251">
-        <v>142.98042297363281</v>
+        <v>142.9804382324219</v>
       </c>
       <c r="C251">
         <v>146.53999328613281</v>
@@ -28392,7 +28392,7 @@
         <v>45293</v>
       </c>
       <c r="B252">
-        <v>145.12701416015619</v>
+        <v>145.12699890136719</v>
       </c>
       <c r="C252">
         <v>148.74000549316409</v>
@@ -28415,7 +28415,7 @@
         <v>45294</v>
       </c>
       <c r="B253">
-        <v>144.24885559082031</v>
+        <v>144.2488708496094</v>
       </c>
       <c r="C253">
         <v>147.8399963378906</v>
@@ -28438,7 +28438,7 @@
         <v>45295</v>
       </c>
       <c r="B254">
-        <v>145.0391845703125</v>
+        <v>145.03919982910159</v>
       </c>
       <c r="C254">
         <v>148.6499938964844</v>
@@ -28484,7 +28484,7 @@
         <v>45299</v>
       </c>
       <c r="B256">
-        <v>145.07823181152341</v>
+        <v>145.07820129394531</v>
       </c>
       <c r="C256">
         <v>148.69000244140619</v>
@@ -28507,7 +28507,7 @@
         <v>45300</v>
       </c>
       <c r="B257">
-        <v>145.67340087890619</v>
+        <v>145.67341613769531</v>
       </c>
       <c r="C257">
         <v>149.30000305175781</v>
@@ -28530,7 +28530,7 @@
         <v>45301</v>
       </c>
       <c r="B258">
-        <v>146.2978515625</v>
+        <v>146.2978820800781</v>
       </c>
       <c r="C258">
         <v>149.94000244140619</v>
@@ -28553,7 +28553,7 @@
         <v>45302</v>
       </c>
       <c r="B259">
-        <v>146.85401916503909</v>
+        <v>146.85400390625</v>
       </c>
       <c r="C259">
         <v>150.50999450683591</v>
@@ -28622,7 +28622,7 @@
         <v>45308</v>
       </c>
       <c r="B262">
-        <v>146.2978515625</v>
+        <v>146.2978820800781</v>
       </c>
       <c r="C262">
         <v>149.94000244140619</v>
@@ -28645,7 +28645,7 @@
         <v>45309</v>
       </c>
       <c r="B263">
-        <v>145.4544372558594</v>
+        <v>145.45442199707031</v>
       </c>
       <c r="C263">
         <v>148.13999938964841</v>
@@ -28691,7 +28691,7 @@
         <v>45313</v>
       </c>
       <c r="B265">
-        <v>145.17950439453119</v>
+        <v>145.17948913574219</v>
       </c>
       <c r="C265">
         <v>147.86000061035159</v>
@@ -28714,7 +28714,7 @@
         <v>45314</v>
       </c>
       <c r="B266">
-        <v>151.18853759765619</v>
+        <v>151.18855285644531</v>
       </c>
       <c r="C266">
         <v>153.97999572753909</v>
@@ -28852,7 +28852,7 @@
         <v>45322</v>
       </c>
       <c r="B272">
-        <v>154.29127502441409</v>
+        <v>154.291259765625</v>
       </c>
       <c r="C272">
         <v>157.13999938964841</v>
@@ -28875,7 +28875,7 @@
         <v>45323</v>
       </c>
       <c r="B273">
-        <v>156.29426574707031</v>
+        <v>156.2942810058594</v>
       </c>
       <c r="C273">
         <v>159.17999267578119</v>
@@ -28898,7 +28898,7 @@
         <v>45324</v>
       </c>
       <c r="B274">
-        <v>155.2240295410156</v>
+        <v>155.22404479980469</v>
       </c>
       <c r="C274">
         <v>158.0899963378906</v>
@@ -28944,7 +28944,7 @@
         <v>45328</v>
       </c>
       <c r="B276">
-        <v>156.07829284667969</v>
+        <v>156.0782775878906</v>
       </c>
       <c r="C276">
         <v>158.96000671386719</v>
@@ -28967,7 +28967,7 @@
         <v>45329</v>
       </c>
       <c r="B277">
-        <v>156.23536682128909</v>
+        <v>156.2353820800781</v>
       </c>
       <c r="C277">
         <v>159.1199951171875</v>
@@ -29036,7 +29036,7 @@
         <v>45334</v>
       </c>
       <c r="B280">
-        <v>154.2618103027344</v>
+        <v>154.26182556152341</v>
       </c>
       <c r="C280">
         <v>157.11000061035159</v>
@@ -29197,7 +29197,7 @@
         <v>45344</v>
       </c>
       <c r="B287">
-        <v>157.6492614746094</v>
+        <v>157.64924621582031</v>
       </c>
       <c r="C287">
         <v>160.55999755859381</v>
@@ -29266,7 +29266,7 @@
         <v>45349</v>
       </c>
       <c r="B290">
-        <v>156.41212463378909</v>
+        <v>156.412109375</v>
       </c>
       <c r="C290">
         <v>159.30000305175781</v>
@@ -29289,7 +29289,7 @@
         <v>45350</v>
       </c>
       <c r="B291">
-        <v>157.14851379394531</v>
+        <v>157.1485290527344</v>
       </c>
       <c r="C291">
         <v>160.05000305175781</v>
@@ -29312,7 +29312,7 @@
         <v>45351</v>
       </c>
       <c r="B292">
-        <v>156.0586242675781</v>
+        <v>156.05863952636719</v>
       </c>
       <c r="C292">
         <v>158.94000244140619</v>
@@ -29335,7 +29335,7 @@
         <v>45352</v>
       </c>
       <c r="B293">
-        <v>155.97027587890619</v>
+        <v>155.97026062011719</v>
       </c>
       <c r="C293">
         <v>158.8500061035156</v>
@@ -29680,7 +29680,7 @@
         <v>45373</v>
       </c>
       <c r="B308">
-        <v>158.72932434082031</v>
+        <v>158.7293395996094</v>
       </c>
       <c r="C308">
         <v>161.6600036621094</v>
@@ -29703,7 +29703,7 @@
         <v>45376</v>
       </c>
       <c r="B309">
-        <v>157.28599548339841</v>
+        <v>157.2859802246094</v>
       </c>
       <c r="C309">
         <v>160.19000244140619</v>
@@ -29749,7 +29749,7 @@
         <v>45378</v>
       </c>
       <c r="B311">
-        <v>159.662109375</v>
+        <v>159.66209411621091</v>
       </c>
       <c r="C311">
         <v>162.61000061035159</v>
@@ -29841,7 +29841,7 @@
         <v>45385</v>
       </c>
       <c r="B315">
-        <v>153.31919860839841</v>
+        <v>153.3192138671875</v>
       </c>
       <c r="C315">
         <v>156.1499938964844</v>
@@ -29887,7 +29887,7 @@
         <v>45387</v>
       </c>
       <c r="B317">
-        <v>153.2701110839844</v>
+        <v>153.27012634277341</v>
       </c>
       <c r="C317">
         <v>156.1000061035156</v>
@@ -29910,7 +29910,7 @@
         <v>45390</v>
       </c>
       <c r="B318">
-        <v>153.21119689941409</v>
+        <v>153.2112121582031</v>
       </c>
       <c r="C318">
         <v>156.03999328613281</v>
@@ -29956,7 +29956,7 @@
         <v>45392</v>
       </c>
       <c r="B320">
-        <v>154.38946533203119</v>
+        <v>154.38945007324219</v>
       </c>
       <c r="C320">
         <v>157.24000549316409</v>
@@ -33738,7 +33738,7 @@
         <v>44929</v>
       </c>
       <c r="B2">
-        <v>99.596214294433594</v>
+        <v>99.596221923828125</v>
       </c>
       <c r="C2">
         <v>106.5100021362305</v>
@@ -33807,7 +33807,7 @@
         <v>44932</v>
       </c>
       <c r="B5">
-        <v>103.3552703857422</v>
+        <v>103.3552627563477</v>
       </c>
       <c r="C5">
         <v>110.5299987792969</v>
@@ -33830,7 +33830,7 @@
         <v>44935</v>
       </c>
       <c r="B6">
-        <v>101.42897796630859</v>
+        <v>101.4289932250977</v>
       </c>
       <c r="C6">
         <v>108.4700012207031</v>
@@ -33853,7 +33853,7 @@
         <v>44936</v>
       </c>
       <c r="B7">
-        <v>102.9438171386719</v>
+        <v>102.94382476806641</v>
       </c>
       <c r="C7">
         <v>110.0899963378906</v>
@@ -33876,7 +33876,7 @@
         <v>44937</v>
       </c>
       <c r="B8">
-        <v>104.140754699707</v>
+        <v>104.14073181152339</v>
       </c>
       <c r="C8">
         <v>111.370002746582</v>
@@ -33991,7 +33991,7 @@
         <v>44945</v>
       </c>
       <c r="B13">
-        <v>104.09397125244141</v>
+        <v>104.093994140625</v>
       </c>
       <c r="C13">
         <v>111.3199996948242</v>
@@ -34014,7 +34014,7 @@
         <v>44946</v>
       </c>
       <c r="B14">
-        <v>105.99221038818359</v>
+        <v>105.9922180175781</v>
       </c>
       <c r="C14">
         <v>113.34999847412109</v>
@@ -34060,7 +34060,7 @@
         <v>44950</v>
       </c>
       <c r="B16">
-        <v>106.42234039306641</v>
+        <v>106.4223556518555</v>
       </c>
       <c r="C16">
         <v>113.80999755859381</v>
@@ -34106,7 +34106,7 @@
         <v>44952</v>
       </c>
       <c r="B18">
-        <v>110.1159591674805</v>
+        <v>110.11595153808589</v>
       </c>
       <c r="C18">
         <v>117.7600021362305</v>
@@ -34152,7 +34152,7 @@
         <v>44956</v>
       </c>
       <c r="B20">
-        <v>106.18858337402339</v>
+        <v>106.188591003418</v>
       </c>
       <c r="C20">
         <v>113.55999755859381</v>
@@ -34175,7 +34175,7 @@
         <v>44957</v>
       </c>
       <c r="B21">
-        <v>108.4795455932617</v>
+        <v>108.47955322265619</v>
       </c>
       <c r="C21">
         <v>116.0100021362305</v>
@@ -34221,7 +34221,7 @@
         <v>44959</v>
       </c>
       <c r="B23">
-        <v>103.93503570556641</v>
+        <v>103.9350280761719</v>
       </c>
       <c r="C23">
         <v>111.15000152587891</v>
@@ -34267,7 +34267,7 @@
         <v>44963</v>
       </c>
       <c r="B25">
-        <v>104.4773864746094</v>
+        <v>104.4773712158203</v>
       </c>
       <c r="C25">
         <v>111.73000335693359</v>
@@ -34313,7 +34313,7 @@
         <v>44965</v>
       </c>
       <c r="B27">
-        <v>106.52520751953119</v>
+        <v>106.5252151489258</v>
       </c>
       <c r="C27">
         <v>113.9199981689453</v>
@@ -34336,7 +34336,7 @@
         <v>44966</v>
       </c>
       <c r="B28">
-        <v>106.9273147583008</v>
+        <v>106.9272994995117</v>
       </c>
       <c r="C28">
         <v>114.34999847412109</v>
@@ -34359,7 +34359,7 @@
         <v>44967</v>
       </c>
       <c r="B29">
-        <v>111.43442535400391</v>
+        <v>111.43443298339839</v>
       </c>
       <c r="C29">
         <v>119.1699981689453</v>
@@ -34382,7 +34382,7 @@
         <v>44970</v>
       </c>
       <c r="B30">
-        <v>111.0009765625</v>
+        <v>111.0009689331055</v>
       </c>
       <c r="C30">
         <v>117.8000030517578</v>
@@ -34405,7 +34405,7 @@
         <v>44971</v>
       </c>
       <c r="B31">
-        <v>109.70062255859381</v>
+        <v>109.7006301879883</v>
       </c>
       <c r="C31">
         <v>116.4199981689453</v>
@@ -34428,7 +34428,7 @@
         <v>44972</v>
       </c>
       <c r="B32">
-        <v>109.3708190917969</v>
+        <v>109.37082672119141</v>
       </c>
       <c r="C32">
         <v>116.0699996948242</v>
@@ -34497,7 +34497,7 @@
         <v>44978</v>
       </c>
       <c r="B35">
-        <v>104.7536315917969</v>
+        <v>104.75363922119141</v>
       </c>
       <c r="C35">
         <v>111.1699981689453</v>
@@ -34520,7 +34520,7 @@
         <v>44979</v>
       </c>
       <c r="B36">
-        <v>103.39675140380859</v>
+        <v>103.39674377441411</v>
       </c>
       <c r="C36">
         <v>109.73000335693359</v>
@@ -34566,7 +34566,7 @@
         <v>44981</v>
       </c>
       <c r="B38">
-        <v>104.3578796386719</v>
+        <v>104.35788726806641</v>
       </c>
       <c r="C38">
         <v>110.75</v>
@@ -34589,7 +34589,7 @@
         <v>44984</v>
       </c>
       <c r="B39">
-        <v>104.1694259643555</v>
+        <v>104.16941070556641</v>
       </c>
       <c r="C39">
         <v>110.5500030517578</v>
@@ -34612,7 +34612,7 @@
         <v>44985</v>
       </c>
       <c r="B40">
-        <v>103.5663757324219</v>
+        <v>103.5663681030273</v>
       </c>
       <c r="C40">
         <v>109.9100036621094</v>
@@ -34681,7 +34681,7 @@
         <v>44988</v>
       </c>
       <c r="B43">
-        <v>106.29897308349609</v>
+        <v>106.2989807128906</v>
       </c>
       <c r="C43">
         <v>112.80999755859381</v>
@@ -34704,7 +34704,7 @@
         <v>44991</v>
       </c>
       <c r="B44">
-        <v>107.2412490844727</v>
+        <v>107.2412643432617</v>
       </c>
       <c r="C44">
         <v>113.80999755859381</v>
@@ -34727,7 +34727,7 @@
         <v>44992</v>
       </c>
       <c r="B45">
-        <v>105.16823577880859</v>
+        <v>105.1682434082031</v>
       </c>
       <c r="C45">
         <v>111.61000061035161</v>
@@ -34750,7 +34750,7 @@
         <v>44993</v>
       </c>
       <c r="B46">
-        <v>103.63232421875</v>
+        <v>103.6323318481445</v>
       </c>
       <c r="C46">
         <v>109.98000335693359</v>
@@ -34819,7 +34819,7 @@
         <v>44998</v>
       </c>
       <c r="B49">
-        <v>100.3908615112305</v>
+        <v>100.390869140625</v>
       </c>
       <c r="C49">
         <v>106.5400009155273</v>
@@ -34865,7 +34865,7 @@
         <v>45000</v>
       </c>
       <c r="B51">
-        <v>95.754844665527344</v>
+        <v>95.754837036132813</v>
       </c>
       <c r="C51">
         <v>101.620002746582</v>
@@ -34888,7 +34888,7 @@
         <v>45001</v>
       </c>
       <c r="B52">
-        <v>95.198883056640625</v>
+        <v>95.198890686035156</v>
       </c>
       <c r="C52">
         <v>101.0299987792969</v>
@@ -34911,7 +34911,7 @@
         <v>45002</v>
       </c>
       <c r="B53">
-        <v>94.077568054199219</v>
+        <v>94.077560424804688</v>
       </c>
       <c r="C53">
         <v>99.839996337890625</v>
@@ -34934,7 +34934,7 @@
         <v>45005</v>
       </c>
       <c r="B54">
-        <v>96.53692626953125</v>
+        <v>96.536918640136719</v>
       </c>
       <c r="C54">
         <v>102.4499969482422</v>
@@ -34957,7 +34957,7 @@
         <v>45006</v>
       </c>
       <c r="B55">
-        <v>100.8620071411133</v>
+        <v>100.86199951171881</v>
       </c>
       <c r="C55">
         <v>107.0400009155273</v>
@@ -35049,7 +35049,7 @@
         <v>45012</v>
       </c>
       <c r="B59">
-        <v>99.693572998046875</v>
+        <v>99.693580627441406</v>
       </c>
       <c r="C59">
         <v>105.8000030517578</v>
@@ -35072,7 +35072,7 @@
         <v>45013</v>
       </c>
       <c r="B60">
-        <v>100.937385559082</v>
+        <v>100.93739318847661</v>
       </c>
       <c r="C60">
         <v>107.120002746582</v>
@@ -35141,7 +35141,7 @@
         <v>45016</v>
       </c>
       <c r="B63">
-        <v>103.33078765869141</v>
+        <v>103.3308029174805</v>
       </c>
       <c r="C63">
         <v>109.6600036621094</v>
@@ -35187,7 +35187,7 @@
         <v>45020</v>
       </c>
       <c r="B65">
-        <v>108.3814239501953</v>
+        <v>108.3814392089844</v>
       </c>
       <c r="C65">
         <v>115.01999664306641</v>
@@ -35210,7 +35210,7 @@
         <v>45021</v>
       </c>
       <c r="B66">
-        <v>110.2377166748047</v>
+        <v>110.2377243041992</v>
       </c>
       <c r="C66">
         <v>116.9899978637695</v>
@@ -35233,7 +35233,7 @@
         <v>45022</v>
       </c>
       <c r="B67">
-        <v>108.4096984863281</v>
+        <v>108.40969085693359</v>
       </c>
       <c r="C67">
         <v>115.0500030517578</v>
@@ -35256,7 +35256,7 @@
         <v>45026</v>
       </c>
       <c r="B68">
-        <v>107.92913818359381</v>
+        <v>107.9291305541992</v>
       </c>
       <c r="C68">
         <v>114.5400009155273</v>
@@ -35279,7 +35279,7 @@
         <v>45027</v>
       </c>
       <c r="B69">
-        <v>108.6923751831055</v>
+        <v>108.6923828125</v>
       </c>
       <c r="C69">
         <v>115.34999847412109</v>
@@ -35302,7 +35302,7 @@
         <v>45028</v>
       </c>
       <c r="B70">
-        <v>108.5793151855469</v>
+        <v>108.57932281494141</v>
       </c>
       <c r="C70">
         <v>115.23000335693359</v>
@@ -35371,7 +35371,7 @@
         <v>45033</v>
       </c>
       <c r="B73">
-        <v>108.0798873901367</v>
+        <v>108.07989501953119</v>
       </c>
       <c r="C73">
         <v>114.6999969482422</v>
@@ -35417,7 +35417,7 @@
         <v>45035</v>
       </c>
       <c r="B75">
-        <v>109.8419723510742</v>
+        <v>109.8419647216797</v>
       </c>
       <c r="C75">
         <v>116.5699996948242</v>
@@ -35463,7 +35463,7 @@
         <v>45037</v>
       </c>
       <c r="B77">
-        <v>109.3142852783203</v>
+        <v>109.3142929077148</v>
       </c>
       <c r="C77">
         <v>116.0100021362305</v>
@@ -35509,7 +35509,7 @@
         <v>45041</v>
       </c>
       <c r="B79">
-        <v>109.7948455810547</v>
+        <v>109.7948532104492</v>
       </c>
       <c r="C79">
         <v>116.51999664306641</v>
@@ -35578,7 +35578,7 @@
         <v>45044</v>
       </c>
       <c r="B82">
-        <v>111.5097961425781</v>
+        <v>111.5098037719727</v>
       </c>
       <c r="C82">
         <v>118.3399963378906</v>
@@ -35601,7 +35601,7 @@
         <v>45047</v>
       </c>
       <c r="B83">
-        <v>108.051628112793</v>
+        <v>108.05162048339839</v>
       </c>
       <c r="C83">
         <v>114.6699981689453</v>
@@ -35647,7 +35647,7 @@
         <v>45049</v>
       </c>
       <c r="B85">
-        <v>101.7006378173828</v>
+        <v>101.7006454467773</v>
       </c>
       <c r="C85">
         <v>107.9300003051758</v>
@@ -35670,7 +35670,7 @@
         <v>45050</v>
       </c>
       <c r="B86">
-        <v>99.919731140136719</v>
+        <v>99.919723510742188</v>
       </c>
       <c r="C86">
         <v>106.0400009155273</v>
@@ -35693,7 +35693,7 @@
         <v>45051</v>
       </c>
       <c r="B87">
-        <v>102.407356262207</v>
+        <v>102.407341003418</v>
       </c>
       <c r="C87">
         <v>108.6800003051758</v>
@@ -35716,7 +35716,7 @@
         <v>45054</v>
       </c>
       <c r="B88">
-        <v>102.8125305175781</v>
+        <v>102.8125381469727</v>
       </c>
       <c r="C88">
         <v>109.11000061035161</v>
@@ -35762,7 +35762,7 @@
         <v>45056</v>
       </c>
       <c r="B90">
-        <v>101.521598815918</v>
+        <v>101.52159118652339</v>
       </c>
       <c r="C90">
         <v>107.7399978637695</v>
@@ -35854,7 +35854,7 @@
         <v>45062</v>
       </c>
       <c r="B94">
-        <v>97.441146850585938</v>
+        <v>97.441154479980469</v>
       </c>
       <c r="C94">
         <v>102.51999664306641</v>
@@ -35877,7 +35877,7 @@
         <v>45063</v>
       </c>
       <c r="B95">
-        <v>99.627204895019531</v>
+        <v>99.627197265625</v>
       </c>
       <c r="C95">
         <v>104.8199996948242</v>
@@ -35900,7 +35900,7 @@
         <v>45064</v>
       </c>
       <c r="B96">
-        <v>100.530143737793</v>
+        <v>100.53013610839839</v>
       </c>
       <c r="C96">
         <v>105.76999664306641</v>
@@ -35923,7 +35923,7 @@
         <v>45065</v>
       </c>
       <c r="B97">
-        <v>100.9958801269531</v>
+        <v>100.99587249755859</v>
       </c>
       <c r="C97">
         <v>106.2600021362305</v>
@@ -35992,7 +35992,7 @@
         <v>45070</v>
       </c>
       <c r="B100">
-        <v>102.2599639892578</v>
+        <v>102.2599716186523</v>
       </c>
       <c r="C100">
         <v>107.5899963378906</v>
@@ -36015,7 +36015,7 @@
         <v>45071</v>
       </c>
       <c r="B101">
-        <v>100.4255905151367</v>
+        <v>100.42559814453119</v>
       </c>
       <c r="C101">
         <v>105.6600036621094</v>
@@ -36061,7 +36061,7 @@
         <v>45076</v>
       </c>
       <c r="B103">
-        <v>98.885856628417969</v>
+        <v>98.885841369628906</v>
       </c>
       <c r="C103">
         <v>104.0400009155273</v>
@@ -36130,7 +36130,7 @@
         <v>45079</v>
       </c>
       <c r="B106">
-        <v>100.5206298828125</v>
+        <v>100.52064514160161</v>
       </c>
       <c r="C106">
         <v>105.7600021362305</v>
@@ -36153,7 +36153,7 @@
         <v>45082</v>
       </c>
       <c r="B107">
-        <v>100.0739288330078</v>
+        <v>100.0739212036133</v>
       </c>
       <c r="C107">
         <v>105.2900009155273</v>
@@ -36199,7 +36199,7 @@
         <v>45084</v>
       </c>
       <c r="B109">
-        <v>103.1534042358398</v>
+        <v>103.1534118652344</v>
       </c>
       <c r="C109">
         <v>108.5299987792969</v>
@@ -36222,7 +36222,7 @@
         <v>45085</v>
       </c>
       <c r="B110">
-        <v>102.8302536010742</v>
+        <v>102.8302459716797</v>
       </c>
       <c r="C110">
         <v>108.19000244140619</v>
@@ -36337,7 +36337,7 @@
         <v>45092</v>
       </c>
       <c r="B115">
-        <v>100.6442031860352</v>
+        <v>100.6441955566406</v>
       </c>
       <c r="C115">
         <v>105.88999938964839</v>
@@ -36360,7 +36360,7 @@
         <v>45093</v>
       </c>
       <c r="B116">
-        <v>99.921852111816406</v>
+        <v>99.921836853027344</v>
       </c>
       <c r="C116">
         <v>105.129997253418</v>
@@ -36383,7 +36383,7 @@
         <v>45097</v>
       </c>
       <c r="B117">
-        <v>97.631233215332031</v>
+        <v>97.631240844726563</v>
       </c>
       <c r="C117">
         <v>102.7200012207031</v>
@@ -36406,7 +36406,7 @@
         <v>45098</v>
       </c>
       <c r="B118">
-        <v>98.724281311035156</v>
+        <v>98.724273681640625</v>
       </c>
       <c r="C118">
         <v>103.870002746582</v>
@@ -36429,7 +36429,7 @@
         <v>45099</v>
       </c>
       <c r="B119">
-        <v>98.182502746582031</v>
+        <v>98.182510375976563</v>
       </c>
       <c r="C119">
         <v>103.3000030517578</v>
@@ -36475,7 +36475,7 @@
         <v>45103</v>
       </c>
       <c r="B121">
-        <v>99.123458862304688</v>
+        <v>99.123451232910156</v>
       </c>
       <c r="C121">
         <v>104.2900009155273</v>
@@ -36521,7 +36521,7 @@
         <v>45105</v>
       </c>
       <c r="B123">
-        <v>100.178466796875</v>
+        <v>100.17848205566411</v>
       </c>
       <c r="C123">
         <v>105.40000152587891</v>
@@ -36544,7 +36544,7 @@
         <v>45106</v>
       </c>
       <c r="B124">
-        <v>101.4140625</v>
+        <v>101.41407775878911</v>
       </c>
       <c r="C124">
         <v>106.6999969482422</v>
@@ -36567,7 +36567,7 @@
         <v>45107</v>
       </c>
       <c r="B125">
-        <v>101.93682861328119</v>
+        <v>101.9368209838867</v>
       </c>
       <c r="C125">
         <v>107.25</v>
@@ -36590,7 +36590,7 @@
         <v>45110</v>
       </c>
       <c r="B126">
-        <v>102.1364288330078</v>
+        <v>102.1364212036133</v>
       </c>
       <c r="C126">
         <v>107.4599990844727</v>
@@ -36705,7 +36705,7 @@
         <v>45118</v>
       </c>
       <c r="B131">
-        <v>100.72023773193359</v>
+        <v>100.7202224731445</v>
       </c>
       <c r="C131">
         <v>105.9700012207031</v>
@@ -36866,7 +36866,7 @@
         <v>45127</v>
       </c>
       <c r="B138">
-        <v>98.287063598632813</v>
+        <v>98.287055969238281</v>
       </c>
       <c r="C138">
         <v>103.4100036621094</v>
@@ -36889,7 +36889,7 @@
         <v>45128</v>
       </c>
       <c r="B139">
-        <v>98.743278503417969</v>
+        <v>98.7432861328125</v>
       </c>
       <c r="C139">
         <v>103.88999938964839</v>
@@ -36981,7 +36981,7 @@
         <v>45134</v>
       </c>
       <c r="B143">
-        <v>100.1974639892578</v>
+        <v>100.1974792480469</v>
       </c>
       <c r="C143">
         <v>105.4199981689453</v>
@@ -37004,7 +37004,7 @@
         <v>45135</v>
       </c>
       <c r="B144">
-        <v>98.999900817871094</v>
+        <v>98.999916076660156</v>
       </c>
       <c r="C144">
         <v>104.1600036621094</v>
@@ -37027,7 +37027,7 @@
         <v>45138</v>
       </c>
       <c r="B145">
-        <v>101.9273147583008</v>
+        <v>101.9273223876953</v>
       </c>
       <c r="C145">
         <v>107.2399978637695</v>
@@ -37050,7 +37050,7 @@
         <v>45139</v>
       </c>
       <c r="B146">
-        <v>101.33803558349609</v>
+        <v>101.3380432128906</v>
       </c>
       <c r="C146">
         <v>106.620002746582</v>
@@ -37073,7 +37073,7 @@
         <v>45140</v>
       </c>
       <c r="B147">
-        <v>100.0739288330078</v>
+        <v>100.0739212036133</v>
       </c>
       <c r="C147">
         <v>105.2900009155273</v>
@@ -37119,7 +37119,7 @@
         <v>45142</v>
       </c>
       <c r="B149">
-        <v>102.09840393066411</v>
+        <v>102.0983963012695</v>
       </c>
       <c r="C149">
         <v>107.4199981689453</v>
@@ -37165,7 +37165,7 @@
         <v>45146</v>
       </c>
       <c r="B151">
-        <v>102.3930587768555</v>
+        <v>102.39305114746089</v>
       </c>
       <c r="C151">
         <v>107.73000335693359</v>
@@ -37188,7 +37188,7 @@
         <v>45147</v>
       </c>
       <c r="B152">
-        <v>104.13238525390619</v>
+        <v>104.1323928833008</v>
       </c>
       <c r="C152">
         <v>109.55999755859381</v>
@@ -37211,7 +37211,7 @@
         <v>45148</v>
       </c>
       <c r="B153">
-        <v>104.6646423339844</v>
+        <v>104.66464996337891</v>
       </c>
       <c r="C153">
         <v>110.120002746582</v>
@@ -37257,7 +37257,7 @@
         <v>45152</v>
       </c>
       <c r="B155">
-        <v>106.37547302246089</v>
+        <v>106.37546539306641</v>
       </c>
       <c r="C155">
         <v>111.9199981689453</v>
@@ -37303,7 +37303,7 @@
         <v>45154</v>
       </c>
       <c r="B157">
-        <v>101.9004287719727</v>
+        <v>101.9004364013672</v>
       </c>
       <c r="C157">
         <v>106.3399963378906</v>
@@ -37326,7 +37326,7 @@
         <v>45155</v>
       </c>
       <c r="B158">
-        <v>103.8744430541992</v>
+        <v>103.8744354248047</v>
       </c>
       <c r="C158">
         <v>108.40000152587891</v>
@@ -37349,7 +37349,7 @@
         <v>45156</v>
       </c>
       <c r="B159">
-        <v>105.4459762573242</v>
+        <v>105.4459686279297</v>
       </c>
       <c r="C159">
         <v>110.0400009155273</v>
@@ -37372,7 +37372,7 @@
         <v>45159</v>
       </c>
       <c r="B160">
-        <v>104.17148590087891</v>
+        <v>104.17149353027339</v>
       </c>
       <c r="C160">
         <v>108.7099990844727</v>
@@ -37487,7 +37487,7 @@
         <v>45166</v>
       </c>
       <c r="B165">
-        <v>104.6027069091797</v>
+        <v>104.6027145385742</v>
       </c>
       <c r="C165">
         <v>109.1600036621094</v>
@@ -37510,7 +37510,7 @@
         <v>45167</v>
       </c>
       <c r="B166">
-        <v>105.22556304931641</v>
+        <v>105.22557067871089</v>
       </c>
       <c r="C166">
         <v>109.80999755859381</v>
@@ -37533,7 +37533,7 @@
         <v>45168</v>
       </c>
       <c r="B167">
-        <v>106.2508926391602</v>
+        <v>106.2509002685547</v>
       </c>
       <c r="C167">
         <v>110.879997253418</v>
@@ -37556,7 +37556,7 @@
         <v>45169</v>
       </c>
       <c r="B168">
-        <v>106.54795074462891</v>
+        <v>106.54795837402339</v>
       </c>
       <c r="C168">
         <v>111.19000244140619</v>
@@ -37579,7 +37579,7 @@
         <v>45170</v>
       </c>
       <c r="B169">
-        <v>108.7806701660156</v>
+        <v>108.7806777954102</v>
       </c>
       <c r="C169">
         <v>113.51999664306641</v>
@@ -37602,7 +37602,7 @@
         <v>45174</v>
       </c>
       <c r="B170">
-        <v>108.7902526855469</v>
+        <v>108.79026794433589</v>
       </c>
       <c r="C170">
         <v>113.5299987792969</v>
@@ -37625,7 +37625,7 @@
         <v>45175</v>
       </c>
       <c r="B171">
-        <v>109.7293395996094</v>
+        <v>109.72934722900391</v>
       </c>
       <c r="C171">
         <v>114.5100021362305</v>
@@ -37694,7 +37694,7 @@
         <v>45180</v>
       </c>
       <c r="B174">
-        <v>109.3939666748047</v>
+        <v>109.3939590454102</v>
       </c>
       <c r="C174">
         <v>114.1600036621094</v>
@@ -37717,7 +37717,7 @@
         <v>45181</v>
       </c>
       <c r="B175">
-        <v>112.5849304199219</v>
+        <v>112.58493804931641</v>
       </c>
       <c r="C175">
         <v>117.4899978637695</v>
@@ -37740,7 +37740,7 @@
         <v>45182</v>
       </c>
       <c r="B176">
-        <v>111.5787734985352</v>
+        <v>111.5787811279297</v>
       </c>
       <c r="C176">
         <v>116.44000244140619</v>
@@ -37763,7 +37763,7 @@
         <v>45183</v>
       </c>
       <c r="B177">
-        <v>113.5719375610352</v>
+        <v>113.5719299316406</v>
       </c>
       <c r="C177">
         <v>118.51999664306641</v>
@@ -37786,7 +37786,7 @@
         <v>45184</v>
       </c>
       <c r="B178">
-        <v>111.8279113769531</v>
+        <v>111.8279190063477</v>
       </c>
       <c r="C178">
         <v>116.6999969482422</v>
@@ -37809,7 +37809,7 @@
         <v>45187</v>
       </c>
       <c r="B179">
-        <v>112.7286758422852</v>
+        <v>112.7286682128906</v>
       </c>
       <c r="C179">
         <v>117.63999938964839</v>
@@ -37832,7 +37832,7 @@
         <v>45188</v>
       </c>
       <c r="B180">
-        <v>112.43161773681641</v>
+        <v>112.43162536621089</v>
       </c>
       <c r="C180">
         <v>117.3300018310547</v>
@@ -37878,7 +37878,7 @@
         <v>45190</v>
       </c>
       <c r="B182">
-        <v>109.9689178466797</v>
+        <v>109.9689102172852</v>
       </c>
       <c r="C182">
         <v>114.7600021362305</v>
@@ -37924,7 +37924,7 @@
         <v>45194</v>
       </c>
       <c r="B184">
-        <v>111.37754821777339</v>
+        <v>111.37754058837891</v>
       </c>
       <c r="C184">
         <v>116.23000335693359</v>
@@ -37970,7 +37970,7 @@
         <v>45196</v>
       </c>
       <c r="B186">
-        <v>115.1818008422852</v>
+        <v>115.1817932128906</v>
       </c>
       <c r="C186">
         <v>120.1999969482422</v>
@@ -37993,7 +37993,7 @@
         <v>45197</v>
       </c>
       <c r="B187">
-        <v>114.4822692871094</v>
+        <v>114.48227691650391</v>
       </c>
       <c r="C187">
         <v>119.4700012207031</v>
@@ -38039,7 +38039,7 @@
         <v>45201</v>
       </c>
       <c r="B189">
-        <v>110.8025817871094</v>
+        <v>110.80258941650391</v>
       </c>
       <c r="C189">
         <v>115.629997253418</v>
@@ -38062,7 +38062,7 @@
         <v>45202</v>
       </c>
       <c r="B190">
-        <v>110.99424743652339</v>
+        <v>110.99423980712891</v>
       </c>
       <c r="C190">
         <v>115.8300018310547</v>
@@ -38108,7 +38108,7 @@
         <v>45204</v>
       </c>
       <c r="B192">
-        <v>104.43979644775391</v>
+        <v>104.43980407714839</v>
       </c>
       <c r="C192">
         <v>108.9899978637695</v>
@@ -38200,7 +38200,7 @@
         <v>45210</v>
       </c>
       <c r="B196">
-        <v>102.04416656494141</v>
+        <v>102.0441818237305</v>
       </c>
       <c r="C196">
         <v>106.4899978637695</v>
@@ -38223,7 +38223,7 @@
         <v>45211</v>
       </c>
       <c r="B197">
-        <v>102.02500915527339</v>
+        <v>102.025016784668</v>
       </c>
       <c r="C197">
         <v>106.4700012207031</v>
@@ -38246,7 +38246,7 @@
         <v>45212</v>
       </c>
       <c r="B198">
-        <v>105.283073425293</v>
+        <v>105.28306579589839</v>
       </c>
       <c r="C198">
         <v>109.870002746582</v>
@@ -38292,7 +38292,7 @@
         <v>45216</v>
       </c>
       <c r="B200">
-        <v>106.73960876464839</v>
+        <v>106.73960113525391</v>
       </c>
       <c r="C200">
         <v>111.38999938964839</v>
@@ -38361,7 +38361,7 @@
         <v>45219</v>
       </c>
       <c r="B203">
-        <v>106.4425582885742</v>
+        <v>106.4425430297852</v>
       </c>
       <c r="C203">
         <v>111.0800018310547</v>
@@ -38407,7 +38407,7 @@
         <v>45223</v>
       </c>
       <c r="B205">
-        <v>103.86485290527339</v>
+        <v>103.86484527587891</v>
       </c>
       <c r="C205">
         <v>108.38999938964839</v>
@@ -38430,7 +38430,7 @@
         <v>45224</v>
       </c>
       <c r="B206">
-        <v>104.05650329589839</v>
+        <v>104.056510925293</v>
       </c>
       <c r="C206">
         <v>108.5899963378906</v>
@@ -38453,7 +38453,7 @@
         <v>45225</v>
       </c>
       <c r="B207">
-        <v>103.1078262329102</v>
+        <v>103.1078338623047</v>
       </c>
       <c r="C207">
         <v>107.59999847412109</v>
@@ -38545,7 +38545,7 @@
         <v>45231</v>
       </c>
       <c r="B211">
-        <v>101.2296524047852</v>
+        <v>101.2296600341797</v>
       </c>
       <c r="C211">
         <v>105.63999938964839</v>
@@ -38591,7 +38591,7 @@
         <v>45233</v>
       </c>
       <c r="B213">
-        <v>103.2803115844727</v>
+        <v>103.2803192138672</v>
       </c>
       <c r="C213">
         <v>107.7799987792969</v>
@@ -38614,7 +38614,7 @@
         <v>45236</v>
       </c>
       <c r="B214">
-        <v>101.450065612793</v>
+        <v>101.45005798339839</v>
       </c>
       <c r="C214">
         <v>105.870002746582</v>
@@ -38637,7 +38637,7 @@
         <v>45237</v>
       </c>
       <c r="B215">
-        <v>99.859359741210938</v>
+        <v>99.859352111816406</v>
       </c>
       <c r="C215">
         <v>104.2099990844727</v>
@@ -38706,7 +38706,7 @@
         <v>45240</v>
       </c>
       <c r="B218">
-        <v>99.418571472167969</v>
+        <v>99.418563842773438</v>
       </c>
       <c r="C218">
         <v>103.75</v>
@@ -38729,7 +38729,7 @@
         <v>45243</v>
       </c>
       <c r="B219">
-        <v>100.4630584716797</v>
+        <v>100.4630508422852</v>
       </c>
       <c r="C219">
         <v>104.8399963378906</v>
@@ -38752,7 +38752,7 @@
         <v>45244</v>
       </c>
       <c r="B220">
-        <v>100.84986877441411</v>
+        <v>100.8498611450195</v>
       </c>
       <c r="C220">
         <v>104.2900009155273</v>
@@ -38798,7 +38798,7 @@
         <v>45246</v>
       </c>
       <c r="B222">
-        <v>99.080230712890625</v>
+        <v>99.080238342285156</v>
       </c>
       <c r="C222">
         <v>102.4599990844727</v>
@@ -38821,7 +38821,7 @@
         <v>45247</v>
       </c>
       <c r="B223">
-        <v>101.4977645874023</v>
+        <v>101.4977722167969</v>
       </c>
       <c r="C223">
         <v>104.9599990844727</v>
@@ -38844,7 +38844,7 @@
         <v>45250</v>
       </c>
       <c r="B224">
-        <v>101.0529403686523</v>
+        <v>101.0529327392578</v>
       </c>
       <c r="C224">
         <v>104.5</v>
@@ -38959,7 +38959,7 @@
         <v>45258</v>
       </c>
       <c r="B229">
-        <v>100.4727249145508</v>
+        <v>100.4727325439453</v>
       </c>
       <c r="C229">
         <v>103.90000152587891</v>
@@ -39005,7 +39005,7 @@
         <v>45260</v>
       </c>
       <c r="B231">
-        <v>99.350990295410156</v>
+        <v>99.350982666015625</v>
       </c>
       <c r="C231">
         <v>102.7399978637695</v>
@@ -39028,7 +39028,7 @@
         <v>45261</v>
       </c>
       <c r="B232">
-        <v>99.592750549316406</v>
+        <v>99.592742919921875</v>
       </c>
       <c r="C232">
         <v>102.9899978637695</v>
@@ -39051,7 +39051,7 @@
         <v>45264</v>
       </c>
       <c r="B233">
-        <v>99.051223754882813</v>
+        <v>99.051216125488281</v>
       </c>
       <c r="C233">
         <v>102.4300003051758</v>
@@ -39074,7 +39074,7 @@
         <v>45265</v>
       </c>
       <c r="B234">
-        <v>97.126861572265625</v>
+        <v>97.126869201660156</v>
       </c>
       <c r="C234">
         <v>100.44000244140619</v>
@@ -39097,7 +39097,7 @@
         <v>45266</v>
       </c>
       <c r="B235">
-        <v>95.840736389160156</v>
+        <v>95.840728759765625</v>
       </c>
       <c r="C235">
         <v>99.110000610351563</v>
@@ -39120,7 +39120,7 @@
         <v>45267</v>
       </c>
       <c r="B236">
-        <v>95.173492431640625</v>
+        <v>95.173500061035156</v>
       </c>
       <c r="C236">
         <v>98.419998168945313</v>
@@ -39304,7 +39304,7 @@
         <v>45279</v>
       </c>
       <c r="B244">
-        <v>99.592750549316406</v>
+        <v>99.592742919921875</v>
       </c>
       <c r="C244">
         <v>102.9899978637695</v>
@@ -39327,7 +39327,7 @@
         <v>45280</v>
       </c>
       <c r="B245">
-        <v>97.929481506347656</v>
+        <v>97.929473876953125</v>
       </c>
       <c r="C245">
         <v>101.26999664306641</v>
@@ -39419,7 +39419,7 @@
         <v>45287</v>
       </c>
       <c r="B249">
-        <v>98.306617736816406</v>
+        <v>98.306625366210938</v>
       </c>
       <c r="C249">
         <v>101.6600036621094</v>
@@ -39580,7 +39580,7 @@
         <v>45299</v>
       </c>
       <c r="B256">
-        <v>97.591026306152344</v>
+        <v>97.591033935546875</v>
       </c>
       <c r="C256">
         <v>100.9199981689453</v>
@@ -39603,7 +39603,7 @@
         <v>45300</v>
       </c>
       <c r="B257">
-        <v>96.38226318359375</v>
+        <v>96.382255554199219</v>
       </c>
       <c r="C257">
         <v>99.669998168945313</v>
@@ -39649,7 +39649,7 @@
         <v>45302</v>
       </c>
       <c r="B259">
-        <v>95.415252685546875</v>
+        <v>95.415245056152344</v>
       </c>
       <c r="C259">
         <v>98.669998168945313</v>
@@ -39672,7 +39672,7 @@
         <v>45303</v>
       </c>
       <c r="B260">
-        <v>96.653030395507813</v>
+        <v>96.653022766113281</v>
       </c>
       <c r="C260">
         <v>99.949996948242188</v>
@@ -39695,7 +39695,7 @@
         <v>45307</v>
       </c>
       <c r="B261">
-        <v>94.467575073242188</v>
+        <v>94.467582702636719</v>
       </c>
       <c r="C261">
         <v>97.69000244140625</v>
@@ -39718,7 +39718,7 @@
         <v>45308</v>
       </c>
       <c r="B262">
-        <v>93.780998229980469</v>
+        <v>93.781005859375</v>
       </c>
       <c r="C262">
         <v>96.980003356933594</v>
@@ -39764,7 +39764,7 @@
         <v>45310</v>
       </c>
       <c r="B264">
-        <v>93.751983642578125</v>
+        <v>93.751991271972656</v>
       </c>
       <c r="C264">
         <v>96.949996948242188</v>
@@ -39948,7 +39948,7 @@
         <v>45322</v>
       </c>
       <c r="B272">
-        <v>99.418678283691406</v>
+        <v>99.418685913085938</v>
       </c>
       <c r="C272">
         <v>102.80999755859381</v>
@@ -40086,7 +40086,7 @@
         <v>45330</v>
       </c>
       <c r="B278">
-        <v>100.54042816162109</v>
+        <v>100.54042053222661</v>
       </c>
       <c r="C278">
         <v>103.9700012207031</v>
@@ -40109,7 +40109,7 @@
         <v>45331</v>
       </c>
       <c r="B279">
-        <v>98.412994384765625</v>
+        <v>98.412986755371094</v>
       </c>
       <c r="C279">
         <v>101.76999664306641</v>
@@ -40132,7 +40132,7 @@
         <v>45334</v>
       </c>
       <c r="B280">
-        <v>99.766807556152344</v>
+        <v>99.766815185546875</v>
       </c>
       <c r="C280">
         <v>103.1699981689453</v>
@@ -40155,7 +40155,7 @@
         <v>45335</v>
       </c>
       <c r="B281">
-        <v>98.907920837402344</v>
+        <v>98.907928466796875</v>
       </c>
       <c r="C281">
         <v>101.3399963378906</v>
@@ -40201,7 +40201,7 @@
         <v>45337</v>
       </c>
       <c r="B283">
-        <v>101.24057769775391</v>
+        <v>101.2405700683594</v>
       </c>
       <c r="C283">
         <v>103.73000335693359</v>
@@ -40224,7 +40224,7 @@
         <v>45338</v>
       </c>
       <c r="B284">
-        <v>101.24057769775391</v>
+        <v>101.2405700683594</v>
       </c>
       <c r="C284">
         <v>103.73000335693359</v>
@@ -40408,7 +40408,7 @@
         <v>45351</v>
       </c>
       <c r="B292">
-        <v>102.011604309082</v>
+        <v>102.01161193847661</v>
       </c>
       <c r="C292">
         <v>104.51999664306641</v>
@@ -40569,7 +40569,7 @@
         <v>45362</v>
       </c>
       <c r="B299">
-        <v>106.4036178588867</v>
+        <v>106.4036102294922</v>
       </c>
       <c r="C299">
         <v>109.01999664306641</v>
@@ -40592,7 +40592,7 @@
         <v>45363</v>
       </c>
       <c r="B300">
-        <v>105.7204055786133</v>
+        <v>105.7204132080078</v>
       </c>
       <c r="C300">
         <v>108.3199996948242</v>
@@ -40638,7 +40638,7 @@
         <v>45365</v>
       </c>
       <c r="B302">
-        <v>108.79481506347661</v>
+        <v>108.79482269287109</v>
       </c>
       <c r="C302">
         <v>111.4700012207031</v>
@@ -40707,7 +40707,7 @@
         <v>45370</v>
       </c>
       <c r="B305">
-        <v>110.3759384155273</v>
+        <v>110.3759307861328</v>
       </c>
       <c r="C305">
         <v>113.0899963378906</v>
@@ -40730,7 +40730,7 @@
         <v>45371</v>
       </c>
       <c r="B306">
-        <v>110.27834320068359</v>
+        <v>110.27833557128911</v>
       </c>
       <c r="C306">
         <v>112.9899978637695</v>
@@ -40822,7 +40822,7 @@
         <v>45377</v>
       </c>
       <c r="B310">
-        <v>111.05914306640619</v>
+        <v>111.0591354370117</v>
       </c>
       <c r="C310">
         <v>113.7900009155273</v>
@@ -40983,7 +40983,7 @@
         <v>45387</v>
       </c>
       <c r="B317">
-        <v>118.4572296142578</v>
+        <v>118.4572219848633</v>
       </c>
       <c r="C317">
         <v>121.370002746582</v>
@@ -41006,7 +41006,7 @@
         <v>45390</v>
       </c>
       <c r="B318">
-        <v>117.6569137573242</v>
+        <v>117.6569061279297</v>
       </c>
       <c r="C318">
         <v>120.5500030517578</v>
@@ -41052,7 +41052,7 @@
         <v>45392</v>
       </c>
       <c r="B320">
-        <v>119.2673034667969</v>
+        <v>119.26731109619141</v>
       </c>
       <c r="C320">
         <v>122.1999969482422</v>
@@ -41144,7 +41144,7 @@
         <v>45398</v>
       </c>
       <c r="B324">
-        <v>115.8415451049805</v>
+        <v>115.841552734375</v>
       </c>
       <c r="C324">
         <v>118.69000244140619</v>
@@ -41236,7 +41236,7 @@
         <v>45404</v>
       </c>
       <c r="B328">
-        <v>117.6666564941406</v>
+        <v>117.6666641235352</v>
       </c>
       <c r="C328">
         <v>120.55999755859381</v>
@@ -41351,7 +41351,7 @@
         <v>45411</v>
       </c>
       <c r="B333">
-        <v>116.76873779296881</v>
+        <v>116.7687454223633</v>
       </c>
       <c r="C333">
         <v>119.63999938964839</v>
@@ -41397,7 +41397,7 @@
         <v>45413</v>
       </c>
       <c r="B335">
-        <v>113.24537658691411</v>
+        <v>113.24538421630859</v>
       </c>
       <c r="C335">
         <v>116.0299987792969</v>
@@ -41489,7 +41489,7 @@
         <v>45419</v>
       </c>
       <c r="B339">
-        <v>113.3820266723633</v>
+        <v>113.38201904296881</v>
       </c>
       <c r="C339">
         <v>116.1699981689453</v>
@@ -41512,7 +41512,7 @@
         <v>45420</v>
       </c>
       <c r="B340">
-        <v>113.3625030517578</v>
+        <v>113.3625106811523</v>
       </c>
       <c r="C340">
         <v>116.15000152587891</v>
@@ -41581,7 +41581,7 @@
         <v>45425</v>
       </c>
       <c r="B343">
-        <v>115.0802688598633</v>
+        <v>115.08026123046881</v>
       </c>
       <c r="C343">
         <v>117.9100036621094</v>
@@ -44857,7 +44857,7 @@
         <v>44930</v>
       </c>
       <c r="B3">
-        <v>34.616230010986328</v>
+        <v>34.616233825683587</v>
       </c>
       <c r="C3">
         <v>40.409999847412109</v>
@@ -44880,7 +44880,7 @@
         <v>44931</v>
       </c>
       <c r="B4">
-        <v>34.410636901855469</v>
+        <v>34.410640716552727</v>
       </c>
       <c r="C4">
         <v>40.169998168945313</v>
@@ -44903,7 +44903,7 @@
         <v>44932</v>
       </c>
       <c r="B5">
-        <v>34.856082916259773</v>
+        <v>34.8560791015625</v>
       </c>
       <c r="C5">
         <v>40.689998626708977</v>
@@ -45018,7 +45018,7 @@
         <v>44939</v>
       </c>
       <c r="B10">
-        <v>32.894416809082031</v>
+        <v>32.894412994384773</v>
       </c>
       <c r="C10">
         <v>38.400001525878913</v>
@@ -45041,7 +45041,7 @@
         <v>44943</v>
       </c>
       <c r="B11">
-        <v>33.005775451660163</v>
+        <v>33.005771636962891</v>
       </c>
       <c r="C11">
         <v>38.529998779296882</v>
@@ -45064,7 +45064,7 @@
         <v>44944</v>
       </c>
       <c r="B12">
-        <v>32.5003662109375</v>
+        <v>32.500358581542969</v>
       </c>
       <c r="C12">
         <v>37.939998626708977</v>
@@ -45087,7 +45087,7 @@
         <v>44945</v>
       </c>
       <c r="B13">
-        <v>33.031478881835938</v>
+        <v>33.031471252441413</v>
       </c>
       <c r="C13">
         <v>38.560001373291023</v>
@@ -45110,7 +45110,7 @@
         <v>44946</v>
       </c>
       <c r="B14">
-        <v>33.245632171630859</v>
+        <v>33.245628356933587</v>
       </c>
       <c r="C14">
         <v>38.810001373291023</v>
@@ -45133,7 +45133,7 @@
         <v>44949</v>
       </c>
       <c r="B15">
-        <v>33.040042877197273</v>
+        <v>33.0400390625</v>
       </c>
       <c r="C15">
         <v>38.569999694824219</v>
@@ -45156,7 +45156,7 @@
         <v>44950</v>
       </c>
       <c r="B16">
-        <v>32.740222930908203</v>
+        <v>32.740219116210938</v>
       </c>
       <c r="C16">
         <v>38.220001220703118</v>
@@ -45179,7 +45179,7 @@
         <v>44951</v>
       </c>
       <c r="B17">
-        <v>32.628856658935547</v>
+        <v>32.628860473632813</v>
       </c>
       <c r="C17">
         <v>38.090000152587891</v>
@@ -45225,7 +45225,7 @@
         <v>44953</v>
       </c>
       <c r="B19">
-        <v>32.166286468505859</v>
+        <v>32.166282653808587</v>
       </c>
       <c r="C19">
         <v>37.549999237060547</v>
@@ -45248,7 +45248,7 @@
         <v>44956</v>
       </c>
       <c r="B20">
-        <v>32.611728668212891</v>
+        <v>32.611724853515618</v>
       </c>
       <c r="C20">
         <v>38.069999694824219</v>
@@ -45271,7 +45271,7 @@
         <v>44957</v>
       </c>
       <c r="B21">
-        <v>32.971508026123047</v>
+        <v>32.971515655517578</v>
       </c>
       <c r="C21">
         <v>38.490001678466797</v>
@@ -45294,7 +45294,7 @@
         <v>44958</v>
       </c>
       <c r="B22">
-        <v>33.177101135253913</v>
+        <v>33.177097320556641</v>
       </c>
       <c r="C22">
         <v>38.729999542236328</v>
@@ -45317,7 +45317,7 @@
         <v>44959</v>
       </c>
       <c r="B23">
-        <v>32.825881958007813</v>
+        <v>32.825885772705078</v>
       </c>
       <c r="C23">
         <v>38.319999694824219</v>
@@ -45363,7 +45363,7 @@
         <v>44963</v>
       </c>
       <c r="B25">
-        <v>32.183414459228523</v>
+        <v>32.183406829833977</v>
       </c>
       <c r="C25">
         <v>37.569999694824219</v>
@@ -45432,7 +45432,7 @@
         <v>44966</v>
       </c>
       <c r="B28">
-        <v>31.480985641479489</v>
+        <v>31.480978012084961</v>
       </c>
       <c r="C28">
         <v>36.75</v>
@@ -45455,7 +45455,7 @@
         <v>44967</v>
       </c>
       <c r="B29">
-        <v>31.566640853881839</v>
+        <v>31.566642761230469</v>
       </c>
       <c r="C29">
         <v>36.849998474121087</v>
@@ -45501,7 +45501,7 @@
         <v>44971</v>
       </c>
       <c r="B31">
-        <v>32.5003662109375</v>
+        <v>32.500358581542969</v>
       </c>
       <c r="C31">
         <v>37.939998626708977</v>
@@ -45570,7 +45570,7 @@
         <v>44974</v>
       </c>
       <c r="B34">
-        <v>32.680259704589837</v>
+        <v>32.680255889892578</v>
       </c>
       <c r="C34">
         <v>38.150001525878913</v>
@@ -45616,7 +45616,7 @@
         <v>44979</v>
       </c>
       <c r="B36">
-        <v>32.688823699951172</v>
+        <v>32.688819885253913</v>
       </c>
       <c r="C36">
         <v>38.159999847412109</v>
@@ -45639,7 +45639,7 @@
         <v>44980</v>
       </c>
       <c r="B37">
-        <v>32.928676605224609</v>
+        <v>32.928668975830078</v>
       </c>
       <c r="C37">
         <v>38.439998626708977</v>
@@ -45685,7 +45685,7 @@
         <v>44984</v>
       </c>
       <c r="B39">
-        <v>33.099998474121087</v>
+        <v>33.100002288818359</v>
       </c>
       <c r="C39">
         <v>38.639999389648438</v>
@@ -45708,7 +45708,7 @@
         <v>44985</v>
       </c>
       <c r="B40">
-        <v>32.603160858154297</v>
+        <v>32.603157043457031</v>
       </c>
       <c r="C40">
         <v>38.060001373291023</v>
@@ -45754,7 +45754,7 @@
         <v>44987</v>
       </c>
       <c r="B42">
-        <v>32.714523315429688</v>
+        <v>32.714519500732422</v>
       </c>
       <c r="C42">
         <v>38.189998626708977</v>
@@ -45777,7 +45777,7 @@
         <v>44988</v>
       </c>
       <c r="B43">
-        <v>32.586032867431641</v>
+        <v>32.586025238037109</v>
       </c>
       <c r="C43">
         <v>38.040000915527337</v>
@@ -45800,7 +45800,7 @@
         <v>44991</v>
       </c>
       <c r="B44">
-        <v>32.645988464355469</v>
+        <v>32.645992279052727</v>
       </c>
       <c r="C44">
         <v>38.110000610351563</v>
@@ -45846,7 +45846,7 @@
         <v>44993</v>
       </c>
       <c r="B46">
-        <v>32.294776916503913</v>
+        <v>32.294773101806641</v>
       </c>
       <c r="C46">
         <v>37.700000762939453</v>
@@ -45869,7 +45869,7 @@
         <v>44994</v>
       </c>
       <c r="B47">
-        <v>32.269077301025391</v>
+        <v>32.269073486328118</v>
       </c>
       <c r="C47">
         <v>37.669998168945313</v>
@@ -45892,7 +45892,7 @@
         <v>44995</v>
       </c>
       <c r="B48">
-        <v>32.234813690185547</v>
+        <v>32.234809875488281</v>
       </c>
       <c r="C48">
         <v>37.630001068115227</v>
@@ -45915,7 +45915,7 @@
         <v>44998</v>
       </c>
       <c r="B49">
-        <v>31.566640853881839</v>
+        <v>31.566642761230469</v>
       </c>
       <c r="C49">
         <v>36.849998474121087</v>
@@ -45938,7 +45938,7 @@
         <v>44999</v>
       </c>
       <c r="B50">
-        <v>31.515239715576168</v>
+        <v>31.515251159667969</v>
       </c>
       <c r="C50">
         <v>36.790000915527337</v>
@@ -45984,7 +45984,7 @@
         <v>45001</v>
       </c>
       <c r="B52">
-        <v>31.09549713134766</v>
+        <v>31.095499038696289</v>
       </c>
       <c r="C52">
         <v>36.299999237060547</v>
@@ -46007,7 +46007,7 @@
         <v>45002</v>
       </c>
       <c r="B53">
-        <v>30.65861892700195</v>
+        <v>30.658620834350589</v>
       </c>
       <c r="C53">
         <v>35.790000915527337</v>
@@ -46030,7 +46030,7 @@
         <v>45005</v>
       </c>
       <c r="B54">
-        <v>31.155464172363281</v>
+        <v>31.155462265014648</v>
       </c>
       <c r="C54">
         <v>36.369998931884773</v>
@@ -46053,7 +46053,7 @@
         <v>45006</v>
       </c>
       <c r="B55">
-        <v>31.395318984985352</v>
+        <v>31.395320892333981</v>
       </c>
       <c r="C55">
         <v>36.650001525878913</v>
@@ -46076,7 +46076,7 @@
         <v>45007</v>
       </c>
       <c r="B56">
-        <v>31.00126838684082</v>
+        <v>31.00127029418945</v>
       </c>
       <c r="C56">
         <v>36.189998626708977</v>
@@ -46099,7 +46099,7 @@
         <v>45008</v>
       </c>
       <c r="B57">
-        <v>30.224687576293949</v>
+        <v>30.224685668945309</v>
       </c>
       <c r="C57">
         <v>34.599998474121087</v>
@@ -46122,7 +46122,7 @@
         <v>45009</v>
       </c>
       <c r="B58">
-        <v>30.792490005493161</v>
+        <v>30.79249382019043</v>
       </c>
       <c r="C58">
         <v>35.25</v>
@@ -46145,7 +46145,7 @@
         <v>45012</v>
       </c>
       <c r="B59">
-        <v>30.923524856567379</v>
+        <v>30.923528671264648</v>
       </c>
       <c r="C59">
         <v>35.400001525878913</v>
@@ -46191,7 +46191,7 @@
         <v>45014</v>
       </c>
       <c r="B61">
-        <v>30.678934097290039</v>
+        <v>30.67893218994141</v>
       </c>
       <c r="C61">
         <v>35.119998931884773</v>
@@ -46214,7 +46214,7 @@
         <v>45015</v>
       </c>
       <c r="B62">
-        <v>30.827432632446289</v>
+        <v>30.827436447143551</v>
       </c>
       <c r="C62">
         <v>35.290000915527337</v>
@@ -46237,7 +46237,7 @@
         <v>45016</v>
       </c>
       <c r="B63">
-        <v>30.678934097290039</v>
+        <v>30.67893218994141</v>
       </c>
       <c r="C63">
         <v>35.119998931884773</v>
@@ -46260,7 +46260,7 @@
         <v>45019</v>
       </c>
       <c r="B64">
-        <v>31.159381866455082</v>
+        <v>31.159379959106449</v>
       </c>
       <c r="C64">
         <v>35.669998168945313</v>
@@ -46352,7 +46352,7 @@
         <v>45026</v>
       </c>
       <c r="B68">
-        <v>30.853639602661129</v>
+        <v>30.853643417358398</v>
       </c>
       <c r="C68">
         <v>35.319999694824219</v>
@@ -46398,7 +46398,7 @@
         <v>45028</v>
       </c>
       <c r="B70">
-        <v>30.967203140258789</v>
+        <v>30.967206954956051</v>
       </c>
       <c r="C70">
         <v>35.450000762939453</v>
@@ -46421,7 +46421,7 @@
         <v>45029</v>
       </c>
       <c r="B71">
-        <v>30.97593879699707</v>
+        <v>30.975936889648441</v>
       </c>
       <c r="C71">
         <v>35.459999084472663</v>
@@ -46444,7 +46444,7 @@
         <v>45030</v>
       </c>
       <c r="B72">
-        <v>30.740083694458011</v>
+        <v>30.740079879760739</v>
       </c>
       <c r="C72">
         <v>35.189998626708977</v>
@@ -46467,7 +46467,7 @@
         <v>45033</v>
       </c>
       <c r="B73">
-        <v>30.9322624206543</v>
+        <v>30.932260513305661</v>
       </c>
       <c r="C73">
         <v>35.409999847412109</v>
@@ -46490,7 +46490,7 @@
         <v>45034</v>
       </c>
       <c r="B74">
-        <v>30.967203140258789</v>
+        <v>30.967206954956051</v>
       </c>
       <c r="C74">
         <v>35.450000762939453</v>
@@ -46559,7 +46559,7 @@
         <v>45037</v>
       </c>
       <c r="B77">
-        <v>31.674770355224609</v>
+        <v>31.67476844787598</v>
       </c>
       <c r="C77">
         <v>36.259998321533203</v>
@@ -46582,7 +46582,7 @@
         <v>45040</v>
       </c>
       <c r="B78">
-        <v>31.88442420959473</v>
+        <v>31.884426116943359</v>
       </c>
       <c r="C78">
         <v>36.5</v>
@@ -46628,7 +46628,7 @@
         <v>45042</v>
       </c>
       <c r="B80">
-        <v>32.618206024169922</v>
+        <v>32.618202209472663</v>
       </c>
       <c r="C80">
         <v>37.340000152587891</v>
@@ -46674,7 +46674,7 @@
         <v>45044</v>
       </c>
       <c r="B82">
-        <v>32.364879608154297</v>
+        <v>32.364875793457031</v>
       </c>
       <c r="C82">
         <v>37.049999237060547</v>
@@ -46697,7 +46697,7 @@
         <v>45047</v>
       </c>
       <c r="B83">
-        <v>32.198902130126953</v>
+        <v>32.198905944824219</v>
       </c>
       <c r="C83">
         <v>36.860000610351563</v>
@@ -46720,7 +46720,7 @@
         <v>45048</v>
       </c>
       <c r="B84">
-        <v>31.666034698486332</v>
+        <v>31.66603851318359</v>
       </c>
       <c r="C84">
         <v>36.25</v>
@@ -46743,7 +46743,7 @@
         <v>45049</v>
       </c>
       <c r="B85">
-        <v>31.517538070678711</v>
+        <v>31.51753997802734</v>
       </c>
       <c r="C85">
         <v>36.080001831054688</v>
@@ -46766,7 +46766,7 @@
         <v>45050</v>
       </c>
       <c r="B86">
-        <v>30.949726104736332</v>
+        <v>30.949728012084961</v>
       </c>
       <c r="C86">
         <v>35.430000305175781</v>
@@ -46789,7 +46789,7 @@
         <v>45051</v>
       </c>
       <c r="B87">
-        <v>31.098236083984379</v>
+        <v>31.098234176635739</v>
       </c>
       <c r="C87">
         <v>35.599998474121087</v>
@@ -46812,7 +46812,7 @@
         <v>45054</v>
       </c>
       <c r="B88">
-        <v>30.967203140258789</v>
+        <v>30.967206954956051</v>
       </c>
       <c r="C88">
         <v>35.450000762939453</v>
@@ -46858,7 +46858,7 @@
         <v>45056</v>
       </c>
       <c r="B90">
-        <v>30.39940071105957</v>
+        <v>30.399394989013668</v>
       </c>
       <c r="C90">
         <v>34.799999237060547</v>
@@ -46881,7 +46881,7 @@
         <v>45057</v>
       </c>
       <c r="B91">
-        <v>29.892740249633789</v>
+        <v>29.892744064331051</v>
       </c>
       <c r="C91">
         <v>34.220001220703118</v>
@@ -46904,7 +46904,7 @@
         <v>45058</v>
       </c>
       <c r="B92">
-        <v>29.447235107421879</v>
+        <v>29.44722938537598</v>
       </c>
       <c r="C92">
         <v>33.709999084472663</v>
@@ -46927,7 +46927,7 @@
         <v>45061</v>
       </c>
       <c r="B93">
-        <v>29.61320686340332</v>
+        <v>29.61320877075195</v>
       </c>
       <c r="C93">
         <v>33.900001525878913</v>
@@ -46950,7 +46950,7 @@
         <v>45062</v>
       </c>
       <c r="B94">
-        <v>29.368610382080082</v>
+        <v>29.36861419677734</v>
       </c>
       <c r="C94">
         <v>33.619998931884773</v>
@@ -46973,7 +46973,7 @@
         <v>45063</v>
       </c>
       <c r="B95">
-        <v>29.185173034667969</v>
+        <v>29.18516731262207</v>
       </c>
       <c r="C95">
         <v>33.409999847412109</v>
@@ -47019,7 +47019,7 @@
         <v>45065</v>
       </c>
       <c r="B97">
-        <v>28.966781616210941</v>
+        <v>28.96678352355957</v>
       </c>
       <c r="C97">
         <v>33.159999847412109</v>
@@ -47042,7 +47042,7 @@
         <v>45068</v>
       </c>
       <c r="B98">
-        <v>28.95804595947266</v>
+        <v>28.958049774169918</v>
       </c>
       <c r="C98">
         <v>33.150001525878913</v>
@@ -47065,7 +47065,7 @@
         <v>45069</v>
       </c>
       <c r="B99">
-        <v>29.683090209960941</v>
+        <v>29.68309211730957</v>
       </c>
       <c r="C99">
         <v>33.979999542236328</v>
@@ -47111,7 +47111,7 @@
         <v>45071</v>
       </c>
       <c r="B101">
-        <v>28.416446685791019</v>
+        <v>28.416448593139648</v>
       </c>
       <c r="C101">
         <v>32.529998779296882</v>
@@ -47134,7 +47134,7 @@
         <v>45072</v>
       </c>
       <c r="B102">
-        <v>28.477598190307621</v>
+        <v>28.477596282958981</v>
       </c>
       <c r="C102">
         <v>32.599998474121087</v>
@@ -47157,7 +47157,7 @@
         <v>45076</v>
       </c>
       <c r="B103">
-        <v>28.233005523681641</v>
+        <v>28.233003616333011</v>
       </c>
       <c r="C103">
         <v>32.319999694824219</v>
@@ -47180,7 +47180,7 @@
         <v>45077</v>
       </c>
       <c r="B104">
-        <v>27.700141906738281</v>
+        <v>27.700139999389648</v>
       </c>
       <c r="C104">
         <v>31.70999908447266</v>
@@ -47226,7 +47226,7 @@
         <v>45079</v>
       </c>
       <c r="B106">
-        <v>28.101970672607418</v>
+        <v>28.101968765258789</v>
       </c>
       <c r="C106">
         <v>32.169998168945313</v>
@@ -47272,7 +47272,7 @@
         <v>45083</v>
       </c>
       <c r="B108">
-        <v>28.40771484375</v>
+        <v>28.407712936401371</v>
       </c>
       <c r="C108">
         <v>32.520000457763672</v>
@@ -47295,7 +47295,7 @@
         <v>45084</v>
       </c>
       <c r="B109">
-        <v>28.320356369018551</v>
+        <v>28.320358276367191</v>
       </c>
       <c r="C109">
         <v>32.419998168945313</v>
@@ -47341,7 +47341,7 @@
         <v>45086</v>
       </c>
       <c r="B111">
-        <v>28.40771484375</v>
+        <v>28.407712936401371</v>
       </c>
       <c r="C111">
         <v>32.520000457763672</v>
@@ -47364,7 +47364,7 @@
         <v>45089</v>
       </c>
       <c r="B112">
-        <v>28.171855926513668</v>
+        <v>28.171854019165039</v>
       </c>
       <c r="C112">
         <v>32.25</v>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="B113">
-        <v>28.224269866943359</v>
+        <v>28.224271774291989</v>
       </c>
       <c r="C113">
         <v>32.310001373291023</v>
@@ -47410,7 +47410,7 @@
         <v>45091</v>
       </c>
       <c r="B114">
-        <v>28.215532302856449</v>
+        <v>28.215534210205082</v>
       </c>
       <c r="C114">
         <v>32.299999237060547</v>
@@ -47433,7 +47433,7 @@
         <v>45092</v>
       </c>
       <c r="B115">
-        <v>28.71345329284668</v>
+        <v>28.71345138549805</v>
       </c>
       <c r="C115">
         <v>32.869998931884773</v>
@@ -47479,7 +47479,7 @@
         <v>45097</v>
       </c>
       <c r="B117">
-        <v>28.53874588012695</v>
+        <v>28.53874397277832</v>
       </c>
       <c r="C117">
         <v>32.669998168945313</v>
@@ -47502,7 +47502,7 @@
         <v>45098</v>
       </c>
       <c r="B118">
-        <v>28.861959457397461</v>
+        <v>28.861957550048832</v>
       </c>
       <c r="C118">
         <v>33.040000915527337</v>
@@ -47525,7 +47525,7 @@
         <v>45099</v>
       </c>
       <c r="B119">
-        <v>28.870693206787109</v>
+        <v>28.87069129943848</v>
       </c>
       <c r="C119">
         <v>33.049999237060547</v>
@@ -47548,7 +47548,7 @@
         <v>45100</v>
       </c>
       <c r="B120">
-        <v>28.95804595947266</v>
+        <v>28.958049774169918</v>
       </c>
       <c r="C120">
         <v>33.150001525878913</v>
@@ -47571,7 +47571,7 @@
         <v>45103</v>
       </c>
       <c r="B121">
-        <v>29.124021530151371</v>
+        <v>29.124019622802731</v>
       </c>
       <c r="C121">
         <v>33.340000152587891</v>
@@ -47594,7 +47594,7 @@
         <v>45104</v>
       </c>
       <c r="B122">
-        <v>29.019195556640621</v>
+        <v>29.019199371337891</v>
       </c>
       <c r="C122">
         <v>33.220001220703118</v>
@@ -47617,7 +47617,7 @@
         <v>45105</v>
       </c>
       <c r="B123">
-        <v>28.599895477294918</v>
+        <v>28.599897384643551</v>
       </c>
       <c r="C123">
         <v>32.740001678466797</v>
@@ -47640,7 +47640,7 @@
         <v>45106</v>
       </c>
       <c r="B124">
-        <v>28.71345329284668</v>
+        <v>28.71345138549805</v>
       </c>
       <c r="C124">
         <v>32.869998931884773</v>
@@ -47663,7 +47663,7 @@
         <v>45107</v>
       </c>
       <c r="B125">
-        <v>29.001724243164059</v>
+        <v>29.001728057861332</v>
       </c>
       <c r="C125">
         <v>33.200000762939453</v>
@@ -47709,7 +47709,7 @@
         <v>45112</v>
       </c>
       <c r="B127">
-        <v>29.124021530151371</v>
+        <v>29.124019622802731</v>
       </c>
       <c r="C127">
         <v>33.340000152587891</v>
@@ -47755,7 +47755,7 @@
         <v>45114</v>
       </c>
       <c r="B129">
-        <v>28.870693206787109</v>
+        <v>28.87069129943848</v>
       </c>
       <c r="C129">
         <v>33.049999237060547</v>
@@ -47778,7 +47778,7 @@
         <v>45117</v>
       </c>
       <c r="B130">
-        <v>28.678512573242191</v>
+        <v>28.67851448059082</v>
       </c>
       <c r="C130">
         <v>32.830001831054688</v>
@@ -47824,7 +47824,7 @@
         <v>45119</v>
       </c>
       <c r="B132">
-        <v>29.464704513549801</v>
+        <v>29.464700698852539</v>
       </c>
       <c r="C132">
         <v>33.729999542236328</v>
@@ -47870,7 +47870,7 @@
         <v>45121</v>
       </c>
       <c r="B134">
-        <v>29.483438491821289</v>
+        <v>29.48343658447266</v>
       </c>
       <c r="C134">
         <v>33.049999237060547</v>
@@ -47893,7 +47893,7 @@
         <v>45124</v>
       </c>
       <c r="B135">
-        <v>29.331785202026371</v>
+        <v>29.331781387329102</v>
       </c>
       <c r="C135">
         <v>32.880001068115227</v>
@@ -47916,7 +47916,7 @@
         <v>45125</v>
       </c>
       <c r="B136">
-        <v>29.519119262695309</v>
+        <v>29.519121170043949</v>
       </c>
       <c r="C136">
         <v>33.090000152587891</v>
@@ -47939,7 +47939,7 @@
         <v>45126</v>
       </c>
       <c r="B137">
-        <v>30.143581390380859</v>
+        <v>30.143583297729489</v>
       </c>
       <c r="C137">
         <v>33.790000915527337</v>
@@ -47962,7 +47962,7 @@
         <v>45127</v>
       </c>
       <c r="B138">
-        <v>30.527177810668949</v>
+        <v>30.527181625366211</v>
       </c>
       <c r="C138">
         <v>34.220001220703118</v>
@@ -47985,7 +47985,7 @@
         <v>45128</v>
       </c>
       <c r="B139">
-        <v>30.429046630859379</v>
+        <v>30.429050445556641</v>
       </c>
       <c r="C139">
         <v>34.110000610351563</v>
@@ -48008,7 +48008,7 @@
         <v>45131</v>
       </c>
       <c r="B140">
-        <v>30.295236587524411</v>
+        <v>30.295232772827148</v>
       </c>
       <c r="C140">
         <v>33.959999084472663</v>
@@ -48031,7 +48031,7 @@
         <v>45132</v>
       </c>
       <c r="B141">
-        <v>30.214950561523441</v>
+        <v>30.214948654174801</v>
       </c>
       <c r="C141">
         <v>33.869998931884773</v>
@@ -48054,7 +48054,7 @@
         <v>45133</v>
       </c>
       <c r="B142">
-        <v>30.25063323974609</v>
+        <v>30.25063514709473</v>
       </c>
       <c r="C142">
         <v>33.909999847412109</v>
@@ -48100,7 +48100,7 @@
         <v>45135</v>
       </c>
       <c r="B144">
-        <v>30.295236587524411</v>
+        <v>30.295232772827148</v>
       </c>
       <c r="C144">
         <v>33.959999084472663</v>
@@ -48146,7 +48146,7 @@
         <v>45139</v>
       </c>
       <c r="B146">
-        <v>29.724302291870121</v>
+        <v>29.724298477172852</v>
       </c>
       <c r="C146">
         <v>33.319999694824219</v>
@@ -48169,7 +48169,7 @@
         <v>45140</v>
       </c>
       <c r="B147">
-        <v>29.420991897583011</v>
+        <v>29.420993804931641</v>
       </c>
       <c r="C147">
         <v>32.979999542236328</v>
@@ -48192,7 +48192,7 @@
         <v>45141</v>
       </c>
       <c r="B148">
-        <v>29.278257369995121</v>
+        <v>29.27825927734375</v>
       </c>
       <c r="C148">
         <v>32.819999694824219</v>
@@ -48238,7 +48238,7 @@
         <v>45145</v>
       </c>
       <c r="B150">
-        <v>29.206893920898441</v>
+        <v>29.20689582824707</v>
       </c>
       <c r="C150">
         <v>32.740001678466797</v>
@@ -48330,7 +48330,7 @@
         <v>45149</v>
       </c>
       <c r="B154">
-        <v>28.939264297485352</v>
+        <v>28.939262390136719</v>
       </c>
       <c r="C154">
         <v>32.439998626708977</v>
@@ -48353,7 +48353,7 @@
         <v>45152</v>
       </c>
       <c r="B155">
-        <v>28.858974456787109</v>
+        <v>28.858976364135739</v>
       </c>
       <c r="C155">
         <v>32.349998474121087</v>
@@ -48445,7 +48445,7 @@
         <v>45156</v>
       </c>
       <c r="B159">
-        <v>28.69840049743652</v>
+        <v>28.698398590087891</v>
       </c>
       <c r="C159">
         <v>32.169998168945313</v>
@@ -48468,7 +48468,7 @@
         <v>45159</v>
       </c>
       <c r="B160">
-        <v>28.653799057006839</v>
+        <v>28.6537971496582</v>
       </c>
       <c r="C160">
         <v>32.119998931884773</v>
@@ -48491,7 +48491,7 @@
         <v>45160</v>
       </c>
       <c r="B161">
-        <v>28.73408317565918</v>
+        <v>28.734085083007809</v>
       </c>
       <c r="C161">
         <v>32.209999084472663</v>
@@ -48514,7 +48514,7 @@
         <v>45161</v>
       </c>
       <c r="B162">
-        <v>29.055234909057621</v>
+        <v>29.05523681640625</v>
       </c>
       <c r="C162">
         <v>32.569999694824219</v>
@@ -48537,7 +48537,7 @@
         <v>45162</v>
       </c>
       <c r="B163">
-        <v>29.019552230834961</v>
+        <v>29.01955413818359</v>
       </c>
       <c r="C163">
         <v>32.529998779296882</v>
@@ -48560,7 +48560,7 @@
         <v>45163</v>
       </c>
       <c r="B164">
-        <v>29.126602172851559</v>
+        <v>29.126604080200199</v>
       </c>
       <c r="C164">
         <v>32.650001525878913</v>
@@ -48583,7 +48583,7 @@
         <v>45166</v>
       </c>
       <c r="B165">
-        <v>29.349624633789059</v>
+        <v>29.349628448486332</v>
       </c>
       <c r="C165">
         <v>32.900001525878913</v>
@@ -48629,7 +48629,7 @@
         <v>45168</v>
       </c>
       <c r="B167">
-        <v>29.8848762512207</v>
+        <v>29.88487434387207</v>
       </c>
       <c r="C167">
         <v>33.5</v>
@@ -48652,7 +48652,7 @@
         <v>45169</v>
       </c>
       <c r="B168">
-        <v>29.617250442504879</v>
+        <v>29.617254257202148</v>
       </c>
       <c r="C168">
         <v>33.200000762939453</v>
@@ -48675,7 +48675,7 @@
         <v>45170</v>
       </c>
       <c r="B169">
-        <v>29.385307312011719</v>
+        <v>29.385305404663089</v>
       </c>
       <c r="C169">
         <v>32.939998626708977</v>
@@ -48721,7 +48721,7 @@
         <v>45175</v>
       </c>
       <c r="B171">
-        <v>28.832216262817379</v>
+        <v>28.83221435546875</v>
       </c>
       <c r="C171">
         <v>32.319999694824219</v>
@@ -48744,7 +48744,7 @@
         <v>45176</v>
       </c>
       <c r="B172">
-        <v>28.832216262817379</v>
+        <v>28.83221435546875</v>
       </c>
       <c r="C172">
         <v>32.319999694824219</v>
@@ -48859,7 +48859,7 @@
         <v>45183</v>
       </c>
       <c r="B177">
-        <v>30.232791900634769</v>
+        <v>30.232786178588871</v>
       </c>
       <c r="C177">
         <v>33.889999389648438</v>
@@ -48882,7 +48882,7 @@
         <v>45184</v>
       </c>
       <c r="B178">
-        <v>29.822427749633789</v>
+        <v>29.822429656982418</v>
       </c>
       <c r="C178">
         <v>33.430000305175781</v>
@@ -48951,7 +48951,7 @@
         <v>45189</v>
       </c>
       <c r="B181">
-        <v>30.15250205993652</v>
+        <v>30.152500152587891</v>
       </c>
       <c r="C181">
         <v>33.799999237060547</v>
@@ -48974,7 +48974,7 @@
         <v>45190</v>
       </c>
       <c r="B182">
-        <v>29.8848762512207</v>
+        <v>29.88487434387207</v>
       </c>
       <c r="C182">
         <v>33.5</v>
@@ -49112,7 +49112,7 @@
         <v>45198</v>
       </c>
       <c r="B188">
-        <v>28.651008605957031</v>
+        <v>28.651010513305661</v>
       </c>
       <c r="C188">
         <v>31.409999847412109</v>
@@ -49135,7 +49135,7 @@
         <v>45201</v>
       </c>
       <c r="B189">
-        <v>27.994253158569339</v>
+        <v>27.994255065917969</v>
       </c>
       <c r="C189">
         <v>30.690000534057621</v>
@@ -49227,7 +49227,7 @@
         <v>45205</v>
       </c>
       <c r="B193">
-        <v>27.820943832397461</v>
+        <v>27.820941925048832</v>
       </c>
       <c r="C193">
         <v>30.5</v>
@@ -49296,7 +49296,7 @@
         <v>45210</v>
       </c>
       <c r="B196">
-        <v>28.532428741455082</v>
+        <v>28.532430648803711</v>
       </c>
       <c r="C196">
         <v>31.280000686645511</v>
@@ -49342,7 +49342,7 @@
         <v>45212</v>
       </c>
       <c r="B198">
-        <v>27.164186477661129</v>
+        <v>27.164188385009769</v>
       </c>
       <c r="C198">
         <v>29.780000686645511</v>
@@ -49365,7 +49365,7 @@
         <v>45215</v>
       </c>
       <c r="B199">
-        <v>27.76621246337891</v>
+        <v>27.766214370727539</v>
       </c>
       <c r="C199">
         <v>30.440000534057621</v>
@@ -49457,7 +49457,7 @@
         <v>45219</v>
       </c>
       <c r="B203">
-        <v>27.2006721496582</v>
+        <v>27.200674057006839</v>
       </c>
       <c r="C203">
         <v>29.819999694824219</v>
@@ -49480,7 +49480,7 @@
         <v>45222</v>
       </c>
       <c r="B204">
-        <v>27.182428359985352</v>
+        <v>27.182426452636719</v>
       </c>
       <c r="C204">
         <v>29.79999923706055</v>
@@ -49549,7 +49549,7 @@
         <v>45225</v>
       </c>
       <c r="B207">
-        <v>27.027360916137699</v>
+        <v>27.027362823486332</v>
       </c>
       <c r="C207">
         <v>29.629999160766602</v>
@@ -49572,7 +49572,7 @@
         <v>45226</v>
       </c>
       <c r="B208">
-        <v>26.425333023071289</v>
+        <v>26.425334930419918</v>
       </c>
       <c r="C208">
         <v>28.969999313354489</v>
@@ -49595,7 +49595,7 @@
         <v>45229</v>
       </c>
       <c r="B209">
-        <v>27.218914031982418</v>
+        <v>27.218915939331051</v>
       </c>
       <c r="C209">
         <v>29.840000152587891</v>
@@ -49664,7 +49664,7 @@
         <v>45232</v>
       </c>
       <c r="B212">
-        <v>28.012496948242191</v>
+        <v>28.012495040893551</v>
       </c>
       <c r="C212">
         <v>30.70999908447266</v>
@@ -49687,7 +49687,7 @@
         <v>45233</v>
       </c>
       <c r="B213">
-        <v>28.3591194152832</v>
+        <v>28.35911750793457</v>
       </c>
       <c r="C213">
         <v>31.090000152587891</v>
@@ -49802,7 +49802,7 @@
         <v>45240</v>
       </c>
       <c r="B218">
-        <v>27.820943832397461</v>
+        <v>27.820941925048832</v>
       </c>
       <c r="C218">
         <v>30.5</v>
@@ -49894,7 +49894,7 @@
         <v>45246</v>
       </c>
       <c r="B222">
-        <v>28.450336456298832</v>
+        <v>28.450334548950199</v>
       </c>
       <c r="C222">
         <v>31.190000534057621</v>
@@ -49940,7 +49940,7 @@
         <v>45250</v>
       </c>
       <c r="B224">
-        <v>28.92465782165527</v>
+        <v>28.92465972900391</v>
       </c>
       <c r="C224">
         <v>31.70999908447266</v>
@@ -49986,7 +49986,7 @@
         <v>45252</v>
       </c>
       <c r="B226">
-        <v>29.234792709350589</v>
+        <v>29.23479080200195</v>
       </c>
       <c r="C226">
         <v>32.049999237060547</v>
@@ -50078,7 +50078,7 @@
         <v>45259</v>
       </c>
       <c r="B230">
-        <v>29.07972526550293</v>
+        <v>29.079727172851559</v>
       </c>
       <c r="C230">
         <v>31.879999160766602</v>
@@ -50101,7 +50101,7 @@
         <v>45260</v>
       </c>
       <c r="B231">
-        <v>29.088846206665039</v>
+        <v>29.088848114013668</v>
       </c>
       <c r="C231">
         <v>31.889999389648441</v>
@@ -50124,7 +50124,7 @@
         <v>45261</v>
       </c>
       <c r="B232">
-        <v>29.225673675537109</v>
+        <v>29.22567176818848</v>
       </c>
       <c r="C232">
         <v>32.040000915527337</v>
@@ -50216,7 +50216,7 @@
         <v>45267</v>
       </c>
       <c r="B236">
-        <v>26.799320220947269</v>
+        <v>26.799318313598629</v>
       </c>
       <c r="C236">
         <v>29.379999160766602</v>
@@ -50308,7 +50308,7 @@
         <v>45273</v>
       </c>
       <c r="B240">
-        <v>27.018239974975589</v>
+        <v>27.01823806762695</v>
       </c>
       <c r="C240">
         <v>29.620000839233398</v>
@@ -50331,7 +50331,7 @@
         <v>45274</v>
       </c>
       <c r="B241">
-        <v>27.337495803833011</v>
+        <v>27.337493896484379</v>
       </c>
       <c r="C241">
         <v>29.969999313354489</v>
@@ -50354,7 +50354,7 @@
         <v>45275</v>
       </c>
       <c r="B242">
-        <v>26.817562103271481</v>
+        <v>26.817564010620121</v>
       </c>
       <c r="C242">
         <v>29.39999961853027</v>
@@ -50377,7 +50377,7 @@
         <v>45278</v>
       </c>
       <c r="B243">
-        <v>26.990875244140621</v>
+        <v>26.990877151489261</v>
       </c>
       <c r="C243">
         <v>29.590000152587891</v>
@@ -50423,7 +50423,7 @@
         <v>45280</v>
       </c>
       <c r="B245">
-        <v>26.899658203125</v>
+        <v>26.899656295776371</v>
       </c>
       <c r="C245">
         <v>29.489999771118161</v>
@@ -50469,7 +50469,7 @@
         <v>45282</v>
       </c>
       <c r="B247">
-        <v>27.236967086791989</v>
+        <v>27.236965179443359</v>
       </c>
       <c r="C247">
         <v>29.14999961853027</v>
@@ -50561,7 +50561,7 @@
         <v>45289</v>
       </c>
       <c r="B251">
-        <v>27.367778778076168</v>
+        <v>27.367780685424801</v>
       </c>
       <c r="C251">
         <v>29.29000091552734</v>
@@ -50584,7 +50584,7 @@
         <v>45293</v>
       </c>
       <c r="B252">
-        <v>27.844308853149411</v>
+        <v>27.844306945800781</v>
       </c>
       <c r="C252">
         <v>29.79999923706055</v>
@@ -50653,7 +50653,7 @@
         <v>45296</v>
       </c>
       <c r="B255">
-        <v>28.29280853271484</v>
+        <v>28.292806625366211</v>
       </c>
       <c r="C255">
         <v>30.280000686645511</v>
@@ -50722,7 +50722,7 @@
         <v>45301</v>
       </c>
       <c r="B258">
-        <v>28.04052734375</v>
+        <v>28.040529251098629</v>
       </c>
       <c r="C258">
         <v>30.010000228881839</v>
@@ -50768,7 +50768,7 @@
         <v>45303</v>
       </c>
       <c r="B260">
-        <v>28.161994934082031</v>
+        <v>28.161996841430661</v>
       </c>
       <c r="C260">
         <v>30.139999389648441</v>
@@ -50814,7 +50814,7 @@
         <v>45308</v>
       </c>
       <c r="B262">
-        <v>27.610713958740231</v>
+        <v>27.610715866088871</v>
       </c>
       <c r="C262">
         <v>29.54999923706055</v>
@@ -50837,7 +50837,7 @@
         <v>45309</v>
       </c>
       <c r="B263">
-        <v>27.433185577392582</v>
+        <v>27.433187484741211</v>
       </c>
       <c r="C263">
         <v>29.360000610351559</v>
@@ -50860,7 +50860,7 @@
         <v>45310</v>
       </c>
       <c r="B264">
-        <v>27.545309066772461</v>
+        <v>27.54531097412109</v>
       </c>
       <c r="C264">
         <v>29.479999542236332</v>
@@ -50975,7 +50975,7 @@
         <v>45317</v>
       </c>
       <c r="B269">
-        <v>27.713495254516602</v>
+        <v>27.713497161865231</v>
       </c>
       <c r="C269">
         <v>29.659999847412109</v>
@@ -51021,7 +51021,7 @@
         <v>45321</v>
       </c>
       <c r="B271">
-        <v>28.068559646606449</v>
+        <v>28.068557739257809</v>
       </c>
       <c r="C271">
         <v>30.04000091552734</v>
@@ -51044,7 +51044,7 @@
         <v>45322</v>
       </c>
       <c r="B272">
-        <v>27.65743446350098</v>
+        <v>27.657436370849609</v>
       </c>
       <c r="C272">
         <v>29.60000038146973</v>
@@ -51113,7 +51113,7 @@
         <v>45327</v>
       </c>
       <c r="B275">
-        <v>27.760213851928711</v>
+        <v>27.76021575927734</v>
       </c>
       <c r="C275">
         <v>29.70999908447266</v>
@@ -51182,7 +51182,7 @@
         <v>45330</v>
       </c>
       <c r="B278">
-        <v>29.395368576049801</v>
+        <v>29.395366668701168</v>
       </c>
       <c r="C278">
         <v>31.45999908447266</v>
@@ -51251,7 +51251,7 @@
         <v>45335</v>
       </c>
       <c r="B281">
-        <v>28.460994720458981</v>
+        <v>28.460992813110352</v>
       </c>
       <c r="C281">
         <v>30.45999908447266</v>
@@ -51297,7 +51297,7 @@
         <v>45337</v>
       </c>
       <c r="B283">
-        <v>28.5544319152832</v>
+        <v>28.554433822631839</v>
       </c>
       <c r="C283">
         <v>30.559999465942379</v>
@@ -51366,7 +51366,7 @@
         <v>45343</v>
       </c>
       <c r="B286">
-        <v>28.264776229858398</v>
+        <v>28.264778137207031</v>
       </c>
       <c r="C286">
         <v>30.25</v>
@@ -51527,7 +51527,7 @@
         <v>45352</v>
       </c>
       <c r="B293">
-        <v>27.82562255859375</v>
+        <v>27.825624465942379</v>
       </c>
       <c r="C293">
         <v>29.780000686645511</v>
@@ -51550,7 +51550,7 @@
         <v>45355</v>
       </c>
       <c r="B294">
-        <v>27.433185577392582</v>
+        <v>27.433187484741211</v>
       </c>
       <c r="C294">
         <v>29.360000610351559</v>
@@ -51596,7 +51596,7 @@
         <v>45357</v>
       </c>
       <c r="B296">
-        <v>27.610713958740231</v>
+        <v>27.610715866088871</v>
       </c>
       <c r="C296">
         <v>29.54999923706055</v>
@@ -51665,7 +51665,7 @@
         <v>45362</v>
       </c>
       <c r="B299">
-        <v>28.068559646606449</v>
+        <v>28.068557739257809</v>
       </c>
       <c r="C299">
         <v>30.04000091552734</v>
@@ -51711,7 +51711,7 @@
         <v>45364</v>
       </c>
       <c r="B301">
-        <v>28.834745407104489</v>
+        <v>28.834743499755859</v>
       </c>
       <c r="C301">
         <v>30.860000610351559</v>
@@ -51849,7 +51849,7 @@
         <v>45372</v>
       </c>
       <c r="B307">
-        <v>28.863580703735352</v>
+        <v>28.863582611083981</v>
       </c>
       <c r="C307">
         <v>30.14999961853027</v>
@@ -52010,7 +52010,7 @@
         <v>45384</v>
       </c>
       <c r="B314">
-        <v>29.026327133178711</v>
+        <v>29.02632904052734</v>
       </c>
       <c r="C314">
         <v>30.319999694824219</v>
@@ -52033,7 +52033,7 @@
         <v>45385</v>
       </c>
       <c r="B315">
-        <v>28.815715789794918</v>
+        <v>28.815713882446289</v>
       </c>
       <c r="C315">
         <v>30.10000038146973</v>
@@ -52079,7 +52079,7 @@
         <v>45387</v>
       </c>
       <c r="B317">
-        <v>28.33704948425293</v>
+        <v>28.3370475769043</v>
       </c>
       <c r="C317">
         <v>29.60000038146973</v>
@@ -52148,7 +52148,7 @@
         <v>45392</v>
       </c>
       <c r="B320">
-        <v>27.906248092651371</v>
+        <v>27.90625</v>
       </c>
       <c r="C320">
         <v>29.14999961853027</v>
@@ -52286,7 +52286,7 @@
         <v>45400</v>
       </c>
       <c r="B326">
-        <v>27.590328216552731</v>
+        <v>27.590330123901371</v>
       </c>
       <c r="C326">
         <v>28.819999694824219</v>
@@ -52332,7 +52332,7 @@
         <v>45404</v>
       </c>
       <c r="B328">
-        <v>28.155155181884769</v>
+        <v>28.155157089233398</v>
       </c>
       <c r="C328">
         <v>29.409999847412109</v>
@@ -52631,7 +52631,7 @@
         <v>45421</v>
       </c>
       <c r="B341">
-        <v>29.06462287902832</v>
+        <v>29.064620971679691</v>
       </c>
       <c r="C341">
         <v>30.360000610351559</v>
@@ -52723,7 +52723,7 @@
         <v>45427</v>
       </c>
       <c r="B345">
-        <v>29.983661651611332</v>
+        <v>29.983659744262699</v>
       </c>
       <c r="C345">
         <v>31.319999694824219</v>
@@ -52792,7 +52792,7 @@
         <v>45432</v>
       </c>
       <c r="B348">
-        <v>30.012380599975589</v>
+        <v>30.012382507324219</v>
       </c>
       <c r="C348">
         <v>31.35000038146973</v>
@@ -52976,7 +52976,7 @@
         <v>45443</v>
       </c>
       <c r="B356">
-        <v>29.706035614013668</v>
+        <v>29.706033706665039</v>
       </c>
       <c r="C356">
         <v>31.030000686645511</v>
@@ -53022,7 +53022,7 @@
         <v>45447</v>
       </c>
       <c r="B358">
-        <v>29.868782043457031</v>
+        <v>29.868780136108398</v>
       </c>
       <c r="C358">
         <v>31.20000076293945</v>
@@ -53068,7 +53068,7 @@
         <v>45449</v>
       </c>
       <c r="B360">
-        <v>29.916646957397461</v>
+        <v>29.91664886474609</v>
       </c>
       <c r="C360">
         <v>31.25</v>
@@ -53229,7 +53229,7 @@
         <v>45460</v>
       </c>
       <c r="B367">
-        <v>29.619874954223629</v>
+        <v>29.619876861572269</v>
       </c>
       <c r="C367">
         <v>30.940000534057621</v>
@@ -53252,7 +53252,7 @@
         <v>45461</v>
       </c>
       <c r="B368">
-        <v>29.792196273803711</v>
+        <v>29.792194366455082</v>
       </c>
       <c r="C368">
         <v>31.120000839233398</v>
@@ -53344,7 +53344,7 @@
         <v>45468</v>
       </c>
       <c r="B372">
-        <v>30.759101867675781</v>
+        <v>30.759099960327148</v>
       </c>
       <c r="C372">
         <v>32.130001068115227</v>
@@ -53367,7 +53367,7 @@
         <v>45469</v>
       </c>
       <c r="B373">
-        <v>30.491046905517582</v>
+        <v>30.491048812866211</v>
       </c>
       <c r="C373">
         <v>31.85000038146973</v>
